--- a/research/traditional_assets/database/data/kuwait/kuwait_recreation.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_recreation.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="kwse_futurekid" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.247</v>
+        <v>-0.00626</v>
+      </c>
+      <c r="E2">
+        <v>0.0191</v>
       </c>
       <c r="G2">
-        <v>-1.607744107744108</v>
+        <v>0.075</v>
       </c>
       <c r="H2">
-        <v>-1.607744107744108</v>
+        <v>0.075</v>
       </c>
       <c r="I2">
-        <v>-2.087542087542087</v>
+        <v>0.2370689655172414</v>
       </c>
       <c r="J2">
-        <v>-2.087542087542087</v>
+        <v>0.2352291841883936</v>
       </c>
       <c r="K2">
-        <v>-10.6</v>
+        <v>4.61</v>
       </c>
       <c r="L2">
-        <v>-1.784511784511784</v>
+        <v>0.1987068965517242</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5.29</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="V2">
-        <v>0.1856140350877193</v>
+        <v>0.2128463476070529</v>
       </c>
       <c r="W2">
-        <v>-0.2054263565891473</v>
+        <v>0.1194300518134715</v>
       </c>
       <c r="X2">
-        <v>0.1114024450313397</v>
+        <v>0.1537881753105716</v>
       </c>
       <c r="Y2">
-        <v>-0.3168288016204869</v>
+        <v>-0.03435812349710009</v>
       </c>
       <c r="Z2">
-        <v>0.09635036496350366</v>
+        <v>0.5259578326909997</v>
       </c>
       <c r="AA2">
-        <v>-0.2011354420113544</v>
+        <v>0.1237206319013995</v>
       </c>
       <c r="AB2">
-        <v>0.06814225155463113</v>
+        <v>0.1127413499942161</v>
       </c>
       <c r="AC2">
-        <v>-0.2692776935659856</v>
+        <v>0.01097928190718335</v>
       </c>
       <c r="AD2">
-        <v>33.6</v>
+        <v>29.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>33.6</v>
+        <v>29.4</v>
       </c>
       <c r="AG2">
-        <v>28.31</v>
+        <v>20.95</v>
       </c>
       <c r="AH2">
-        <v>0.5410628019323671</v>
+        <v>0.4254703328509407</v>
       </c>
       <c r="AI2">
-        <v>0.4596443228454173</v>
+        <v>0.4066390041493776</v>
       </c>
       <c r="AJ2">
-        <v>0.4983277591973244</v>
+        <v>0.3454245671887881</v>
       </c>
       <c r="AK2">
-        <v>0.4174900457159711</v>
+        <v>0.3281127642913078</v>
       </c>
       <c r="AL2">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="AM2">
-        <v>1.337</v>
+        <v>0.9490000000000001</v>
       </c>
       <c r="AN2">
-        <v>-4.363636363636363</v>
+        <v>3.164693218514532</v>
       </c>
       <c r="AO2">
-        <v>-8.920863309352519</v>
+        <v>5.445544554455446</v>
       </c>
       <c r="AP2">
-        <v>-3.676623376623377</v>
+        <v>2.255113024757804</v>
       </c>
       <c r="AQ2">
-        <v>-9.274495138369485</v>
+        <v>5.795574288724973</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.247</v>
+        <v>-0.00626</v>
+      </c>
+      <c r="E3">
+        <v>0.0191</v>
       </c>
       <c r="G3">
-        <v>-1.607744107744108</v>
+        <v>0.075</v>
       </c>
       <c r="H3">
-        <v>-1.607744107744108</v>
+        <v>0.075</v>
       </c>
       <c r="I3">
-        <v>-2.087542087542087</v>
+        <v>0.2370689655172414</v>
       </c>
       <c r="J3">
-        <v>-2.087542087542087</v>
+        <v>0.2352291841883936</v>
       </c>
       <c r="K3">
-        <v>-10.6</v>
+        <v>4.61</v>
       </c>
       <c r="L3">
-        <v>-1.784511784511784</v>
+        <v>0.1987068965517242</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5.29</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="V3">
-        <v>0.1856140350877193</v>
+        <v>0.2128463476070529</v>
       </c>
       <c r="W3">
-        <v>-0.2054263565891473</v>
+        <v>0.1194300518134715</v>
       </c>
       <c r="X3">
-        <v>0.1114024450313397</v>
+        <v>0.1537881753105716</v>
       </c>
       <c r="Y3">
-        <v>-0.3168288016204869</v>
+        <v>-0.03435812349710009</v>
       </c>
       <c r="Z3">
-        <v>0.09635036496350366</v>
+        <v>0.5259578326909997</v>
       </c>
       <c r="AA3">
-        <v>-0.2011354420113544</v>
+        <v>0.1237206319013995</v>
       </c>
       <c r="AB3">
-        <v>0.06814225155463113</v>
+        <v>0.1127413499942161</v>
       </c>
       <c r="AC3">
-        <v>-0.2692776935659856</v>
+        <v>0.01097928190718335</v>
       </c>
       <c r="AD3">
-        <v>33.6</v>
+        <v>29.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>33.6</v>
+        <v>29.4</v>
       </c>
       <c r="AG3">
-        <v>28.31</v>
+        <v>20.95</v>
       </c>
       <c r="AH3">
-        <v>0.5410628019323671</v>
+        <v>0.4254703328509407</v>
       </c>
       <c r="AI3">
-        <v>0.4596443228454173</v>
+        <v>0.4066390041493776</v>
       </c>
       <c r="AJ3">
-        <v>0.4983277591973244</v>
+        <v>0.3454245671887881</v>
       </c>
       <c r="AK3">
-        <v>0.4174900457159711</v>
+        <v>0.3281127642913078</v>
       </c>
       <c r="AL3">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="AM3">
-        <v>1.337</v>
+        <v>0.9490000000000001</v>
       </c>
       <c r="AN3">
-        <v>-4.363636363636363</v>
+        <v>3.164693218514532</v>
       </c>
       <c r="AO3">
-        <v>-8.920863309352519</v>
+        <v>5.445544554455446</v>
       </c>
       <c r="AP3">
-        <v>-3.676623376623377</v>
+        <v>2.255113024757804</v>
       </c>
       <c r="AQ3">
-        <v>-9.274495138369485</v>
+        <v>5.795574288724973</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Future Kid Entertainment and Real Estate Company K.P.S.C. (KWSE:FUTUREKID)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KWSE:FUTUREKID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.425470332850941</v>
+      </c>
+      <c r="F2">
+        <v>0.16</v>
+      </c>
+      <c r="G2">
+        <v>39.7</v>
+      </c>
+      <c r="H2">
+        <v>62.2942888003402</v>
+      </c>
+      <c r="I2">
+        <v>60.65</v>
+      </c>
+      <c r="J2">
+        <v>64.90028880034011</v>
+      </c>
+      <c r="K2">
+        <v>29.4</v>
+      </c>
+      <c r="L2">
+        <v>11.056</v>
+      </c>
+      <c r="M2">
+        <v>0.112741349994216</v>
+      </c>
+      <c r="N2">
+        <v>0.107898966430573</v>
+      </c>
+      <c r="O2">
+        <v>0.0573141743119266</v>
+      </c>
+      <c r="P2">
+        <v>0.040205</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.153788175310572</v>
+      </c>
+      <c r="T2">
+        <v>0.120793055274492</v>
+      </c>
+      <c r="U2">
+        <v>1.61242318879753</v>
+      </c>
+      <c r="V2">
+        <v>1.1497486875313</v>
+      </c>
+      <c r="W2">
+        <v>10.51728199777875</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>39.7</v>
+      </c>
+      <c r="AB2">
+        <v>0.07131389334354851</v>
+      </c>
+      <c r="AC2">
+        <v>0.06742844036697249</v>
+      </c>
+      <c r="AD2">
+        <v>0.15</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="AH2">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="AI2">
+        <v>9.23</v>
+      </c>
+      <c r="AJ2">
+        <v>29.4</v>
+      </c>
+      <c r="AK2">
+        <v>29.4</v>
+      </c>
+      <c r="AL2">
+        <v>1.01</v>
+      </c>
+      <c r="AM2">
+        <v>29.4</v>
+      </c>
+      <c r="AN2">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1093677934739479</v>
+      </c>
+      <c r="C2">
+        <v>71.99942752751369</v>
+      </c>
+      <c r="D2">
+        <v>63.54942752751369</v>
+      </c>
+      <c r="E2">
+        <v>-29.4</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H2">
+        <v>39.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K2">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L2">
+        <v>5.5</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>5.5</v>
+      </c>
+      <c r="O2">
+        <v>0.8250000000000002</v>
+      </c>
+      <c r="P2">
+        <v>4.675</v>
+      </c>
+      <c r="Q2">
+        <v>8.465</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1093677934739479</v>
+      </c>
+      <c r="T2">
+        <v>0.9895378048425109</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.15</v>
+      </c>
+      <c r="W2">
+        <v>0.038845</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.109262391783737</v>
+      </c>
+      <c r="C3">
+        <v>71.40348840898214</v>
+      </c>
+      <c r="D3">
+        <v>63.64448840898215</v>
+      </c>
+      <c r="E3">
+        <v>-28.709</v>
+      </c>
+      <c r="F3">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="G3">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H3">
+        <v>39.7</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K3">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L3">
+        <v>5.5</v>
+      </c>
+      <c r="M3">
+        <v>0.0315787</v>
+      </c>
+      <c r="N3">
+        <v>5.4684213</v>
+      </c>
+      <c r="O3">
+        <v>0.8202631950000001</v>
+      </c>
+      <c r="P3">
+        <v>4.648158105</v>
+      </c>
+      <c r="Q3">
+        <v>8.438158104999999</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1099736785694313</v>
+      </c>
+      <c r="T3">
+        <v>0.9980338365002495</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.15</v>
+      </c>
+      <c r="W3">
+        <v>0.038845</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>174.1680309829094</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1091569900935261</v>
+      </c>
+      <c r="C4">
+        <v>70.8078341115484</v>
+      </c>
+      <c r="D4">
+        <v>63.73983411154841</v>
+      </c>
+      <c r="E4">
+        <v>-28.018</v>
+      </c>
+      <c r="F4">
+        <v>1.382</v>
+      </c>
+      <c r="G4">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H4">
+        <v>39.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K4">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L4">
+        <v>5.5</v>
+      </c>
+      <c r="M4">
+        <v>0.0631574</v>
+      </c>
+      <c r="N4">
+        <v>5.4368426</v>
+      </c>
+      <c r="O4">
+        <v>0.8155263900000002</v>
+      </c>
+      <c r="P4">
+        <v>4.62131621</v>
+      </c>
+      <c r="Q4">
+        <v>8.411316209999999</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1105919286668634</v>
+      </c>
+      <c r="T4">
+        <v>1.006703256559167</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.15</v>
+      </c>
+      <c r="W4">
+        <v>0.038845</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>87.08401549145468</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1090515884033152</v>
+      </c>
+      <c r="C5">
+        <v>70.21246591720315</v>
+      </c>
+      <c r="D5">
+        <v>63.83546591720314</v>
+      </c>
+      <c r="E5">
+        <v>-27.327</v>
+      </c>
+      <c r="F5">
+        <v>2.073</v>
+      </c>
+      <c r="G5">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H5">
+        <v>39.7</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K5">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L5">
+        <v>5.5</v>
+      </c>
+      <c r="M5">
+        <v>0.0947361</v>
+      </c>
+      <c r="N5">
+        <v>5.4052639</v>
+      </c>
+      <c r="O5">
+        <v>0.8107895850000001</v>
+      </c>
+      <c r="P5">
+        <v>4.594474314999999</v>
+      </c>
+      <c r="Q5">
+        <v>8.384474314999999</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1112229261889847</v>
+      </c>
+      <c r="T5">
+        <v>1.015551427547134</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.15</v>
+      </c>
+      <c r="W5">
+        <v>0.038845</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>58.05601032763645</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1089461867131043</v>
+      </c>
+      <c r="C6">
+        <v>69.61738511564215</v>
+      </c>
+      <c r="D6">
+        <v>63.93138511564215</v>
+      </c>
+      <c r="E6">
+        <v>-26.636</v>
+      </c>
+      <c r="F6">
+        <v>2.764</v>
+      </c>
+      <c r="G6">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H6">
+        <v>39.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K6">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L6">
+        <v>5.5</v>
+      </c>
+      <c r="M6">
+        <v>0.1263148</v>
+      </c>
+      <c r="N6">
+        <v>5.3736852</v>
+      </c>
+      <c r="O6">
+        <v>0.80605278</v>
+      </c>
+      <c r="P6">
+        <v>4.56763242</v>
+      </c>
+      <c r="Q6">
+        <v>8.357632419999998</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1118670694928169</v>
+      </c>
+      <c r="T6">
+        <v>1.024583935430683</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.15</v>
+      </c>
+      <c r="W6">
+        <v>0.038845</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>43.54200774572734</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1088407850228933</v>
+      </c>
+      <c r="C7">
+        <v>69.02259300432461</v>
+      </c>
+      <c r="D7">
+        <v>64.0275930043246</v>
+      </c>
+      <c r="E7">
+        <v>-25.945</v>
+      </c>
+      <c r="F7">
+        <v>3.455</v>
+      </c>
+      <c r="G7">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H7">
+        <v>39.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K7">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L7">
+        <v>5.5</v>
+      </c>
+      <c r="M7">
+        <v>0.1578935</v>
+      </c>
+      <c r="N7">
+        <v>5.3421065</v>
+      </c>
+      <c r="O7">
+        <v>0.8013159750000001</v>
+      </c>
+      <c r="P7">
+        <v>4.540790525</v>
+      </c>
+      <c r="Q7">
+        <v>8.330790524999999</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1125247737083088</v>
+      </c>
+      <c r="T7">
+        <v>1.033806601374939</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.15</v>
+      </c>
+      <c r="W7">
+        <v>0.038845</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>34.83360619658187</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1087353833326824</v>
+      </c>
+      <c r="C8">
+        <v>68.42809088853136</v>
+      </c>
+      <c r="D8">
+        <v>64.12409088853136</v>
+      </c>
+      <c r="E8">
+        <v>-25.254</v>
+      </c>
+      <c r="F8">
+        <v>4.146</v>
+      </c>
+      <c r="G8">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H8">
+        <v>39.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K8">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L8">
+        <v>5.5</v>
+      </c>
+      <c r="M8">
+        <v>0.1894722</v>
+      </c>
+      <c r="N8">
+        <v>5.3105278</v>
+      </c>
+      <c r="O8">
+        <v>0.7965791700000001</v>
+      </c>
+      <c r="P8">
+        <v>4.51394863</v>
+      </c>
+      <c r="Q8">
+        <v>8.303948629999999</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1131964716305132</v>
+      </c>
+      <c r="T8">
+        <v>1.043225494254179</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.15</v>
+      </c>
+      <c r="W8">
+        <v>0.038845</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>29.02800516381823</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1086299816424715</v>
+      </c>
+      <c r="C9">
+        <v>67.83388008142411</v>
+      </c>
+      <c r="D9">
+        <v>64.22088008142411</v>
+      </c>
+      <c r="E9">
+        <v>-24.563</v>
+      </c>
+      <c r="F9">
+        <v>4.837</v>
+      </c>
+      <c r="G9">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H9">
+        <v>39.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K9">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L9">
+        <v>5.5</v>
+      </c>
+      <c r="M9">
+        <v>0.2210509</v>
+      </c>
+      <c r="N9">
+        <v>5.2789491</v>
+      </c>
+      <c r="O9">
+        <v>0.7918423650000002</v>
+      </c>
+      <c r="P9">
+        <v>4.487106735</v>
+      </c>
+      <c r="Q9">
+        <v>8.277106735</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1138826146693242</v>
+      </c>
+      <c r="T9">
+        <v>1.052846943969532</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.15</v>
+      </c>
+      <c r="W9">
+        <v>0.038845</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>24.88114728327276</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1085245799522606</v>
+      </c>
+      <c r="C10">
+        <v>67.23996190410486</v>
+      </c>
+      <c r="D10">
+        <v>64.31796190410486</v>
+      </c>
+      <c r="E10">
+        <v>-23.872</v>
+      </c>
+      <c r="F10">
+        <v>5.528</v>
+      </c>
+      <c r="G10">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H10">
+        <v>39.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K10">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L10">
+        <v>5.5</v>
+      </c>
+      <c r="M10">
+        <v>0.2526296</v>
+      </c>
+      <c r="N10">
+        <v>5.2473704</v>
+      </c>
+      <c r="O10">
+        <v>0.7871055600000002</v>
+      </c>
+      <c r="P10">
+        <v>4.46026484</v>
+      </c>
+      <c r="Q10">
+        <v>8.25026484</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1145836738611528</v>
+      </c>
+      <c r="T10">
+        <v>1.062677555635218</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.15</v>
+      </c>
+      <c r="W10">
+        <v>0.038845</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>21.77100387286367</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1084191782620497</v>
+      </c>
+      <c r="C11">
+        <v>66.6463376856761</v>
+      </c>
+      <c r="D11">
+        <v>64.41533768567609</v>
+      </c>
+      <c r="E11">
+        <v>-23.181</v>
+      </c>
+      <c r="F11">
+        <v>6.218999999999999</v>
+      </c>
+      <c r="G11">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H11">
+        <v>39.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K11">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L11">
+        <v>5.5</v>
+      </c>
+      <c r="M11">
+        <v>0.2842083</v>
+      </c>
+      <c r="N11">
+        <v>5.2157917</v>
+      </c>
+      <c r="O11">
+        <v>0.782368755</v>
+      </c>
+      <c r="P11">
+        <v>4.433422944999999</v>
+      </c>
+      <c r="Q11">
+        <v>8.223422944999999</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1153001409473073</v>
+      </c>
+      <c r="T11">
+        <v>1.07272422470015</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.15</v>
+      </c>
+      <c r="W11">
+        <v>0.038845</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>19.35200344254548</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1083137765718387</v>
+      </c>
+      <c r="C12">
+        <v>66.05300876330141</v>
+      </c>
+      <c r="D12">
+        <v>64.5130087633014</v>
+      </c>
+      <c r="E12">
+        <v>-22.49</v>
+      </c>
+      <c r="F12">
+        <v>6.91</v>
+      </c>
+      <c r="G12">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H12">
+        <v>39.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K12">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L12">
+        <v>5.5</v>
+      </c>
+      <c r="M12">
+        <v>0.315787</v>
+      </c>
+      <c r="N12">
+        <v>5.184213</v>
+      </c>
+      <c r="O12">
+        <v>0.7776319500000001</v>
+      </c>
+      <c r="P12">
+        <v>4.40658105</v>
+      </c>
+      <c r="Q12">
+        <v>8.196581049999999</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1160325295242653</v>
+      </c>
+      <c r="T12">
+        <v>1.082994153077637</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.15</v>
+      </c>
+      <c r="W12">
+        <v>0.038845</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>17.41680309829093</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1082083748816278</v>
+      </c>
+      <c r="C13">
+        <v>65.45997648226675</v>
+      </c>
+      <c r="D13">
+        <v>64.61097648226675</v>
+      </c>
+      <c r="E13">
+        <v>-21.799</v>
+      </c>
+      <c r="F13">
+        <v>7.600999999999999</v>
+      </c>
+      <c r="G13">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H13">
+        <v>39.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K13">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L13">
+        <v>5.5</v>
+      </c>
+      <c r="M13">
+        <v>0.3473657</v>
+      </c>
+      <c r="N13">
+        <v>5.1526343</v>
+      </c>
+      <c r="O13">
+        <v>0.7728951450000001</v>
+      </c>
+      <c r="P13">
+        <v>4.379739154999999</v>
+      </c>
+      <c r="Q13">
+        <v>8.169739154999998</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1167813762714919</v>
+      </c>
+      <c r="T13">
+        <v>1.093494866362483</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.15</v>
+      </c>
+      <c r="W13">
+        <v>0.038845</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>15.83345736208267</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1081029731914169</v>
+      </c>
+      <c r="C14">
+        <v>64.8672421960421</v>
+      </c>
+      <c r="D14">
+        <v>64.7092421960421</v>
+      </c>
+      <c r="E14">
+        <v>-21.108</v>
+      </c>
+      <c r="F14">
+        <v>8.292</v>
+      </c>
+      <c r="G14">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H14">
+        <v>39.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K14">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L14">
+        <v>5.5</v>
+      </c>
+      <c r="M14">
+        <v>0.3789444</v>
+      </c>
+      <c r="N14">
+        <v>5.1210556</v>
+      </c>
+      <c r="O14">
+        <v>0.7681583400000002</v>
+      </c>
+      <c r="P14">
+        <v>4.35289726</v>
+      </c>
+      <c r="Q14">
+        <v>8.142897259999998</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1175472422629737</v>
+      </c>
+      <c r="T14">
+        <v>1.104234232221984</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.15</v>
+      </c>
+      <c r="W14">
+        <v>0.038845</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>14.51400258190911</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.107997571501206</v>
+      </c>
+      <c r="C15">
+        <v>64.27480726634393</v>
+      </c>
+      <c r="D15">
+        <v>64.80780726634393</v>
+      </c>
+      <c r="E15">
+        <v>-20.417</v>
+      </c>
+      <c r="F15">
+        <v>8.982999999999999</v>
+      </c>
+      <c r="G15">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H15">
+        <v>39.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K15">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L15">
+        <v>5.5</v>
+      </c>
+      <c r="M15">
+        <v>0.4105231</v>
+      </c>
+      <c r="N15">
+        <v>5.0894769</v>
+      </c>
+      <c r="O15">
+        <v>0.7634215350000001</v>
+      </c>
+      <c r="P15">
+        <v>4.326055365</v>
+      </c>
+      <c r="Q15">
+        <v>8.116055364999999</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1183307143692023</v>
+      </c>
+      <c r="T15">
+        <v>1.115220480055267</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.15</v>
+      </c>
+      <c r="W15">
+        <v>0.038845</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>13.39754084483918</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.108082569810995</v>
+      </c>
+      <c r="C16">
+        <v>63.50429875368622</v>
+      </c>
+      <c r="D16">
+        <v>64.72829875368622</v>
+      </c>
+      <c r="E16">
+        <v>-19.726</v>
+      </c>
+      <c r="F16">
+        <v>9.673999999999999</v>
+      </c>
+      <c r="G16">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H16">
+        <v>39.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K16">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L16">
+        <v>5.5</v>
+      </c>
+      <c r="M16">
+        <v>0.4575802</v>
+      </c>
+      <c r="N16">
+        <v>5.0424198</v>
+      </c>
+      <c r="O16">
+        <v>0.7563629700000002</v>
+      </c>
+      <c r="P16">
+        <v>4.28605683</v>
+      </c>
+      <c r="Q16">
+        <v>8.076056829999999</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.119132406756971</v>
+      </c>
+      <c r="T16">
+        <v>1.126462222024207</v>
+      </c>
+      <c r="U16">
+        <v>0.0473</v>
+      </c>
+      <c r="V16">
+        <v>0.15</v>
+      </c>
+      <c r="W16">
+        <v>0.040205</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>12.01975085460429</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1079907681207841</v>
+      </c>
+      <c r="C17">
+        <v>62.89917967958799</v>
+      </c>
+      <c r="D17">
+        <v>64.81417967958798</v>
+      </c>
+      <c r="E17">
+        <v>-19.035</v>
+      </c>
+      <c r="F17">
+        <v>10.365</v>
+      </c>
+      <c r="G17">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H17">
+        <v>39.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K17">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L17">
+        <v>5.5</v>
+      </c>
+      <c r="M17">
+        <v>0.4902644999999999</v>
+      </c>
+      <c r="N17">
+        <v>5.0097355</v>
+      </c>
+      <c r="O17">
+        <v>0.751460325</v>
+      </c>
+      <c r="P17">
+        <v>4.258275175</v>
+      </c>
+      <c r="Q17">
+        <v>8.048275174999999</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1199529624950401</v>
+      </c>
+      <c r="T17">
+        <v>1.137968475568887</v>
+      </c>
+      <c r="U17">
+        <v>0.0473</v>
+      </c>
+      <c r="V17">
+        <v>0.15</v>
+      </c>
+      <c r="W17">
+        <v>0.040205</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>11.218434130964</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1078989664305732</v>
+      </c>
+      <c r="C18">
+        <v>62.29428880034015</v>
+      </c>
+      <c r="D18">
+        <v>64.90028880034015</v>
+      </c>
+      <c r="E18">
+        <v>-18.344</v>
+      </c>
+      <c r="F18">
+        <v>11.056</v>
+      </c>
+      <c r="G18">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H18">
+        <v>39.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K18">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L18">
+        <v>5.5</v>
+      </c>
+      <c r="M18">
+        <v>0.5229488</v>
+      </c>
+      <c r="N18">
+        <v>4.9770512</v>
+      </c>
+      <c r="O18">
+        <v>0.7465576800000001</v>
+      </c>
+      <c r="P18">
+        <v>4.23049352</v>
+      </c>
+      <c r="Q18">
+        <v>8.020493519999999</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1207930552744919</v>
+      </c>
+      <c r="T18">
+        <v>1.149748687531298</v>
+      </c>
+      <c r="U18">
+        <v>0.0473</v>
+      </c>
+      <c r="V18">
+        <v>0.15</v>
+      </c>
+      <c r="W18">
+        <v>0.040205</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>10.51728199777875</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1083562647403623</v>
+      </c>
+      <c r="C19">
+        <v>61.17660124769478</v>
+      </c>
+      <c r="D19">
+        <v>64.47360124769477</v>
+      </c>
+      <c r="E19">
+        <v>-17.653</v>
+      </c>
+      <c r="F19">
+        <v>11.747</v>
+      </c>
+      <c r="G19">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H19">
+        <v>39.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K19">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L19">
+        <v>5.5</v>
+      </c>
+      <c r="M19">
+        <v>0.6002717</v>
+      </c>
+      <c r="N19">
+        <v>4.8997283</v>
+      </c>
+      <c r="O19">
+        <v>0.7349592450000001</v>
+      </c>
+      <c r="P19">
+        <v>4.164769055</v>
+      </c>
+      <c r="Q19">
+        <v>7.954769054999999</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1216533912534485</v>
+      </c>
+      <c r="T19">
+        <v>1.161812760022924</v>
+      </c>
+      <c r="U19">
+        <v>0.0511</v>
+      </c>
+      <c r="V19">
+        <v>0.15</v>
+      </c>
+      <c r="W19">
+        <v>0.043435</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>9.162517573292227</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1082967630501514</v>
+      </c>
+      <c r="C20">
+        <v>60.54080221073032</v>
+      </c>
+      <c r="D20">
+        <v>64.52880221073032</v>
+      </c>
+      <c r="E20">
+        <v>-16.962</v>
+      </c>
+      <c r="F20">
+        <v>12.438</v>
+      </c>
+      <c r="G20">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H20">
+        <v>39.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K20">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L20">
+        <v>5.5</v>
+      </c>
+      <c r="M20">
+        <v>0.6355818</v>
+      </c>
+      <c r="N20">
+        <v>4.8644182</v>
+      </c>
+      <c r="O20">
+        <v>0.7296627300000001</v>
+      </c>
+      <c r="P20">
+        <v>4.13475547</v>
+      </c>
+      <c r="Q20">
+        <v>7.924755469999999</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1225347110367699</v>
+      </c>
+      <c r="T20">
+        <v>1.174171078185077</v>
+      </c>
+      <c r="U20">
+        <v>0.0511</v>
+      </c>
+      <c r="V20">
+        <v>0.15</v>
+      </c>
+      <c r="W20">
+        <v>0.043435</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>8.653488819220438</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1082372613599404</v>
+      </c>
+      <c r="C21">
+        <v>59.90509777860883</v>
+      </c>
+      <c r="D21">
+        <v>64.58409777860882</v>
+      </c>
+      <c r="E21">
+        <v>-16.271</v>
+      </c>
+      <c r="F21">
+        <v>13.129</v>
+      </c>
+      <c r="G21">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H21">
+        <v>39.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K21">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L21">
+        <v>5.5</v>
+      </c>
+      <c r="M21">
+        <v>0.6708919</v>
+      </c>
+      <c r="N21">
+        <v>4.8291081</v>
+      </c>
+      <c r="O21">
+        <v>0.7243662150000001</v>
+      </c>
+      <c r="P21">
+        <v>4.104741885</v>
+      </c>
+      <c r="Q21">
+        <v>7.894741884999999</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1234377918023956</v>
+      </c>
+      <c r="T21">
+        <v>1.186834540005555</v>
+      </c>
+      <c r="U21">
+        <v>0.0511</v>
+      </c>
+      <c r="V21">
+        <v>0.15</v>
+      </c>
+      <c r="W21">
+        <v>0.043435</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>8.198042039261466</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1081777596697295</v>
+      </c>
+      <c r="C22">
+        <v>59.26948819474317</v>
+      </c>
+      <c r="D22">
+        <v>64.63948819474317</v>
+      </c>
+      <c r="E22">
+        <v>-15.58</v>
+      </c>
+      <c r="F22">
+        <v>13.82</v>
+      </c>
+      <c r="G22">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H22">
+        <v>39.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K22">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L22">
+        <v>5.5</v>
+      </c>
+      <c r="M22">
+        <v>0.706202</v>
+      </c>
+      <c r="N22">
+        <v>4.793798</v>
+      </c>
+      <c r="O22">
+        <v>0.7190697</v>
+      </c>
+      <c r="P22">
+        <v>4.074728299999999</v>
+      </c>
+      <c r="Q22">
+        <v>7.864728299999999</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1243634495871619</v>
+      </c>
+      <c r="T22">
+        <v>1.199814588371544</v>
+      </c>
+      <c r="U22">
+        <v>0.0511</v>
+      </c>
+      <c r="V22">
+        <v>0.15</v>
+      </c>
+      <c r="W22">
+        <v>0.043435</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>7.788139937298393</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1084574079795186</v>
+      </c>
+      <c r="C23">
+        <v>58.31898494672389</v>
+      </c>
+      <c r="D23">
+        <v>64.37998494672388</v>
+      </c>
+      <c r="E23">
+        <v>-14.889</v>
+      </c>
+      <c r="F23">
+        <v>14.511</v>
+      </c>
+      <c r="G23">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H23">
+        <v>39.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K23">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L23">
+        <v>5.5</v>
+      </c>
+      <c r="M23">
+        <v>0.769083</v>
+      </c>
+      <c r="N23">
+        <v>4.730917</v>
+      </c>
+      <c r="O23">
+        <v>0.7096375500000001</v>
+      </c>
+      <c r="P23">
+        <v>4.02127945</v>
+      </c>
+      <c r="Q23">
+        <v>7.811279449999999</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.125312541746226</v>
+      </c>
+      <c r="T23">
+        <v>1.213123245556926</v>
+      </c>
+      <c r="U23">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V23">
+        <v>0.15</v>
+      </c>
+      <c r="W23">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>7.151373778902927</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1084140562893077</v>
+      </c>
+      <c r="C24">
+        <v>57.66807715384357</v>
+      </c>
+      <c r="D24">
+        <v>64.42007715384356</v>
+      </c>
+      <c r="E24">
+        <v>-14.198</v>
+      </c>
+      <c r="F24">
+        <v>15.202</v>
+      </c>
+      <c r="G24">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H24">
+        <v>39.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K24">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L24">
+        <v>5.5</v>
+      </c>
+      <c r="M24">
+        <v>0.805706</v>
+      </c>
+      <c r="N24">
+        <v>4.694294</v>
+      </c>
+      <c r="O24">
+        <v>0.7041441000000002</v>
+      </c>
+      <c r="P24">
+        <v>3.9901499</v>
+      </c>
+      <c r="Q24">
+        <v>7.7801499</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1262859696016765</v>
+      </c>
+      <c r="T24">
+        <v>1.226773150362446</v>
+      </c>
+      <c r="U24">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V24">
+        <v>0.15</v>
+      </c>
+      <c r="W24">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>6.82631133440734</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1083707045990968</v>
+      </c>
+      <c r="C25">
+        <v>57.01721932638918</v>
+      </c>
+      <c r="D25">
+        <v>64.46021932638918</v>
+      </c>
+      <c r="E25">
+        <v>-13.507</v>
+      </c>
+      <c r="F25">
+        <v>15.893</v>
+      </c>
+      <c r="G25">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H25">
+        <v>39.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K25">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L25">
+        <v>5.5</v>
+      </c>
+      <c r="M25">
+        <v>0.842329</v>
+      </c>
+      <c r="N25">
+        <v>4.657671</v>
+      </c>
+      <c r="O25">
+        <v>0.69865065</v>
+      </c>
+      <c r="P25">
+        <v>3.959020349999999</v>
+      </c>
+      <c r="Q25">
+        <v>7.749020349999999</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1272846812975282</v>
+      </c>
+      <c r="T25">
+        <v>1.240777598149928</v>
+      </c>
+      <c r="U25">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V25">
+        <v>0.15</v>
+      </c>
+      <c r="W25">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>6.529515189433107</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1083273529088858</v>
+      </c>
+      <c r="C26">
+        <v>56.36641155782402</v>
+      </c>
+      <c r="D26">
+        <v>64.50041155782402</v>
+      </c>
+      <c r="E26">
+        <v>-12.816</v>
+      </c>
+      <c r="F26">
+        <v>16.584</v>
+      </c>
+      <c r="G26">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H26">
+        <v>39.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K26">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L26">
+        <v>5.5</v>
+      </c>
+      <c r="M26">
+        <v>0.8789520000000001</v>
+      </c>
+      <c r="N26">
+        <v>4.621048</v>
+      </c>
+      <c r="O26">
+        <v>0.6931572000000001</v>
+      </c>
+      <c r="P26">
+        <v>3.9278908</v>
+      </c>
+      <c r="Q26">
+        <v>7.717890799999999</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1283096748801129</v>
+      </c>
+      <c r="T26">
+        <v>1.25515058403708</v>
+      </c>
+      <c r="U26">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V26">
+        <v>0.15</v>
+      </c>
+      <c r="W26">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>6.257452056540061</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1087090012186749</v>
+      </c>
+      <c r="C27">
+        <v>55.32328990506657</v>
+      </c>
+      <c r="D27">
+        <v>64.14828990506656</v>
+      </c>
+      <c r="E27">
+        <v>-12.125</v>
+      </c>
+      <c r="F27">
+        <v>17.275</v>
+      </c>
+      <c r="G27">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H27">
+        <v>39.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K27">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L27">
+        <v>5.5</v>
+      </c>
+      <c r="M27">
+        <v>0.9501249999999999</v>
+      </c>
+      <c r="N27">
+        <v>4.549875</v>
+      </c>
+      <c r="O27">
+        <v>0.6824812500000002</v>
+      </c>
+      <c r="P27">
+        <v>3.86739375</v>
+      </c>
+      <c r="Q27">
+        <v>7.657393749999999</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1293620016248999</v>
+      </c>
+      <c r="T27">
+        <v>1.269906849547889</v>
+      </c>
+      <c r="U27">
+        <v>0.055</v>
+      </c>
+      <c r="V27">
+        <v>0.15</v>
+      </c>
+      <c r="W27">
+        <v>0.04675</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>5.788712011577425</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.108682649528464</v>
+      </c>
+      <c r="C28">
+        <v>54.65647925499169</v>
+      </c>
+      <c r="D28">
+        <v>64.17247925499169</v>
+      </c>
+      <c r="E28">
+        <v>-11.434</v>
+      </c>
+      <c r="F28">
+        <v>17.966</v>
+      </c>
+      <c r="G28">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H28">
+        <v>39.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K28">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L28">
+        <v>5.5</v>
+      </c>
+      <c r="M28">
+        <v>0.9881299999999998</v>
+      </c>
+      <c r="N28">
+        <v>4.51187</v>
+      </c>
+      <c r="O28">
+        <v>0.6767805000000001</v>
+      </c>
+      <c r="P28">
+        <v>3.8350895</v>
+      </c>
+      <c r="Q28">
+        <v>7.6250895</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1304427696330594</v>
+      </c>
+      <c r="T28">
+        <v>1.285061933045477</v>
+      </c>
+      <c r="U28">
+        <v>0.055</v>
+      </c>
+      <c r="V28">
+        <v>0.15</v>
+      </c>
+      <c r="W28">
+        <v>0.04675</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>5.56606924190137</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.108656297838253</v>
+      </c>
+      <c r="C29">
+        <v>53.98968685467455</v>
+      </c>
+      <c r="D29">
+        <v>64.19668685467454</v>
+      </c>
+      <c r="E29">
+        <v>-10.743</v>
+      </c>
+      <c r="F29">
+        <v>18.657</v>
+      </c>
+      <c r="G29">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H29">
+        <v>39.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K29">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L29">
+        <v>5.5</v>
+      </c>
+      <c r="M29">
+        <v>1.026135</v>
+      </c>
+      <c r="N29">
+        <v>4.473865</v>
+      </c>
+      <c r="O29">
+        <v>0.6710797500000001</v>
+      </c>
+      <c r="P29">
+        <v>3.80278525</v>
+      </c>
+      <c r="Q29">
+        <v>7.592785249999999</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1315531477236343</v>
+      </c>
+      <c r="T29">
+        <v>1.300632224310122</v>
+      </c>
+      <c r="U29">
+        <v>0.055</v>
+      </c>
+      <c r="V29">
+        <v>0.15</v>
+      </c>
+      <c r="W29">
+        <v>0.04675</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>5.359918529238356</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1086299461480421</v>
+      </c>
+      <c r="C30">
+        <v>53.32291272477582</v>
+      </c>
+      <c r="D30">
+        <v>64.22091272477581</v>
+      </c>
+      <c r="E30">
+        <v>-10.052</v>
+      </c>
+      <c r="F30">
+        <v>19.348</v>
+      </c>
+      <c r="G30">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H30">
+        <v>39.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K30">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L30">
+        <v>5.5</v>
+      </c>
+      <c r="M30">
+        <v>1.06414</v>
+      </c>
+      <c r="N30">
+        <v>4.43586</v>
+      </c>
+      <c r="O30">
+        <v>0.6653790000000001</v>
+      </c>
+      <c r="P30">
+        <v>3.770481</v>
+      </c>
+      <c r="Q30">
+        <v>7.560480999999999</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1326943696500585</v>
+      </c>
+      <c r="T30">
+        <v>1.316635023665452</v>
+      </c>
+      <c r="U30">
+        <v>0.055</v>
+      </c>
+      <c r="V30">
+        <v>0.15</v>
+      </c>
+      <c r="W30">
+        <v>0.04675</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>5.168492867479843</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1086035944578312</v>
+      </c>
+      <c r="C31">
+        <v>52.65615688598743</v>
+      </c>
+      <c r="D31">
+        <v>64.24515688598743</v>
+      </c>
+      <c r="E31">
+        <v>-9.361000000000001</v>
+      </c>
+      <c r="F31">
+        <v>20.039</v>
+      </c>
+      <c r="G31">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H31">
+        <v>39.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K31">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L31">
+        <v>5.5</v>
+      </c>
+      <c r="M31">
+        <v>1.102145</v>
+      </c>
+      <c r="N31">
+        <v>4.397855</v>
+      </c>
+      <c r="O31">
+        <v>0.65967825</v>
+      </c>
+      <c r="P31">
+        <v>3.73817675</v>
+      </c>
+      <c r="Q31">
+        <v>7.528176749999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1338677386730017</v>
+      </c>
+      <c r="T31">
+        <v>1.333088606101214</v>
+      </c>
+      <c r="U31">
+        <v>0.055</v>
+      </c>
+      <c r="V31">
+        <v>0.15</v>
+      </c>
+      <c r="W31">
+        <v>0.04675</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>4.990268975497779</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1085772427676203</v>
+      </c>
+      <c r="C32">
+        <v>51.98941935903256</v>
+      </c>
+      <c r="D32">
+        <v>64.26941935903255</v>
+      </c>
+      <c r="E32">
+        <v>-8.670000000000002</v>
+      </c>
+      <c r="F32">
+        <v>20.73</v>
+      </c>
+      <c r="G32">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H32">
+        <v>39.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K32">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L32">
+        <v>5.5</v>
+      </c>
+      <c r="M32">
+        <v>1.14015</v>
+      </c>
+      <c r="N32">
+        <v>4.35985</v>
+      </c>
+      <c r="O32">
+        <v>0.6539775000000001</v>
+      </c>
+      <c r="P32">
+        <v>3.7058725</v>
+      </c>
+      <c r="Q32">
+        <v>7.495872499999999</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1350746325251718</v>
+      </c>
+      <c r="T32">
+        <v>1.350012290892283</v>
+      </c>
+      <c r="U32">
+        <v>0.055</v>
+      </c>
+      <c r="V32">
+        <v>0.15</v>
+      </c>
+      <c r="W32">
+        <v>0.04675</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>4.823926676314521</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1085508910774094</v>
+      </c>
+      <c r="C33">
+        <v>51.32270016466563</v>
+      </c>
+      <c r="D33">
+        <v>64.29370016466562</v>
+      </c>
+      <c r="E33">
+        <v>-7.978999999999999</v>
+      </c>
+      <c r="F33">
+        <v>21.421</v>
+      </c>
+      <c r="G33">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H33">
+        <v>39.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K33">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L33">
+        <v>5.5</v>
+      </c>
+      <c r="M33">
+        <v>1.178155</v>
+      </c>
+      <c r="N33">
+        <v>4.321845</v>
+      </c>
+      <c r="O33">
+        <v>0.6482767500000001</v>
+      </c>
+      <c r="P33">
+        <v>3.67356825</v>
+      </c>
+      <c r="Q33">
+        <v>7.463568249999999</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1363165088078397</v>
+      </c>
+      <c r="T33">
+        <v>1.367426517271499</v>
+      </c>
+      <c r="U33">
+        <v>0.055</v>
+      </c>
+      <c r="V33">
+        <v>0.15</v>
+      </c>
+      <c r="W33">
+        <v>0.04675</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>4.66831613836889</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1085245393871984</v>
+      </c>
+      <c r="C34">
+        <v>50.65599932367256</v>
+      </c>
+      <c r="D34">
+        <v>64.31799932367255</v>
+      </c>
+      <c r="E34">
+        <v>-7.288</v>
+      </c>
+      <c r="F34">
+        <v>22.112</v>
+      </c>
+      <c r="G34">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H34">
+        <v>39.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K34">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L34">
+        <v>5.5</v>
+      </c>
+      <c r="M34">
+        <v>1.21616</v>
+      </c>
+      <c r="N34">
+        <v>4.28384</v>
+      </c>
+      <c r="O34">
+        <v>0.642576</v>
+      </c>
+      <c r="P34">
+        <v>3.641264</v>
+      </c>
+      <c r="Q34">
+        <v>7.431263999999999</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1375949108635271</v>
+      </c>
+      <c r="T34">
+        <v>1.385352926779515</v>
+      </c>
+      <c r="U34">
+        <v>0.055</v>
+      </c>
+      <c r="V34">
+        <v>0.15</v>
+      </c>
+      <c r="W34">
+        <v>0.04675</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>4.522431259044863</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1095640876969875</v>
+      </c>
+      <c r="C35">
+        <v>49.02014622569661</v>
+      </c>
+      <c r="D35">
+        <v>63.3731462256966</v>
+      </c>
+      <c r="E35">
+        <v>-6.596999999999998</v>
+      </c>
+      <c r="F35">
+        <v>22.803</v>
+      </c>
+      <c r="G35">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H35">
+        <v>39.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K35">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L35">
+        <v>5.5</v>
+      </c>
+      <c r="M35">
+        <v>1.3408164</v>
+      </c>
+      <c r="N35">
+        <v>4.1591836</v>
+      </c>
+      <c r="O35">
+        <v>0.6238775400000001</v>
+      </c>
+      <c r="P35">
+        <v>3.535306059999999</v>
+      </c>
+      <c r="Q35">
+        <v>7.325306059999999</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1389114741746083</v>
+      </c>
+      <c r="T35">
+        <v>1.403814452989264</v>
+      </c>
+      <c r="U35">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V35">
+        <v>0.15</v>
+      </c>
+      <c r="W35">
+        <v>0.04998</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>4.101978466253843</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1107838360067766</v>
+      </c>
+      <c r="C36">
+        <v>47.25530392605128</v>
+      </c>
+      <c r="D36">
+        <v>62.29930392605129</v>
+      </c>
+      <c r="E36">
+        <v>-5.905999999999999</v>
+      </c>
+      <c r="F36">
+        <v>23.494</v>
+      </c>
+      <c r="G36">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H36">
+        <v>39.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K36">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L36">
+        <v>5.5</v>
+      </c>
+      <c r="M36">
+        <v>1.480122</v>
+      </c>
+      <c r="N36">
+        <v>4.019878</v>
+      </c>
+      <c r="O36">
+        <v>0.6029817000000002</v>
+      </c>
+      <c r="P36">
+        <v>3.4168963</v>
+      </c>
+      <c r="Q36">
+        <v>7.206896299999999</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1402679333436009</v>
+      </c>
+      <c r="T36">
+        <v>1.422835419387186</v>
+      </c>
+      <c r="U36">
+        <v>0.063</v>
+      </c>
+      <c r="V36">
+        <v>0.15</v>
+      </c>
+      <c r="W36">
+        <v>0.05355</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>3.71590990472407</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1108254843165657</v>
+      </c>
+      <c r="C37">
+        <v>46.528279722477</v>
+      </c>
+      <c r="D37">
+        <v>62.263279722477</v>
+      </c>
+      <c r="E37">
+        <v>-5.215</v>
+      </c>
+      <c r="F37">
+        <v>24.185</v>
+      </c>
+      <c r="G37">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H37">
+        <v>39.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K37">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L37">
+        <v>5.5</v>
+      </c>
+      <c r="M37">
+        <v>1.523655</v>
+      </c>
+      <c r="N37">
+        <v>3.976345</v>
+      </c>
+      <c r="O37">
+        <v>0.5964517500000002</v>
+      </c>
+      <c r="P37">
+        <v>3.37989325</v>
+      </c>
+      <c r="Q37">
+        <v>7.169893249999999</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1416661297177934</v>
+      </c>
+      <c r="T37">
+        <v>1.44244164628966</v>
+      </c>
+      <c r="U37">
+        <v>0.063</v>
+      </c>
+      <c r="V37">
+        <v>0.15</v>
+      </c>
+      <c r="W37">
+        <v>0.05355</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>3.609741050303382</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1108671326263548</v>
+      </c>
+      <c r="C38">
+        <v>45.80129715639087</v>
+      </c>
+      <c r="D38">
+        <v>62.22729715639086</v>
+      </c>
+      <c r="E38">
+        <v>-4.524000000000001</v>
+      </c>
+      <c r="F38">
+        <v>24.876</v>
+      </c>
+      <c r="G38">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H38">
+        <v>39.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K38">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L38">
+        <v>5.5</v>
+      </c>
+      <c r="M38">
+        <v>1.567188</v>
+      </c>
+      <c r="N38">
+        <v>3.932812</v>
+      </c>
+      <c r="O38">
+        <v>0.5899218000000002</v>
+      </c>
+      <c r="P38">
+        <v>3.3428902</v>
+      </c>
+      <c r="Q38">
+        <v>7.132890199999999</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1431080197286793</v>
+      </c>
+      <c r="T38">
+        <v>1.462660567782836</v>
+      </c>
+      <c r="U38">
+        <v>0.063</v>
+      </c>
+      <c r="V38">
+        <v>0.15</v>
+      </c>
+      <c r="W38">
+        <v>0.05355</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>3.509470465572733</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1131417309361438</v>
+      </c>
+      <c r="C39">
+        <v>43.20635837056616</v>
+      </c>
+      <c r="D39">
+        <v>60.32335837056615</v>
+      </c>
+      <c r="E39">
+        <v>-3.833000000000002</v>
+      </c>
+      <c r="F39">
+        <v>25.567</v>
+      </c>
+      <c r="G39">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H39">
+        <v>39.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K39">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L39">
+        <v>5.5</v>
+      </c>
+      <c r="M39">
+        <v>1.7922467</v>
+      </c>
+      <c r="N39">
+        <v>3.7077533</v>
+      </c>
+      <c r="O39">
+        <v>0.5561629950000001</v>
+      </c>
+      <c r="P39">
+        <v>3.151590305</v>
+      </c>
+      <c r="Q39">
+        <v>6.941590304999999</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1445956840256251</v>
+      </c>
+      <c r="T39">
+        <v>1.483521359799606</v>
+      </c>
+      <c r="U39">
+        <v>0.0701</v>
+      </c>
+      <c r="V39">
+        <v>0.15</v>
+      </c>
+      <c r="W39">
+        <v>0.05958499999999999</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>3.068773958406508</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1201236292459329</v>
+      </c>
+      <c r="C40">
+        <v>37.33640167921411</v>
+      </c>
+      <c r="D40">
+        <v>55.14440167921411</v>
+      </c>
+      <c r="E40">
+        <v>-3.141999999999999</v>
+      </c>
+      <c r="F40">
+        <v>26.258</v>
+      </c>
+      <c r="G40">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H40">
+        <v>39.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K40">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L40">
+        <v>5.5</v>
+      </c>
+      <c r="M40">
+        <v>2.3999812</v>
+      </c>
+      <c r="N40">
+        <v>3.1000188</v>
+      </c>
+      <c r="O40">
+        <v>0.46500282</v>
+      </c>
+      <c r="P40">
+        <v>2.63501598</v>
+      </c>
+      <c r="Q40">
+        <v>6.42501598</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1461313374934402</v>
+      </c>
+      <c r="T40">
+        <v>1.505055080591109</v>
+      </c>
+      <c r="U40">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V40">
+        <v>0.15</v>
+      </c>
+      <c r="W40">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>2.291684618196176</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.120406677555722</v>
+      </c>
+      <c r="C41">
+        <v>36.45413632989299</v>
+      </c>
+      <c r="D41">
+        <v>54.95313632989298</v>
+      </c>
+      <c r="E41">
+        <v>-2.451000000000001</v>
+      </c>
+      <c r="F41">
+        <v>26.949</v>
+      </c>
+      <c r="G41">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H41">
+        <v>39.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K41">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L41">
+        <v>5.5</v>
+      </c>
+      <c r="M41">
+        <v>2.4631386</v>
+      </c>
+      <c r="N41">
+        <v>3.0368614</v>
+      </c>
+      <c r="O41">
+        <v>0.45552921</v>
+      </c>
+      <c r="P41">
+        <v>2.58133219</v>
+      </c>
+      <c r="Q41">
+        <v>6.371332189999999</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1477173402552819</v>
+      </c>
+      <c r="T41">
+        <v>1.527294825015121</v>
+      </c>
+      <c r="U41">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V41">
+        <v>0.15</v>
+      </c>
+      <c r="W41">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>2.232923474139864</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1206897258655111</v>
+      </c>
+      <c r="C42">
+        <v>35.57319318145296</v>
+      </c>
+      <c r="D42">
+        <v>54.76319318145296</v>
+      </c>
+      <c r="E42">
+        <v>-1.759999999999998</v>
+      </c>
+      <c r="F42">
+        <v>27.64</v>
+      </c>
+      <c r="G42">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H42">
+        <v>39.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K42">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L42">
+        <v>5.5</v>
+      </c>
+      <c r="M42">
+        <v>2.526296</v>
+      </c>
+      <c r="N42">
+        <v>2.973704</v>
+      </c>
+      <c r="O42">
+        <v>0.4460556</v>
+      </c>
+      <c r="P42">
+        <v>2.527648399999999</v>
+      </c>
+      <c r="Q42">
+        <v>6.317648399999999</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1493562097758518</v>
+      </c>
+      <c r="T42">
+        <v>1.550275894253267</v>
+      </c>
+      <c r="U42">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V42">
+        <v>0.15</v>
+      </c>
+      <c r="W42">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>2.177100387286367</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1209727741753001</v>
+      </c>
+      <c r="C43">
+        <v>34.69355857072904</v>
+      </c>
+      <c r="D43">
+        <v>54.57455857072905</v>
+      </c>
+      <c r="E43">
+        <v>-1.068999999999999</v>
+      </c>
+      <c r="F43">
+        <v>28.331</v>
+      </c>
+      <c r="G43">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H43">
+        <v>39.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K43">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L43">
+        <v>5.5</v>
+      </c>
+      <c r="M43">
+        <v>2.5894534</v>
+      </c>
+      <c r="N43">
+        <v>2.9105466</v>
+      </c>
+      <c r="O43">
+        <v>0.4365819900000001</v>
+      </c>
+      <c r="P43">
+        <v>2.47396461</v>
+      </c>
+      <c r="Q43">
+        <v>6.263964609999999</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.151050634195424</v>
+      </c>
+      <c r="T43">
+        <v>1.574035982787621</v>
+      </c>
+      <c r="U43">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V43">
+        <v>0.15</v>
+      </c>
+      <c r="W43">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>2.124000377840358</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1212558224850892</v>
+      </c>
+      <c r="C44">
+        <v>33.81521902216384</v>
+      </c>
+      <c r="D44">
+        <v>54.38721902216383</v>
+      </c>
+      <c r="E44">
+        <v>-0.3780000000000037</v>
+      </c>
+      <c r="F44">
+        <v>29.02199999999999</v>
+      </c>
+      <c r="G44">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H44">
+        <v>39.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K44">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L44">
+        <v>5.5</v>
+      </c>
+      <c r="M44">
+        <v>2.6526108</v>
+      </c>
+      <c r="N44">
+        <v>2.8473892</v>
+      </c>
+      <c r="O44">
+        <v>0.4271083800000001</v>
+      </c>
+      <c r="P44">
+        <v>2.42028082</v>
+      </c>
+      <c r="Q44">
+        <v>6.210280819999999</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1528034870432572</v>
+      </c>
+      <c r="T44">
+        <v>1.598615384719711</v>
+      </c>
+      <c r="U44">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V44">
+        <v>0.15</v>
+      </c>
+      <c r="W44">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>2.073428940272731</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1215388707948783</v>
+      </c>
+      <c r="C45">
+        <v>32.9381612445986</v>
+      </c>
+      <c r="D45">
+        <v>54.2011612445986</v>
+      </c>
+      <c r="E45">
+        <v>0.3129999999999988</v>
+      </c>
+      <c r="F45">
+        <v>29.713</v>
+      </c>
+      <c r="G45">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H45">
+        <v>39.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K45">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L45">
+        <v>5.5</v>
+      </c>
+      <c r="M45">
+        <v>2.7157682</v>
+      </c>
+      <c r="N45">
+        <v>2.7842318</v>
+      </c>
+      <c r="O45">
+        <v>0.4176347700000001</v>
+      </c>
+      <c r="P45">
+        <v>2.36659703</v>
+      </c>
+      <c r="Q45">
+        <v>6.156597029999999</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1546178434997865</v>
+      </c>
+      <c r="T45">
+        <v>1.624057221807314</v>
+      </c>
+      <c r="U45">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V45">
+        <v>0.15</v>
+      </c>
+      <c r="W45">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>2.02520966259197</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1297133191046674</v>
+      </c>
+      <c r="C46">
+        <v>27.3736774108996</v>
+      </c>
+      <c r="D46">
+        <v>49.3276774108996</v>
+      </c>
+      <c r="E46">
+        <v>1.003999999999998</v>
+      </c>
+      <c r="F46">
+        <v>30.404</v>
+      </c>
+      <c r="G46">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H46">
+        <v>39.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K46">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L46">
+        <v>5.5</v>
+      </c>
+      <c r="M46">
+        <v>3.42045</v>
+      </c>
+      <c r="N46">
+        <v>2.07955</v>
+      </c>
+      <c r="O46">
+        <v>0.3119325000000001</v>
+      </c>
+      <c r="P46">
+        <v>1.7676175</v>
+      </c>
+      <c r="Q46">
+        <v>5.557617499999999</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1564969984011917</v>
+      </c>
+      <c r="T46">
+        <v>1.650407695933759</v>
+      </c>
+      <c r="U46">
+        <v>0.1125</v>
+      </c>
+      <c r="V46">
+        <v>0.15</v>
+      </c>
+      <c r="W46">
+        <v>0.095625</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>1.607975558771507</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1301757174144565</v>
+      </c>
+      <c r="C47">
+        <v>26.43305929236637</v>
+      </c>
+      <c r="D47">
+        <v>49.07805929236637</v>
+      </c>
+      <c r="E47">
+        <v>1.695</v>
+      </c>
+      <c r="F47">
+        <v>31.095</v>
+      </c>
+      <c r="G47">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H47">
+        <v>39.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K47">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L47">
+        <v>5.5</v>
+      </c>
+      <c r="M47">
+        <v>3.4981875</v>
+      </c>
+      <c r="N47">
+        <v>2.0018125</v>
+      </c>
+      <c r="O47">
+        <v>0.3002718750000001</v>
+      </c>
+      <c r="P47">
+        <v>1.701540625</v>
+      </c>
+      <c r="Q47">
+        <v>5.491540624999999</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1584444862081026</v>
+      </c>
+      <c r="T47">
+        <v>1.677716369119348</v>
+      </c>
+      <c r="U47">
+        <v>0.1125</v>
+      </c>
+      <c r="V47">
+        <v>0.15</v>
+      </c>
+      <c r="W47">
+        <v>0.095625</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>1.572242768576584</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1306381157242455</v>
+      </c>
+      <c r="C48">
+        <v>25.49495479239321</v>
+      </c>
+      <c r="D48">
+        <v>48.8309547923932</v>
+      </c>
+      <c r="E48">
+        <v>2.385999999999999</v>
+      </c>
+      <c r="F48">
+        <v>31.786</v>
+      </c>
+      <c r="G48">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H48">
+        <v>39.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K48">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L48">
+        <v>5.5</v>
+      </c>
+      <c r="M48">
+        <v>3.575925</v>
+      </c>
+      <c r="N48">
+        <v>1.924075</v>
+      </c>
+      <c r="O48">
+        <v>0.2886112500000001</v>
+      </c>
+      <c r="P48">
+        <v>1.63546375</v>
+      </c>
+      <c r="Q48">
+        <v>5.425463749999999</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1604641031930473</v>
+      </c>
+      <c r="T48">
+        <v>1.706036474645144</v>
+      </c>
+      <c r="U48">
+        <v>0.1125</v>
+      </c>
+      <c r="V48">
+        <v>0.15</v>
+      </c>
+      <c r="W48">
+        <v>0.095625</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>1.538063577955354</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1311005140340346</v>
+      </c>
+      <c r="C49">
+        <v>24.55932613352069</v>
+      </c>
+      <c r="D49">
+        <v>48.58632613352069</v>
+      </c>
+      <c r="E49">
+        <v>3.076999999999998</v>
+      </c>
+      <c r="F49">
+        <v>32.477</v>
+      </c>
+      <c r="G49">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H49">
+        <v>39.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K49">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L49">
+        <v>5.5</v>
+      </c>
+      <c r="M49">
+        <v>3.6536625</v>
+      </c>
+      <c r="N49">
+        <v>1.8463375</v>
+      </c>
+      <c r="O49">
+        <v>0.2769506250000001</v>
+      </c>
+      <c r="P49">
+        <v>1.569386875</v>
+      </c>
+      <c r="Q49">
+        <v>5.359386874999999</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1625599321396879</v>
+      </c>
+      <c r="T49">
+        <v>1.735425263398328</v>
+      </c>
+      <c r="U49">
+        <v>0.1125</v>
+      </c>
+      <c r="V49">
+        <v>0.15</v>
+      </c>
+      <c r="W49">
+        <v>0.095625</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>1.505338820977581</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1688871003466443</v>
+      </c>
+      <c r="C50">
+        <v>9.755386409561019</v>
+      </c>
+      <c r="D50">
+        <v>34.47338640956102</v>
+      </c>
+      <c r="E50">
+        <v>3.768000000000001</v>
+      </c>
+      <c r="F50">
+        <v>33.168</v>
+      </c>
+      <c r="G50">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H50">
+        <v>39.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K50">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L50">
+        <v>5.5</v>
+      </c>
+      <c r="M50">
+        <v>6.520828799999999</v>
+      </c>
+      <c r="N50">
+        <v>-1.020828799999999</v>
+      </c>
+      <c r="O50">
+        <v>-0.1531243199999999</v>
+      </c>
+      <c r="P50">
+        <v>-0.8677044799999996</v>
+      </c>
+      <c r="Q50">
+        <v>2.92229552</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1662659978279284</v>
+      </c>
+      <c r="T50">
+        <v>1.787393617872916</v>
+      </c>
+      <c r="U50">
+        <v>0.1966</v>
+      </c>
+      <c r="V50">
+        <v>0.1265176598410313</v>
+      </c>
+      <c r="W50">
+        <v>0.1717266280752532</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.8434510656068751</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1704651003466443</v>
+      </c>
+      <c r="C51">
+        <v>8.651224504006194</v>
+      </c>
+      <c r="D51">
+        <v>34.06022450400619</v>
+      </c>
+      <c r="E51">
+        <v>4.458999999999996</v>
+      </c>
+      <c r="F51">
+        <v>33.85899999999999</v>
+      </c>
+      <c r="G51">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H51">
+        <v>39.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K51">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L51">
+        <v>5.5</v>
+      </c>
+      <c r="M51">
+        <v>6.656679399999999</v>
+      </c>
+      <c r="N51">
+        <v>-1.156679399999999</v>
+      </c>
+      <c r="O51">
+        <v>-0.1735019099999999</v>
+      </c>
+      <c r="P51">
+        <v>-0.983177489999999</v>
+      </c>
+      <c r="Q51">
+        <v>2.80682251</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1687653311186721</v>
+      </c>
+      <c r="T51">
+        <v>1.822440551556698</v>
+      </c>
+      <c r="U51">
+        <v>0.1966</v>
+      </c>
+      <c r="V51">
+        <v>0.1239356667830511</v>
+      </c>
+      <c r="W51">
+        <v>0.1722342479104521</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.8262377785536736</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1720431003466443</v>
+      </c>
+      <c r="C52">
+        <v>7.556848763517607</v>
+      </c>
+      <c r="D52">
+        <v>33.65684876351761</v>
+      </c>
+      <c r="E52">
+        <v>5.149999999999999</v>
+      </c>
+      <c r="F52">
+        <v>34.55</v>
+      </c>
+      <c r="G52">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H52">
+        <v>39.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K52">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L52">
+        <v>5.5</v>
+      </c>
+      <c r="M52">
+        <v>6.792529999999999</v>
+      </c>
+      <c r="N52">
+        <v>-1.292529999999999</v>
+      </c>
+      <c r="O52">
+        <v>-0.1938794999999999</v>
+      </c>
+      <c r="P52">
+        <v>-1.098650499999999</v>
+      </c>
+      <c r="Q52">
+        <v>2.6913495</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1713646377410455</v>
+      </c>
+      <c r="T52">
+        <v>1.858889362587832</v>
+      </c>
+      <c r="U52">
+        <v>0.1966</v>
+      </c>
+      <c r="V52">
+        <v>0.12145695344739</v>
+      </c>
+      <c r="W52">
+        <v>0.1727215629522431</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.8097130229826001</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1827378625691837</v>
+      </c>
+      <c r="C53">
+        <v>4.365103037126275</v>
+      </c>
+      <c r="D53">
+        <v>31.15610303712628</v>
+      </c>
+      <c r="E53">
+        <v>5.841000000000001</v>
+      </c>
+      <c r="F53">
+        <v>35.241</v>
+      </c>
+      <c r="G53">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H53">
+        <v>39.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K53">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L53">
+        <v>5.5</v>
+      </c>
+      <c r="M53">
+        <v>7.5345258</v>
+      </c>
+      <c r="N53">
+        <v>-2.0345258</v>
+      </c>
+      <c r="O53">
+        <v>-0.30517887</v>
+      </c>
+      <c r="P53">
+        <v>-1.72934693</v>
+      </c>
+      <c r="Q53">
+        <v>2.060653069999999</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1747736348838003</v>
+      </c>
+      <c r="T53">
+        <v>1.906692069506836</v>
+      </c>
+      <c r="U53">
+        <v>0.2138</v>
+      </c>
+      <c r="V53">
+        <v>0.1094959420007561</v>
+      </c>
+      <c r="W53">
+        <v>0.1903897676002383</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.7299729466717069</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1844878625691837</v>
+      </c>
+      <c r="C54">
+        <v>3.299856484575763</v>
+      </c>
+      <c r="D54">
+        <v>30.78185648457576</v>
+      </c>
+      <c r="E54">
+        <v>6.531999999999996</v>
+      </c>
+      <c r="F54">
+        <v>35.932</v>
+      </c>
+      <c r="G54">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H54">
+        <v>39.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K54">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L54">
+        <v>5.5</v>
+      </c>
+      <c r="M54">
+        <v>7.682261599999999</v>
+      </c>
+      <c r="N54">
+        <v>-2.182261599999999</v>
+      </c>
+      <c r="O54">
+        <v>-0.3273392399999998</v>
+      </c>
+      <c r="P54">
+        <v>-1.854922359999999</v>
+      </c>
+      <c r="Q54">
+        <v>1.93507764</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1776064189438794</v>
+      </c>
+      <c r="T54">
+        <v>1.946414820954895</v>
+      </c>
+      <c r="U54">
+        <v>0.2138</v>
+      </c>
+      <c r="V54">
+        <v>0.1073902508084339</v>
+      </c>
+      <c r="W54">
+        <v>0.1908399643771568</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.7159350053895588</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1862378625691837</v>
+      </c>
+      <c r="C55">
+        <v>2.24349410133631</v>
+      </c>
+      <c r="D55">
+        <v>30.41649410133631</v>
+      </c>
+      <c r="E55">
+        <v>7.222999999999999</v>
+      </c>
+      <c r="F55">
+        <v>36.623</v>
+      </c>
+      <c r="G55">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H55">
+        <v>39.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K55">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L55">
+        <v>5.5</v>
+      </c>
+      <c r="M55">
+        <v>7.829997399999999</v>
+      </c>
+      <c r="N55">
+        <v>-2.329997399999999</v>
+      </c>
+      <c r="O55">
+        <v>-0.3494996099999999</v>
+      </c>
+      <c r="P55">
+        <v>-1.980497789999999</v>
+      </c>
+      <c r="Q55">
+        <v>1.80950221</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1805597470065152</v>
+      </c>
+      <c r="T55">
+        <v>1.987827902251807</v>
+      </c>
+      <c r="U55">
+        <v>0.2138</v>
+      </c>
+      <c r="V55">
+        <v>0.1053640196611049</v>
+      </c>
+      <c r="W55">
+        <v>0.1912731725964558</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.7024267977406993</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1879878625691837</v>
+      </c>
+      <c r="C56">
+        <v>1.195703248778479</v>
+      </c>
+      <c r="D56">
+        <v>30.05970324877848</v>
+      </c>
+      <c r="E56">
+        <v>7.914000000000001</v>
+      </c>
+      <c r="F56">
+        <v>37.314</v>
+      </c>
+      <c r="G56">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H56">
+        <v>39.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K56">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L56">
+        <v>5.5</v>
+      </c>
+      <c r="M56">
+        <v>7.977733199999999</v>
+      </c>
+      <c r="N56">
+        <v>-2.477733199999999</v>
+      </c>
+      <c r="O56">
+        <v>-0.3716599799999999</v>
+      </c>
+      <c r="P56">
+        <v>-2.106073219999999</v>
+      </c>
+      <c r="Q56">
+        <v>1.68392678</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1836414806370916</v>
+      </c>
+      <c r="T56">
+        <v>2.03104155230076</v>
+      </c>
+      <c r="U56">
+        <v>0.2138</v>
+      </c>
+      <c r="V56">
+        <v>0.1034128341118252</v>
+      </c>
+      <c r="W56">
+        <v>0.1916903360668918</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.6894188940788344</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1897378625691837</v>
+      </c>
+      <c r="C57">
+        <v>0.1561857874208243</v>
+      </c>
+      <c r="D57">
+        <v>29.71118578742083</v>
+      </c>
+      <c r="E57">
+        <v>8.605000000000004</v>
+      </c>
+      <c r="F57">
+        <v>38.005</v>
+      </c>
+      <c r="G57">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H57">
+        <v>39.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K57">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L57">
+        <v>5.5</v>
+      </c>
+      <c r="M57">
+        <v>8.125469000000001</v>
+      </c>
+      <c r="N57">
+        <v>-2.625469000000001</v>
+      </c>
+      <c r="O57">
+        <v>-0.3938203500000002</v>
+      </c>
+      <c r="P57">
+        <v>-2.23164865</v>
+      </c>
+      <c r="Q57">
+        <v>1.558351349999999</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1868601802068047</v>
+      </c>
+      <c r="T57">
+        <v>2.076175809018554</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0.1015326007643374</v>
+      </c>
+      <c r="W57">
+        <v>0.1920923299565847</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.6768840050955827</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1914878625691837</v>
+      </c>
+      <c r="C58">
+        <v>-0.8753427539648797</v>
+      </c>
+      <c r="D58">
+        <v>29.37065724603512</v>
+      </c>
+      <c r="E58">
+        <v>9.295999999999999</v>
+      </c>
+      <c r="F58">
+        <v>38.696</v>
+      </c>
+      <c r="G58">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H58">
+        <v>39.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K58">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L58">
+        <v>5.5</v>
+      </c>
+      <c r="M58">
+        <v>8.273204799999998</v>
+      </c>
+      <c r="N58">
+        <v>-2.773204799999998</v>
+      </c>
+      <c r="O58">
+        <v>-0.4159807199999999</v>
+      </c>
+      <c r="P58">
+        <v>-2.357224079999999</v>
+      </c>
+      <c r="Q58">
+        <v>1.432775920000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1902251843024139</v>
+      </c>
+      <c r="T58">
+        <v>2.123361622859885</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0.09971951860783143</v>
+      </c>
+      <c r="W58">
+        <v>0.1924799669216456</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.6647967907188761</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1932378625691837</v>
+      </c>
+      <c r="C59">
+        <v>-1.899153952757132</v>
+      </c>
+      <c r="D59">
+        <v>29.03784604724287</v>
+      </c>
+      <c r="E59">
+        <v>9.987000000000002</v>
+      </c>
+      <c r="F59">
+        <v>39.387</v>
+      </c>
+      <c r="G59">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H59">
+        <v>39.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K59">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L59">
+        <v>5.5</v>
+      </c>
+      <c r="M59">
+        <v>8.4209406</v>
+      </c>
+      <c r="N59">
+        <v>-2.9209406</v>
+      </c>
+      <c r="O59">
+        <v>-0.43814109</v>
+      </c>
+      <c r="P59">
+        <v>-2.48279951</v>
+      </c>
+      <c r="Q59">
+        <v>1.30720049</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1937467002164236</v>
+      </c>
+      <c r="T59">
+        <v>2.172742125717092</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0.09797005336909752</v>
+      </c>
+      <c r="W59">
+        <v>0.192854002589687</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.6531336891273167</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1949878625691837</v>
+      </c>
+      <c r="C60">
+        <v>-2.915507214827436</v>
+      </c>
+      <c r="D60">
+        <v>28.71249278517256</v>
+      </c>
+      <c r="E60">
+        <v>10.678</v>
+      </c>
+      <c r="F60">
+        <v>40.078</v>
+      </c>
+      <c r="G60">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H60">
+        <v>39.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K60">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L60">
+        <v>5.5</v>
+      </c>
+      <c r="M60">
+        <v>8.568676399999999</v>
+      </c>
+      <c r="N60">
+        <v>-3.068676399999999</v>
+      </c>
+      <c r="O60">
+        <v>-0.4603014599999999</v>
+      </c>
+      <c r="P60">
+        <v>-2.608374939999999</v>
+      </c>
+      <c r="Q60">
+        <v>1.18162506</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1974359073644336</v>
+      </c>
+      <c r="T60">
+        <v>2.224474081091308</v>
+      </c>
+      <c r="U60">
+        <v>0.2138</v>
+      </c>
+      <c r="V60">
+        <v>0.09628091451790619</v>
+      </c>
+      <c r="W60">
+        <v>0.1932151404760716</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.6418727634527079</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1967378625691837</v>
+      </c>
+      <c r="C61">
+        <v>-3.924650448860646</v>
+      </c>
+      <c r="D61">
+        <v>28.39434955113935</v>
+      </c>
+      <c r="E61">
+        <v>11.36899999999999</v>
+      </c>
+      <c r="F61">
+        <v>40.76899999999999</v>
+      </c>
+      <c r="G61">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H61">
+        <v>39.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K61">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L61">
+        <v>5.5</v>
+      </c>
+      <c r="M61">
+        <v>8.716412199999997</v>
+      </c>
+      <c r="N61">
+        <v>-3.216412199999997</v>
+      </c>
+      <c r="O61">
+        <v>-0.4824618299999996</v>
+      </c>
+      <c r="P61">
+        <v>-2.733950369999997</v>
+      </c>
+      <c r="Q61">
+        <v>1.056049630000002</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2013050758367369</v>
+      </c>
+      <c r="T61">
+        <v>2.278729546483779</v>
+      </c>
+      <c r="U61">
+        <v>0.2138</v>
+      </c>
+      <c r="V61">
+        <v>0.09464903461082307</v>
+      </c>
+      <c r="W61">
+        <v>0.193564036400206</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.6309935640721537</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1984878625691837</v>
+      </c>
+      <c r="C62">
+        <v>-4.926820696336193</v>
+      </c>
+      <c r="D62">
+        <v>28.0831793036638</v>
+      </c>
+      <c r="E62">
+        <v>12.06</v>
+      </c>
+      <c r="F62">
+        <v>41.45999999999999</v>
+      </c>
+      <c r="G62">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H62">
+        <v>39.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K62">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L62">
+        <v>5.5</v>
+      </c>
+      <c r="M62">
+        <v>8.864147999999998</v>
+      </c>
+      <c r="N62">
+        <v>-3.364147999999998</v>
+      </c>
+      <c r="O62">
+        <v>-0.5046221999999998</v>
+      </c>
+      <c r="P62">
+        <v>-2.859525799999998</v>
+      </c>
+      <c r="Q62">
+        <v>0.9304742000000008</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2053677027326553</v>
+      </c>
+      <c r="T62">
+        <v>2.335697785145873</v>
+      </c>
+      <c r="U62">
+        <v>0.2138</v>
+      </c>
+      <c r="V62">
+        <v>0.09307155070064267</v>
+      </c>
+      <c r="W62">
+        <v>0.1939013024602026</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.620477004670951</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2002378625691837</v>
+      </c>
+      <c r="C63">
+        <v>-5.922244720535296</v>
+      </c>
+      <c r="D63">
+        <v>27.7787552794647</v>
+      </c>
+      <c r="E63">
+        <v>12.751</v>
+      </c>
+      <c r="F63">
+        <v>42.151</v>
+      </c>
+      <c r="G63">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H63">
+        <v>39.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K63">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L63">
+        <v>5.5</v>
+      </c>
+      <c r="M63">
+        <v>9.011883799999998</v>
+      </c>
+      <c r="N63">
+        <v>-3.511883799999998</v>
+      </c>
+      <c r="O63">
+        <v>-0.5267825699999997</v>
+      </c>
+      <c r="P63">
+        <v>-2.985101229999998</v>
+      </c>
+      <c r="Q63">
+        <v>0.8048987700000012</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2096386694693901</v>
+      </c>
+      <c r="T63">
+        <v>2.395587471944486</v>
+      </c>
+      <c r="U63">
+        <v>0.2138</v>
+      </c>
+      <c r="V63">
+        <v>0.09154578757440261</v>
+      </c>
+      <c r="W63">
+        <v>0.1942275106165927</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.6103052504960174</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2019878625691837</v>
+      </c>
+      <c r="C64">
+        <v>-6.911139557649506</v>
+      </c>
+      <c r="D64">
+        <v>27.4808604423505</v>
+      </c>
+      <c r="E64">
+        <v>13.442</v>
+      </c>
+      <c r="F64">
+        <v>42.842</v>
+      </c>
+      <c r="G64">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H64">
+        <v>39.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K64">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L64">
+        <v>5.5</v>
+      </c>
+      <c r="M64">
+        <v>9.159619599999999</v>
+      </c>
+      <c r="N64">
+        <v>-3.659619599999999</v>
+      </c>
+      <c r="O64">
+        <v>-0.54894294</v>
+      </c>
+      <c r="P64">
+        <v>-3.110676659999999</v>
+      </c>
+      <c r="Q64">
+        <v>0.6793233399999998</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2141344239291108</v>
+      </c>
+      <c r="T64">
+        <v>2.458629247521972</v>
+      </c>
+      <c r="U64">
+        <v>0.2138</v>
+      </c>
+      <c r="V64">
+        <v>0.09006924261352516</v>
+      </c>
+      <c r="W64">
+        <v>0.1945431959292283</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.6004616174235009</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2037378625691837</v>
+      </c>
+      <c r="C65">
+        <v>-7.893713032805586</v>
+      </c>
+      <c r="D65">
+        <v>27.18928696719441</v>
+      </c>
+      <c r="E65">
+        <v>14.133</v>
+      </c>
+      <c r="F65">
+        <v>43.53299999999999</v>
+      </c>
+      <c r="G65">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H65">
+        <v>39.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K65">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L65">
+        <v>5.5</v>
+      </c>
+      <c r="M65">
+        <v>9.307355399999999</v>
+      </c>
+      <c r="N65">
+        <v>-3.807355399999999</v>
+      </c>
+      <c r="O65">
+        <v>-0.5711033099999999</v>
+      </c>
+      <c r="P65">
+        <v>-3.236252089999999</v>
+      </c>
+      <c r="Q65">
+        <v>0.5537479100000002</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2188731921434112</v>
+      </c>
+      <c r="T65">
+        <v>2.525078686644188</v>
+      </c>
+      <c r="U65">
+        <v>0.2138</v>
+      </c>
+      <c r="V65">
+        <v>0.08863957209585015</v>
+      </c>
+      <c r="W65">
+        <v>0.1948488594859072</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.590930480639001</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2054878625691837</v>
+      </c>
+      <c r="C66">
+        <v>-8.87016424358491</v>
+      </c>
+      <c r="D66">
+        <v>26.90383575641509</v>
+      </c>
+      <c r="E66">
+        <v>14.824</v>
+      </c>
+      <c r="F66">
+        <v>44.224</v>
+      </c>
+      <c r="G66">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H66">
+        <v>39.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K66">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L66">
+        <v>5.5</v>
+      </c>
+      <c r="M66">
+        <v>9.455091199999998</v>
+      </c>
+      <c r="N66">
+        <v>-3.955091199999998</v>
+      </c>
+      <c r="O66">
+        <v>-0.5932636799999998</v>
+      </c>
+      <c r="P66">
+        <v>-3.361827519999999</v>
+      </c>
+      <c r="Q66">
+        <v>0.4281724800000006</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2238752252585059</v>
+      </c>
+      <c r="T66">
+        <v>2.595219761273193</v>
+      </c>
+      <c r="U66">
+        <v>0.2138</v>
+      </c>
+      <c r="V66">
+        <v>0.0872545787818525</v>
+      </c>
+      <c r="W66">
+        <v>0.1951449710564399</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.5816971918790166</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2072378625691837</v>
+      </c>
+      <c r="C67">
+        <v>-9.840684013401436</v>
+      </c>
+      <c r="D67">
+        <v>26.62431598659857</v>
+      </c>
+      <c r="E67">
+        <v>15.515</v>
+      </c>
+      <c r="F67">
+        <v>44.915</v>
+      </c>
+      <c r="G67">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H67">
+        <v>39.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K67">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L67">
+        <v>5.5</v>
+      </c>
+      <c r="M67">
+        <v>9.602827</v>
+      </c>
+      <c r="N67">
+        <v>-4.102827</v>
+      </c>
+      <c r="O67">
+        <v>-0.61542405</v>
+      </c>
+      <c r="P67">
+        <v>-3.487402949999999</v>
+      </c>
+      <c r="Q67">
+        <v>0.3025970499999997</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2291630888373204</v>
+      </c>
+      <c r="T67">
+        <v>2.66936889730957</v>
+      </c>
+      <c r="U67">
+        <v>0.2138</v>
+      </c>
+      <c r="V67">
+        <v>0.08591220064674705</v>
+      </c>
+      <c r="W67">
+        <v>0.1954319715017254</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.5727480043116471</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2089878625691837</v>
+      </c>
+      <c r="C68">
+        <v>-10.80545531690792</v>
+      </c>
+      <c r="D68">
+        <v>26.35054468309208</v>
+      </c>
+      <c r="E68">
+        <v>16.206</v>
+      </c>
+      <c r="F68">
+        <v>45.606</v>
+      </c>
+      <c r="G68">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H68">
+        <v>39.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K68">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L68">
+        <v>5.5</v>
+      </c>
+      <c r="M68">
+        <v>9.750562799999999</v>
+      </c>
+      <c r="N68">
+        <v>-4.250562799999999</v>
+      </c>
+      <c r="O68">
+        <v>-0.6375844199999999</v>
+      </c>
+      <c r="P68">
+        <v>-3.612978379999999</v>
+      </c>
+      <c r="Q68">
+        <v>0.1770216200000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2347620032148886</v>
+      </c>
+      <c r="T68">
+        <v>2.747879747230439</v>
+      </c>
+      <c r="U68">
+        <v>0.2138</v>
+      </c>
+      <c r="V68">
+        <v>0.08461050063694787</v>
+      </c>
+      <c r="W68">
+        <v>0.1957102749638205</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.564070004246319</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2107378625691837</v>
+      </c>
+      <c r="C69">
+        <v>-11.76465367942308</v>
+      </c>
+      <c r="D69">
+        <v>26.08234632057692</v>
+      </c>
+      <c r="E69">
+        <v>16.897</v>
+      </c>
+      <c r="F69">
+        <v>46.297</v>
+      </c>
+      <c r="G69">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H69">
+        <v>39.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K69">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L69">
+        <v>5.5</v>
+      </c>
+      <c r="M69">
+        <v>9.898298599999999</v>
+      </c>
+      <c r="N69">
+        <v>-4.398298599999999</v>
+      </c>
+      <c r="O69">
+        <v>-0.6597447899999999</v>
+      </c>
+      <c r="P69">
+        <v>-3.738553809999999</v>
+      </c>
+      <c r="Q69">
+        <v>0.0514461900000005</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2407002457365519</v>
+      </c>
+      <c r="T69">
+        <v>2.831148830479847</v>
+      </c>
+      <c r="U69">
+        <v>0.2138</v>
+      </c>
+      <c r="V69">
+        <v>0.0833476573438591</v>
+      </c>
+      <c r="W69">
+        <v>0.1959802708598829</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.5556510489590606</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2124878625691837</v>
+      </c>
+      <c r="C70">
+        <v>-12.71844755221214</v>
+      </c>
+      <c r="D70">
+        <v>25.81955244778786</v>
+      </c>
+      <c r="E70">
+        <v>17.588</v>
+      </c>
+      <c r="F70">
+        <v>46.988</v>
+      </c>
+      <c r="G70">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H70">
+        <v>39.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K70">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L70">
+        <v>5.5</v>
+      </c>
+      <c r="M70">
+        <v>10.0460344</v>
+      </c>
+      <c r="N70">
+        <v>-4.5460344</v>
+      </c>
+      <c r="O70">
+        <v>-0.6819051600000001</v>
+      </c>
+      <c r="P70">
+        <v>-3.86412924</v>
+      </c>
+      <c r="Q70">
+        <v>-0.07412924000000043</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2470096284158192</v>
+      </c>
+      <c r="T70">
+        <v>2.919622231432342</v>
+      </c>
+      <c r="U70">
+        <v>0.2138</v>
+      </c>
+      <c r="V70">
+        <v>0.08212195650056703</v>
+      </c>
+      <c r="W70">
+        <v>0.1962423257001787</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.5474797100037803</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2142378625691837</v>
+      </c>
+      <c r="C71">
+        <v>-13.66699866530674</v>
+      </c>
+      <c r="D71">
+        <v>25.56200133469327</v>
+      </c>
+      <c r="E71">
+        <v>18.279</v>
+      </c>
+      <c r="F71">
+        <v>47.679</v>
+      </c>
+      <c r="G71">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H71">
+        <v>39.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K71">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L71">
+        <v>5.5</v>
+      </c>
+      <c r="M71">
+        <v>10.1937702</v>
+      </c>
+      <c r="N71">
+        <v>-4.693770199999999</v>
+      </c>
+      <c r="O71">
+        <v>-0.7040655300000001</v>
+      </c>
+      <c r="P71">
+        <v>-3.989704669999999</v>
+      </c>
+      <c r="Q71">
+        <v>-0.19970467</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2537260680421359</v>
+      </c>
+      <c r="T71">
+        <v>3.013803593736612</v>
+      </c>
+      <c r="U71">
+        <v>0.2138</v>
+      </c>
+      <c r="V71">
+        <v>0.08093178321795012</v>
+      </c>
+      <c r="W71">
+        <v>0.1964967847480023</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.5395452214530008</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2159878625691837</v>
+      </c>
+      <c r="C72">
+        <v>-14.61046235941696</v>
+      </c>
+      <c r="D72">
+        <v>25.30953764058304</v>
+      </c>
+      <c r="E72">
+        <v>18.97</v>
+      </c>
+      <c r="F72">
+        <v>48.37</v>
+      </c>
+      <c r="G72">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H72">
+        <v>39.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K72">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L72">
+        <v>5.5</v>
+      </c>
+      <c r="M72">
+        <v>10.341506</v>
+      </c>
+      <c r="N72">
+        <v>-4.841505999999999</v>
+      </c>
+      <c r="O72">
+        <v>-0.7262259</v>
+      </c>
+      <c r="P72">
+        <v>-4.115280099999999</v>
+      </c>
+      <c r="Q72">
+        <v>-0.3252800999999996</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2608902703102071</v>
+      </c>
+      <c r="T72">
+        <v>3.114263713527832</v>
+      </c>
+      <c r="U72">
+        <v>0.2138</v>
+      </c>
+      <c r="V72">
+        <v>0.07977561488626514</v>
+      </c>
+      <c r="W72">
+        <v>0.1967439735373165</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.5318374325751007</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2177378625691837</v>
+      </c>
+      <c r="C73">
+        <v>-15.54898789836708</v>
+      </c>
+      <c r="D73">
+        <v>25.06201210163291</v>
+      </c>
+      <c r="E73">
+        <v>19.66099999999999</v>
+      </c>
+      <c r="F73">
+        <v>49.06099999999999</v>
+      </c>
+      <c r="G73">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H73">
+        <v>39.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K73">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L73">
+        <v>5.5</v>
+      </c>
+      <c r="M73">
+        <v>10.4892418</v>
+      </c>
+      <c r="N73">
+        <v>-4.989241799999999</v>
+      </c>
+      <c r="O73">
+        <v>-0.7483862699999999</v>
+      </c>
+      <c r="P73">
+        <v>-4.240855529999998</v>
+      </c>
+      <c r="Q73">
+        <v>-0.4508555299999992</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2685485554933177</v>
+      </c>
+      <c r="T73">
+        <v>3.221652117442584</v>
+      </c>
+      <c r="U73">
+        <v>0.2138</v>
+      </c>
+      <c r="V73">
+        <v>0.07865201467659942</v>
+      </c>
+      <c r="W73">
+        <v>0.196984199262143</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.5243467645106628</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2194878625691837</v>
+      </c>
+      <c r="C74">
+        <v>-16.48271876337505</v>
+      </c>
+      <c r="D74">
+        <v>24.81928123662495</v>
+      </c>
+      <c r="E74">
+        <v>20.352</v>
+      </c>
+      <c r="F74">
+        <v>49.752</v>
+      </c>
+      <c r="G74">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H74">
+        <v>39.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K74">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L74">
+        <v>5.5</v>
+      </c>
+      <c r="M74">
+        <v>10.6369776</v>
+      </c>
+      <c r="N74">
+        <v>-5.136977599999998</v>
+      </c>
+      <c r="O74">
+        <v>-0.7705466399999998</v>
+      </c>
+      <c r="P74">
+        <v>-4.366430959999998</v>
+      </c>
+      <c r="Q74">
+        <v>-0.5764309599999988</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2767538610466505</v>
+      </c>
+      <c r="T74">
+        <v>3.336711121636962</v>
+      </c>
+      <c r="U74">
+        <v>0.2138</v>
+      </c>
+      <c r="V74">
+        <v>0.07755962558386888</v>
+      </c>
+      <c r="W74">
+        <v>0.1972177520501688</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.5170641705591259</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2212378625691837</v>
+      </c>
+      <c r="C75">
+        <v>-17.41179293039519</v>
+      </c>
+      <c r="D75">
+        <v>24.5812070696048</v>
+      </c>
+      <c r="E75">
+        <v>21.043</v>
+      </c>
+      <c r="F75">
+        <v>50.443</v>
+      </c>
+      <c r="G75">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H75">
+        <v>39.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K75">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L75">
+        <v>5.5</v>
+      </c>
+      <c r="M75">
+        <v>10.7847134</v>
+      </c>
+      <c r="N75">
+        <v>-5.284713399999999</v>
+      </c>
+      <c r="O75">
+        <v>-0.79270701</v>
+      </c>
+      <c r="P75">
+        <v>-4.492006389999999</v>
+      </c>
+      <c r="Q75">
+        <v>-0.7020063900000002</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2855669670113412</v>
+      </c>
+      <c r="T75">
+        <v>3.460293015030923</v>
+      </c>
+      <c r="U75">
+        <v>0.2138</v>
+      </c>
+      <c r="V75">
+        <v>0.07649716495943232</v>
+      </c>
+      <c r="W75">
+        <v>0.1974449061316733</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.5099810997295486</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2229878625691837</v>
+      </c>
+      <c r="C76">
+        <v>-18.33634313165044</v>
+      </c>
+      <c r="D76">
+        <v>24.34765686834955</v>
+      </c>
+      <c r="E76">
+        <v>21.73399999999999</v>
+      </c>
+      <c r="F76">
+        <v>51.13399999999999</v>
+      </c>
+      <c r="G76">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H76">
+        <v>39.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K76">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L76">
+        <v>5.5</v>
+      </c>
+      <c r="M76">
+        <v>10.9324492</v>
+      </c>
+      <c r="N76">
+        <v>-5.432449199999999</v>
+      </c>
+      <c r="O76">
+        <v>-0.8148673799999999</v>
+      </c>
+      <c r="P76">
+        <v>-4.617581819999999</v>
+      </c>
+      <c r="Q76">
+        <v>-0.8275818199999998</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2950580042040851</v>
+      </c>
+      <c r="T76">
+        <v>3.593381207916729</v>
+      </c>
+      <c r="U76">
+        <v>0.2138</v>
+      </c>
+      <c r="V76">
+        <v>0.07546341948700756</v>
+      </c>
+      <c r="W76">
+        <v>0.1976659209136778</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.503089463246717</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2439004162103987</v>
+      </c>
+      <c r="C77">
+        <v>-21.5098913863304</v>
+      </c>
+      <c r="D77">
+        <v>21.8651086136696</v>
+      </c>
+      <c r="E77">
+        <v>22.425</v>
+      </c>
+      <c r="F77">
+        <v>51.825</v>
+      </c>
+      <c r="G77">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H77">
+        <v>39.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K77">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L77">
+        <v>5.5</v>
+      </c>
+      <c r="M77">
+        <v>12.37581</v>
+      </c>
+      <c r="N77">
+        <v>-6.87581</v>
+      </c>
+      <c r="O77">
+        <v>-1.0313715</v>
+      </c>
+      <c r="P77">
+        <v>-5.844438499999999</v>
+      </c>
+      <c r="Q77">
+        <v>-2.0544385</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3069585389371086</v>
+      </c>
+      <c r="T77">
+        <v>3.760256611503147</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.06666230331590418</v>
+      </c>
+      <c r="W77">
+        <v>0.2228810419681621</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.4444153554393612</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2459004162103987</v>
+      </c>
+      <c r="C78">
+        <v>-22.41204604274072</v>
+      </c>
+      <c r="D78">
+        <v>21.65395395725928</v>
+      </c>
+      <c r="E78">
+        <v>23.116</v>
+      </c>
+      <c r="F78">
+        <v>52.516</v>
+      </c>
+      <c r="G78">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H78">
+        <v>39.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K78">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L78">
+        <v>5.5</v>
+      </c>
+      <c r="M78">
+        <v>12.5408208</v>
+      </c>
+      <c r="N78">
+        <v>-7.040820800000001</v>
+      </c>
+      <c r="O78">
+        <v>-1.05612312</v>
+      </c>
+      <c r="P78">
+        <v>-5.98469768</v>
+      </c>
+      <c r="Q78">
+        <v>-2.194697680000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3181318113928214</v>
+      </c>
+      <c r="T78">
+        <v>3.916933970315778</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.06578516774595808</v>
+      </c>
+      <c r="W78">
+        <v>0.2230905019422652</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.4385677849730537</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2479004162103987</v>
+      </c>
+      <c r="C79">
+        <v>-23.31016140242962</v>
+      </c>
+      <c r="D79">
+        <v>21.44683859757037</v>
+      </c>
+      <c r="E79">
+        <v>23.807</v>
+      </c>
+      <c r="F79">
+        <v>53.20699999999999</v>
+      </c>
+      <c r="G79">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H79">
+        <v>39.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K79">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L79">
+        <v>5.5</v>
+      </c>
+      <c r="M79">
+        <v>12.7058316</v>
+      </c>
+      <c r="N79">
+        <v>-7.2058316</v>
+      </c>
+      <c r="O79">
+        <v>-1.08087474</v>
+      </c>
+      <c r="P79">
+        <v>-6.124956859999999</v>
+      </c>
+      <c r="Q79">
+        <v>-2.33495686</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3302766727577268</v>
+      </c>
+      <c r="T79">
+        <v>4.08723544728603</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.06493081491808848</v>
+      </c>
+      <c r="W79">
+        <v>0.2232945213975605</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.4328720994539232</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2499004162103987</v>
+      </c>
+      <c r="C80">
+        <v>-24.20435227227798</v>
+      </c>
+      <c r="D80">
+        <v>21.24364772772202</v>
+      </c>
+      <c r="E80">
+        <v>24.498</v>
+      </c>
+      <c r="F80">
+        <v>53.898</v>
+      </c>
+      <c r="G80">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H80">
+        <v>39.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K80">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L80">
+        <v>5.5</v>
+      </c>
+      <c r="M80">
+        <v>12.8708424</v>
+      </c>
+      <c r="N80">
+        <v>-7.370842399999999</v>
+      </c>
+      <c r="O80">
+        <v>-1.10562636</v>
+      </c>
+      <c r="P80">
+        <v>-6.265216039999999</v>
+      </c>
+      <c r="Q80">
+        <v>-2.475216039999999</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3435256124285325</v>
+      </c>
+      <c r="T80">
+        <v>4.273018876708123</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.0640983685729848</v>
+      </c>
+      <c r="W80">
+        <v>0.2234933095847712</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.4273224571532319</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2519004162103987</v>
+      </c>
+      <c r="C81">
+        <v>-25.09472914920297</v>
+      </c>
+      <c r="D81">
+        <v>21.04427085079703</v>
+      </c>
+      <c r="E81">
+        <v>25.189</v>
+      </c>
+      <c r="F81">
+        <v>54.589</v>
+      </c>
+      <c r="G81">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H81">
+        <v>39.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K81">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L81">
+        <v>5.5</v>
+      </c>
+      <c r="M81">
+        <v>13.0358532</v>
+      </c>
+      <c r="N81">
+        <v>-7.5358532</v>
+      </c>
+      <c r="O81">
+        <v>-1.13037798</v>
+      </c>
+      <c r="P81">
+        <v>-6.40547522</v>
+      </c>
+      <c r="Q81">
+        <v>-2.61547522</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3580363558775102</v>
+      </c>
+      <c r="T81">
+        <v>4.476495966075175</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.06328699681889638</v>
+      </c>
+      <c r="W81">
+        <v>0.2236870651596476</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.4219133121259757</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2539004162103987</v>
+      </c>
+      <c r="C82">
+        <v>-25.98139842052798</v>
+      </c>
+      <c r="D82">
+        <v>20.84860157947202</v>
+      </c>
+      <c r="E82">
+        <v>25.88</v>
+      </c>
+      <c r="F82">
+        <v>55.28</v>
+      </c>
+      <c r="G82">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H82">
+        <v>39.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K82">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L82">
+        <v>5.5</v>
+      </c>
+      <c r="M82">
+        <v>13.200864</v>
+      </c>
+      <c r="N82">
+        <v>-7.700864000000001</v>
+      </c>
+      <c r="O82">
+        <v>-1.1551296</v>
+      </c>
+      <c r="P82">
+        <v>-6.545734400000001</v>
+      </c>
+      <c r="Q82">
+        <v>-2.755734400000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3739981736713858</v>
+      </c>
+      <c r="T82">
+        <v>4.700320764378935</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.06249590935866017</v>
+      </c>
+      <c r="W82">
+        <v>0.223875976845152</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.416639395724401</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2559004162103987</v>
+      </c>
+      <c r="C83">
+        <v>-26.86446255327719</v>
+      </c>
+      <c r="D83">
+        <v>20.6565374467228</v>
+      </c>
+      <c r="E83">
+        <v>26.571</v>
+      </c>
+      <c r="F83">
+        <v>55.971</v>
+      </c>
+      <c r="G83">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H83">
+        <v>39.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K83">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L83">
+        <v>5.5</v>
+      </c>
+      <c r="M83">
+        <v>13.3658748</v>
+      </c>
+      <c r="N83">
+        <v>-7.8658748</v>
+      </c>
+      <c r="O83">
+        <v>-1.17988122</v>
+      </c>
+      <c r="P83">
+        <v>-6.68599358</v>
+      </c>
+      <c r="Q83">
+        <v>-2.895993580000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3916401828119851</v>
+      </c>
+      <c r="T83">
+        <v>4.9477060677673</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.0617243549221335</v>
+      </c>
+      <c r="W83">
+        <v>0.2240602240445946</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.4114956994808899</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2579004162103987</v>
+      </c>
+      <c r="C84">
+        <v>-27.74402027310267</v>
+      </c>
+      <c r="D84">
+        <v>20.46797972689733</v>
+      </c>
+      <c r="E84">
+        <v>27.262</v>
+      </c>
+      <c r="F84">
+        <v>56.662</v>
+      </c>
+      <c r="G84">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H84">
+        <v>39.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K84">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L84">
+        <v>5.5</v>
+      </c>
+      <c r="M84">
+        <v>13.5308856</v>
+      </c>
+      <c r="N84">
+        <v>-8.030885600000001</v>
+      </c>
+      <c r="O84">
+        <v>-1.20463284</v>
+      </c>
+      <c r="P84">
+        <v>-6.826252760000001</v>
+      </c>
+      <c r="Q84">
+        <v>-3.036252760000002</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4112424151904286</v>
+      </c>
+      <c r="T84">
+        <v>5.222578627087706</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.06097161888649772</v>
+      </c>
+      <c r="W84">
+        <v>0.2242399774099044</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.4064774592433181</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2599004162103987</v>
+      </c>
+      <c r="C85">
+        <v>-28.62016673350028</v>
+      </c>
+      <c r="D85">
+        <v>20.28283326649972</v>
+      </c>
+      <c r="E85">
+        <v>27.953</v>
+      </c>
+      <c r="F85">
+        <v>57.353</v>
+      </c>
+      <c r="G85">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H85">
+        <v>39.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K85">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L85">
+        <v>5.5</v>
+      </c>
+      <c r="M85">
+        <v>13.6958964</v>
+      </c>
+      <c r="N85">
+        <v>-8.195896400000001</v>
+      </c>
+      <c r="O85">
+        <v>-1.22938446</v>
+      </c>
+      <c r="P85">
+        <v>-6.96651194</v>
+      </c>
+      <c r="Q85">
+        <v>-3.176511940000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4331507925545716</v>
+      </c>
+      <c r="T85">
+        <v>5.529789134563454</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.06023702106858812</v>
+      </c>
+      <c r="W85">
+        <v>0.2244153993688212</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.401580140457254</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2619004162103987</v>
+      </c>
+      <c r="C86">
+        <v>-29.49299367592401</v>
+      </c>
+      <c r="D86">
+        <v>20.10100632407598</v>
+      </c>
+      <c r="E86">
+        <v>28.64399999999999</v>
+      </c>
+      <c r="F86">
+        <v>58.04399999999999</v>
+      </c>
+      <c r="G86">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H86">
+        <v>39.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K86">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L86">
+        <v>5.5</v>
+      </c>
+      <c r="M86">
+        <v>13.8609072</v>
+      </c>
+      <c r="N86">
+        <v>-8.360907199999998</v>
+      </c>
+      <c r="O86">
+        <v>-1.25413608</v>
+      </c>
+      <c r="P86">
+        <v>-7.106771119999998</v>
+      </c>
+      <c r="Q86">
+        <v>-3.316771119999999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4577977170892321</v>
+      </c>
+      <c r="T86">
+        <v>5.875400955473666</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.05951991367491445</v>
+      </c>
+      <c r="W86">
+        <v>0.2245866446144304</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3967994244994296</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2639004162103987</v>
+      </c>
+      <c r="C87">
+        <v>-30.36258958136461</v>
+      </c>
+      <c r="D87">
+        <v>19.92241041863538</v>
+      </c>
+      <c r="E87">
+        <v>29.33499999999999</v>
+      </c>
+      <c r="F87">
+        <v>58.73499999999999</v>
+      </c>
+      <c r="G87">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H87">
+        <v>39.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K87">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L87">
+        <v>5.5</v>
+      </c>
+      <c r="M87">
+        <v>14.025918</v>
+      </c>
+      <c r="N87">
+        <v>-8.525917999999999</v>
+      </c>
+      <c r="O87">
+        <v>-1.2788877</v>
+      </c>
+      <c r="P87">
+        <v>-7.247030299999999</v>
+      </c>
+      <c r="Q87">
+        <v>-3.4570303</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4857308982285142</v>
+      </c>
+      <c r="T87">
+        <v>6.267094352505245</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.05881967939638604</v>
+      </c>
+      <c r="W87">
+        <v>0.224753860560143</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.392131195975907</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2659004162103987</v>
+      </c>
+      <c r="C88">
+        <v>-31.22903981391881</v>
+      </c>
+      <c r="D88">
+        <v>19.74696018608118</v>
+      </c>
+      <c r="E88">
+        <v>30.026</v>
+      </c>
+      <c r="F88">
+        <v>59.42599999999999</v>
+      </c>
+      <c r="G88">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H88">
+        <v>39.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K88">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L88">
+        <v>5.5</v>
+      </c>
+      <c r="M88">
+        <v>14.1909288</v>
+      </c>
+      <c r="N88">
+        <v>-8.6909288</v>
+      </c>
+      <c r="O88">
+        <v>-1.30363932</v>
+      </c>
+      <c r="P88">
+        <v>-7.38728948</v>
+      </c>
+      <c r="Q88">
+        <v>-3.597289480000001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5176545338162652</v>
+      </c>
+      <c r="T88">
+        <v>6.714743949112762</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.05813572963596295</v>
+      </c>
+      <c r="W88">
+        <v>0.2249171877629321</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3875715309064196</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2679004162103987</v>
+      </c>
+      <c r="C89">
+        <v>-32.09242675683861</v>
+      </c>
+      <c r="D89">
+        <v>19.57457324316139</v>
+      </c>
+      <c r="E89">
+        <v>30.717</v>
+      </c>
+      <c r="F89">
+        <v>60.117</v>
+      </c>
+      <c r="G89">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H89">
+        <v>39.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K89">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L89">
+        <v>5.5</v>
+      </c>
+      <c r="M89">
+        <v>14.3559396</v>
+      </c>
+      <c r="N89">
+        <v>-8.855939599999999</v>
+      </c>
+      <c r="O89">
+        <v>-1.32839094</v>
+      </c>
+      <c r="P89">
+        <v>-7.527548659999999</v>
+      </c>
+      <c r="Q89">
+        <v>-3.73754866</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.554489497955978</v>
+      </c>
+      <c r="T89">
+        <v>7.231262714429128</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.05746750285853809</v>
+      </c>
+      <c r="W89">
+        <v>0.2250767603173811</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.3831166857235873</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2699004162103987</v>
+      </c>
+      <c r="C90">
+        <v>-32.95282994151604</v>
+      </c>
+      <c r="D90">
+        <v>19.40517005848395</v>
+      </c>
+      <c r="E90">
+        <v>31.40799999999999</v>
+      </c>
+      <c r="F90">
+        <v>60.80799999999999</v>
+      </c>
+      <c r="G90">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H90">
+        <v>39.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K90">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L90">
+        <v>5.5</v>
+      </c>
+      <c r="M90">
+        <v>14.5209504</v>
+      </c>
+      <c r="N90">
+        <v>-9.020950399999998</v>
+      </c>
+      <c r="O90">
+        <v>-1.35314256</v>
+      </c>
+      <c r="P90">
+        <v>-7.667807839999998</v>
+      </c>
+      <c r="Q90">
+        <v>-3.877807839999999</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5974636227856429</v>
+      </c>
+      <c r="T90">
+        <v>7.833867940631557</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.05681446305332743</v>
+      </c>
+      <c r="W90">
+        <v>0.2252327062228654</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3787630870221829</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2719004162103987</v>
+      </c>
+      <c r="C91">
+        <v>-33.81032616982796</v>
+      </c>
+      <c r="D91">
+        <v>19.23867383017204</v>
+      </c>
+      <c r="E91">
+        <v>32.099</v>
+      </c>
+      <c r="F91">
+        <v>61.499</v>
+      </c>
+      <c r="G91">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H91">
+        <v>39.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K91">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L91">
+        <v>5.5</v>
+      </c>
+      <c r="M91">
+        <v>14.6859612</v>
+      </c>
+      <c r="N91">
+        <v>-9.185961199999999</v>
+      </c>
+      <c r="O91">
+        <v>-1.37789418</v>
+      </c>
+      <c r="P91">
+        <v>-7.808067019999999</v>
+      </c>
+      <c r="Q91">
+        <v>-4.01806702</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6482512248570651</v>
+      </c>
+      <c r="T91">
+        <v>8.546037753416245</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.05617609829991925</v>
+      </c>
+      <c r="W91">
+        <v>0.2253851477259793</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.3745073219994617</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2739004162103987</v>
+      </c>
+      <c r="C92">
+        <v>-34.66498963023591</v>
+      </c>
+      <c r="D92">
+        <v>19.07501036976409</v>
+      </c>
+      <c r="E92">
+        <v>32.79</v>
+      </c>
+      <c r="F92">
+        <v>62.19</v>
+      </c>
+      <c r="G92">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H92">
+        <v>39.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K92">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L92">
+        <v>5.5</v>
+      </c>
+      <c r="M92">
+        <v>14.850972</v>
+      </c>
+      <c r="N92">
+        <v>-9.350972000000001</v>
+      </c>
+      <c r="O92">
+        <v>-1.4026458</v>
+      </c>
+      <c r="P92">
+        <v>-7.9483262</v>
+      </c>
+      <c r="Q92">
+        <v>-4.158326200000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7091963473427716</v>
+      </c>
+      <c r="T92">
+        <v>9.40064152875787</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.05555191942992015</v>
+      </c>
+      <c r="W92">
+        <v>0.2255342016401351</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.3703461295328009</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2759004162103987</v>
+      </c>
+      <c r="C93">
+        <v>-35.51689200801022</v>
+      </c>
+      <c r="D93">
+        <v>18.91410799198979</v>
+      </c>
+      <c r="E93">
+        <v>33.481</v>
+      </c>
+      <c r="F93">
+        <v>62.881</v>
+      </c>
+      <c r="G93">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H93">
+        <v>39.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K93">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L93">
+        <v>5.5</v>
+      </c>
+      <c r="M93">
+        <v>15.0159828</v>
+      </c>
+      <c r="N93">
+        <v>-9.515982800000002</v>
+      </c>
+      <c r="O93">
+        <v>-1.42739742</v>
+      </c>
+      <c r="P93">
+        <v>-8.088585380000001</v>
+      </c>
+      <c r="Q93">
+        <v>-4.298585380000002</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7836848303808572</v>
+      </c>
+      <c r="T93">
+        <v>10.44515725417541</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.0549414587768441</v>
+      </c>
+      <c r="W93">
+        <v>0.2256799796440896</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.3662763918456273</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2779004162103987</v>
+      </c>
+      <c r="C94">
+        <v>-36.36610258992192</v>
+      </c>
+      <c r="D94">
+        <v>18.75589741007808</v>
+      </c>
+      <c r="E94">
+        <v>34.172</v>
+      </c>
+      <c r="F94">
+        <v>63.572</v>
+      </c>
+      <c r="G94">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H94">
+        <v>39.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K94">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L94">
+        <v>5.5</v>
+      </c>
+      <c r="M94">
+        <v>15.1809936</v>
+      </c>
+      <c r="N94">
+        <v>-9.680993599999999</v>
+      </c>
+      <c r="O94">
+        <v>-1.45214904</v>
+      </c>
+      <c r="P94">
+        <v>-8.228844559999999</v>
+      </c>
+      <c r="Q94">
+        <v>-4.43884456</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8767954341784647</v>
+      </c>
+      <c r="T94">
+        <v>11.75080191094734</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.05434426900753059</v>
+      </c>
+      <c r="W94">
+        <v>0.2258225885610017</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3622951267168705</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2799004162103987</v>
+      </c>
+      <c r="C95">
+        <v>-37.21268836372423</v>
+      </c>
+      <c r="D95">
+        <v>18.60031163627576</v>
+      </c>
+      <c r="E95">
+        <v>34.86299999999999</v>
+      </c>
+      <c r="F95">
+        <v>64.26299999999999</v>
+      </c>
+      <c r="G95">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H95">
+        <v>39.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K95">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L95">
+        <v>5.5</v>
+      </c>
+      <c r="M95">
+        <v>15.3460044</v>
+      </c>
+      <c r="N95">
+        <v>-9.846004399999998</v>
+      </c>
+      <c r="O95">
+        <v>-1.47690066</v>
+      </c>
+      <c r="P95">
+        <v>-8.369103739999998</v>
+      </c>
+      <c r="Q95">
+        <v>-4.579103739999999</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.9965090676325312</v>
+      </c>
+      <c r="T95">
+        <v>13.42948789822553</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.05375992202895499</v>
+      </c>
+      <c r="W95">
+        <v>0.2259621306194856</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3583994801930332</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2819004162103987</v>
+      </c>
+      <c r="C96">
+        <v>-38.05671411272318</v>
+      </c>
+      <c r="D96">
+        <v>18.44728588727682</v>
+      </c>
+      <c r="E96">
+        <v>35.55399999999999</v>
+      </c>
+      <c r="F96">
+        <v>64.95399999999999</v>
+      </c>
+      <c r="G96">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H96">
+        <v>39.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K96">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L96">
+        <v>5.5</v>
+      </c>
+      <c r="M96">
+        <v>15.5110152</v>
+      </c>
+      <c r="N96">
+        <v>-10.0110152</v>
+      </c>
+      <c r="O96">
+        <v>-1.50165228</v>
+      </c>
+      <c r="P96">
+        <v>-8.509362919999999</v>
+      </c>
+      <c r="Q96">
+        <v>-4.71936292</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.156127245571287</v>
+      </c>
+      <c r="T96">
+        <v>15.66773588126313</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.05318800796481717</v>
+      </c>
+      <c r="W96">
+        <v>0.2260987036980017</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.3545867197654478</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2839004162103987</v>
+      </c>
+      <c r="C97">
+        <v>-38.89824250571816</v>
+      </c>
+      <c r="D97">
+        <v>18.29675749428183</v>
+      </c>
+      <c r="E97">
+        <v>36.245</v>
+      </c>
+      <c r="F97">
+        <v>65.645</v>
+      </c>
+      <c r="G97">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H97">
+        <v>39.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K97">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L97">
+        <v>5.5</v>
+      </c>
+      <c r="M97">
+        <v>15.676026</v>
+      </c>
+      <c r="N97">
+        <v>-10.176026</v>
+      </c>
+      <c r="O97">
+        <v>-1.5264039</v>
+      </c>
+      <c r="P97">
+        <v>-8.6496221</v>
+      </c>
+      <c r="Q97">
+        <v>-4.859622100000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.379592694685545</v>
+      </c>
+      <c r="T97">
+        <v>18.80128305751576</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.05262813419676646</v>
+      </c>
+      <c r="W97">
+        <v>0.2262324015538122</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.350854227978443</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2859004162103987</v>
+      </c>
+      <c r="C98">
+        <v>-39.73733418257478</v>
+      </c>
+      <c r="D98">
+        <v>18.14866581742522</v>
+      </c>
+      <c r="E98">
+        <v>36.936</v>
+      </c>
+      <c r="F98">
+        <v>66.336</v>
+      </c>
+      <c r="G98">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H98">
+        <v>39.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K98">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L98">
+        <v>5.5</v>
+      </c>
+      <c r="M98">
+        <v>15.8410368</v>
+      </c>
+      <c r="N98">
+        <v>-10.3410368</v>
+      </c>
+      <c r="O98">
+        <v>-1.55115552</v>
+      </c>
+      <c r="P98">
+        <v>-8.789881280000001</v>
+      </c>
+      <c r="Q98">
+        <v>-4.999881280000002</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.714790868356927</v>
+      </c>
+      <c r="T98">
+        <v>23.50160382189465</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.05207992446555014</v>
+      </c>
+      <c r="W98">
+        <v>0.2263633140376267</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.3471994964370009</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2879004162103987</v>
+      </c>
+      <c r="C99">
+        <v>-40.57404783567517</v>
+      </c>
+      <c r="D99">
+        <v>18.00295216432481</v>
+      </c>
+      <c r="E99">
+        <v>37.62699999999999</v>
+      </c>
+      <c r="F99">
+        <v>67.02699999999999</v>
+      </c>
+      <c r="G99">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H99">
+        <v>39.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K99">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L99">
+        <v>5.5</v>
+      </c>
+      <c r="M99">
+        <v>16.0060476</v>
+      </c>
+      <c r="N99">
+        <v>-10.5060476</v>
+      </c>
+      <c r="O99">
+        <v>-1.57590714</v>
+      </c>
+      <c r="P99">
+        <v>-8.930140459999999</v>
+      </c>
+      <c r="Q99">
+        <v>-5.14014046</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.27345449114257</v>
+      </c>
+      <c r="T99">
+        <v>31.3354717625262</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.05154301802776097</v>
+      </c>
+      <c r="W99">
+        <v>0.2264915272949707</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.343620120185073</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2899004162103987</v>
+      </c>
+      <c r="C100">
+        <v>-41.40844028747613</v>
+      </c>
+      <c r="D100">
+        <v>17.85955971252386</v>
+      </c>
+      <c r="E100">
+        <v>38.31799999999999</v>
+      </c>
+      <c r="F100">
+        <v>67.71799999999999</v>
+      </c>
+      <c r="G100">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H100">
+        <v>39.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K100">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L100">
+        <v>5.5</v>
+      </c>
+      <c r="M100">
+        <v>16.1710584</v>
+      </c>
+      <c r="N100">
+        <v>-10.6710584</v>
+      </c>
+      <c r="O100">
+        <v>-1.60065876</v>
+      </c>
+      <c r="P100">
+        <v>-9.07039964</v>
+      </c>
+      <c r="Q100">
+        <v>-5.280399640000001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.390781736713854</v>
+      </c>
+      <c r="T100">
+        <v>47.0032076437893</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.05101706886421238</v>
+      </c>
+      <c r="W100">
+        <v>0.2266171239552261</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3401137924280825</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2919004162103987</v>
+      </c>
+      <c r="C101">
+        <v>-42.24056656438971</v>
+      </c>
+      <c r="D101">
+        <v>17.71843343561028</v>
+      </c>
+      <c r="E101">
+        <v>39.00899999999999</v>
+      </c>
+      <c r="F101">
+        <v>68.40899999999999</v>
+      </c>
+      <c r="G101">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="H101">
+        <v>39.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K101">
+        <v>3.789999999999999</v>
+      </c>
+      <c r="L101">
+        <v>5.5</v>
+      </c>
+      <c r="M101">
+        <v>16.3360692</v>
+      </c>
+      <c r="N101">
+        <v>-10.8360692</v>
+      </c>
+      <c r="O101">
+        <v>-1.62541038</v>
+      </c>
+      <c r="P101">
+        <v>-9.210658819999997</v>
+      </c>
+      <c r="Q101">
+        <v>-5.420658819999998</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.74276347342771</v>
+      </c>
+      <c r="T101">
+        <v>94.0064152875786</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.05050174493629106</v>
+      </c>
+      <c r="W101">
+        <v>0.2267401833092137</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3366782995752736</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kuwait/kuwait_recreation.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_recreation.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09308324910803162</v>
+        <v>0.09298187423436957</v>
       </c>
       <c r="C2">
-        <v>73.53033706672996</v>
+        <v>72.93512556724156</v>
       </c>
       <c r="D2">
-        <v>65.06033706672996</v>
+        <v>65.20012556724156</v>
       </c>
       <c r="E2">
-        <v>-33</v>
+        <v>-32.265</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.735</v>
       </c>
       <c r="G2">
         <v>8.470000000000001</v>
@@ -1451,28 +1451,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0369705</v>
       </c>
       <c r="N2">
-        <v>5.768999999999999</v>
+        <v>5.732029499999999</v>
       </c>
       <c r="O2">
-        <v>0.8653499999999998</v>
+        <v>0.8598044249999999</v>
       </c>
       <c r="P2">
-        <v>4.903649999999999</v>
+        <v>4.872225074999999</v>
       </c>
       <c r="Q2">
-        <v>9.254649999999998</v>
+        <v>9.223225074999998</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09308324910803162</v>
+        <v>0.0934892163983531</v>
       </c>
       <c r="T2">
-        <v>0.8969457633378592</v>
+        <v>0.904646812821063</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>156.0433318456607</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09298187423436957</v>
+        <v>0.09288049936070754</v>
       </c>
       <c r="C3">
-        <v>72.93512556724156</v>
+        <v>72.34051605973588</v>
       </c>
       <c r="D3">
-        <v>65.20012556724156</v>
+        <v>65.34051605973588</v>
       </c>
       <c r="E3">
-        <v>-32.265</v>
+        <v>-31.53</v>
       </c>
       <c r="F3">
-        <v>0.735</v>
+        <v>1.47</v>
       </c>
       <c r="G3">
         <v>8.470000000000001</v>
@@ -1533,28 +1533,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M3">
-        <v>0.0369705</v>
+        <v>0.07394099999999999</v>
       </c>
       <c r="N3">
-        <v>5.732029499999999</v>
+        <v>5.695059</v>
       </c>
       <c r="O3">
-        <v>0.8598044249999999</v>
+        <v>0.8542588499999999</v>
       </c>
       <c r="P3">
-        <v>4.872225074999999</v>
+        <v>4.84080015</v>
       </c>
       <c r="Q3">
-        <v>9.223225074999998</v>
+        <v>9.191800149999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0934892163983531</v>
+        <v>0.09390346873541586</v>
       </c>
       <c r="T3">
-        <v>0.904646812821063</v>
+        <v>0.9125050265794344</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>156.0433318456607</v>
+        <v>78.02166592283037</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09288049936070754</v>
+        <v>0.09277912448704546</v>
       </c>
       <c r="C4">
-        <v>72.34051605973588</v>
+        <v>71.74651244127546</v>
       </c>
       <c r="D4">
-        <v>65.34051605973588</v>
+        <v>65.48151244127546</v>
       </c>
       <c r="E4">
-        <v>-31.53</v>
+        <v>-30.795</v>
       </c>
       <c r="F4">
-        <v>1.47</v>
+        <v>2.205</v>
       </c>
       <c r="G4">
         <v>8.470000000000001</v>
@@ -1615,28 +1615,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M4">
-        <v>0.07394099999999999</v>
+        <v>0.1109115</v>
       </c>
       <c r="N4">
-        <v>5.695059</v>
+        <v>5.658088499999999</v>
       </c>
       <c r="O4">
-        <v>0.8542588499999999</v>
+        <v>0.8487132749999998</v>
       </c>
       <c r="P4">
-        <v>4.84080015</v>
+        <v>4.809375224999999</v>
       </c>
       <c r="Q4">
-        <v>9.191800149999999</v>
+        <v>9.160375224999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09390346873541586</v>
+        <v>0.09432626235777884</v>
       </c>
       <c r="T4">
-        <v>0.9125050265794344</v>
+        <v>0.9205252653637513</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>78.02166592283037</v>
+        <v>52.01444394855357</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09277912448704546</v>
+        <v>0.09267774961338343</v>
       </c>
       <c r="C5">
-        <v>71.74651244127546</v>
+        <v>71.15311864263282</v>
       </c>
       <c r="D5">
-        <v>65.48151244127546</v>
+        <v>65.62311864263282</v>
       </c>
       <c r="E5">
-        <v>-30.795</v>
+        <v>-30.06</v>
       </c>
       <c r="F5">
-        <v>2.205</v>
+        <v>2.94</v>
       </c>
       <c r="G5">
         <v>8.470000000000001</v>
@@ -1697,28 +1697,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M5">
-        <v>0.1109115</v>
+        <v>0.147882</v>
       </c>
       <c r="N5">
-        <v>5.658088499999999</v>
+        <v>5.621117999999999</v>
       </c>
       <c r="O5">
-        <v>0.8487132749999998</v>
+        <v>0.8431676999999999</v>
       </c>
       <c r="P5">
-        <v>4.809375224999999</v>
+        <v>4.7779503</v>
       </c>
       <c r="Q5">
-        <v>9.160375224999999</v>
+        <v>9.1289503</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09432626235777884</v>
+        <v>0.09475786418060775</v>
       </c>
       <c r="T5">
-        <v>0.9205252653637513</v>
+        <v>0.9287125924560751</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>52.01444394855357</v>
+        <v>39.01083296141518</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09267774961338343</v>
+        <v>0.09257637473972138</v>
       </c>
       <c r="C6">
-        <v>71.15311864263282</v>
+        <v>70.56033862865617</v>
       </c>
       <c r="D6">
-        <v>65.62311864263282</v>
+        <v>65.76533862865617</v>
       </c>
       <c r="E6">
-        <v>-30.06</v>
+        <v>-29.325</v>
       </c>
       <c r="F6">
-        <v>2.94</v>
+        <v>3.675</v>
       </c>
       <c r="G6">
         <v>8.470000000000001</v>
@@ -1779,28 +1779,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M6">
-        <v>0.147882</v>
+        <v>0.1848525</v>
       </c>
       <c r="N6">
-        <v>5.621117999999999</v>
+        <v>5.584147499999999</v>
       </c>
       <c r="O6">
-        <v>0.8431676999999999</v>
+        <v>0.8376221249999999</v>
       </c>
       <c r="P6">
-        <v>4.7779503</v>
+        <v>4.746525374999999</v>
       </c>
       <c r="Q6">
-        <v>9.1289503</v>
+        <v>9.097525375</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09475786418060775</v>
+        <v>0.09519855235760147</v>
       </c>
       <c r="T6">
-        <v>0.9287125924560751</v>
+        <v>0.9370722843292898</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>39.01083296141518</v>
+        <v>31.20866636913214</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09257637473972138</v>
+        <v>0.09247499986605935</v>
       </c>
       <c r="C7">
-        <v>70.56033862865617</v>
+        <v>69.96817639863909</v>
       </c>
       <c r="D7">
-        <v>65.76533862865617</v>
+        <v>65.90817639863909</v>
       </c>
       <c r="E7">
-        <v>-29.325</v>
+        <v>-28.59</v>
       </c>
       <c r="F7">
-        <v>3.675</v>
+        <v>4.41</v>
       </c>
       <c r="G7">
         <v>8.470000000000001</v>
@@ -1861,28 +1861,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M7">
-        <v>0.1848525</v>
+        <v>0.221823</v>
       </c>
       <c r="N7">
-        <v>5.584147499999999</v>
+        <v>5.547177</v>
       </c>
       <c r="O7">
-        <v>0.8376221249999999</v>
+        <v>0.8320765499999999</v>
       </c>
       <c r="P7">
-        <v>4.746525374999999</v>
+        <v>4.71510045</v>
       </c>
       <c r="Q7">
-        <v>9.097525375</v>
+        <v>9.06610045</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09519855235760147</v>
+        <v>0.09564861687878654</v>
       </c>
       <c r="T7">
-        <v>0.9370722843292898</v>
+        <v>0.9456098419870409</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>31.20866636913214</v>
+        <v>26.00722197427679</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09247499986605934</v>
+        <v>0.0923736249923973</v>
       </c>
       <c r="C8">
-        <v>69.9681763986391</v>
+        <v>69.37663598669562</v>
       </c>
       <c r="D8">
-        <v>65.9081763986391</v>
+        <v>66.05163598669562</v>
       </c>
       <c r="E8">
-        <v>-28.59</v>
+        <v>-27.855</v>
       </c>
       <c r="F8">
-        <v>4.41</v>
+        <v>5.145</v>
       </c>
       <c r="G8">
         <v>8.470000000000001</v>
@@ -1943,28 +1943,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M8">
-        <v>0.221823</v>
+        <v>0.2587935</v>
       </c>
       <c r="N8">
-        <v>5.547177</v>
+        <v>5.510206499999999</v>
       </c>
       <c r="O8">
-        <v>0.8320765499999999</v>
+        <v>0.8265309749999998</v>
       </c>
       <c r="P8">
-        <v>4.71510045</v>
+        <v>4.683675524999999</v>
       </c>
       <c r="Q8">
-        <v>9.06610045</v>
+        <v>9.034675524999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09564861687878654</v>
+        <v>0.09610836020687881</v>
       </c>
       <c r="T8">
-        <v>0.9456098419870409</v>
+        <v>0.9543310030352814</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>26.00722197427679</v>
+        <v>22.2919045493801</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09237362499239729</v>
+        <v>0.09227225011873526</v>
       </c>
       <c r="C9">
-        <v>69.37663598669563</v>
+        <v>68.78572146213986</v>
       </c>
       <c r="D9">
-        <v>66.05163598669563</v>
+        <v>66.19572146213986</v>
       </c>
       <c r="E9">
-        <v>-27.855</v>
+        <v>-27.12</v>
       </c>
       <c r="F9">
-        <v>5.145</v>
+        <v>5.88</v>
       </c>
       <c r="G9">
         <v>8.470000000000001</v>
@@ -2025,28 +2025,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M9">
-        <v>0.2587935</v>
+        <v>0.295764</v>
       </c>
       <c r="N9">
-        <v>5.510206499999999</v>
+        <v>5.473235999999999</v>
       </c>
       <c r="O9">
-        <v>0.8265309749999998</v>
+        <v>0.8209853999999999</v>
       </c>
       <c r="P9">
-        <v>4.683675524999999</v>
+        <v>4.652250599999999</v>
       </c>
       <c r="Q9">
-        <v>9.034675524999999</v>
+        <v>9.003250599999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09610836020687881</v>
+        <v>0.096578097955147</v>
       </c>
       <c r="T9">
-        <v>0.9543310030352814</v>
+        <v>0.9632417545410923</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.2919045493801</v>
+        <v>19.50541648070759</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09227225011873526</v>
+        <v>0.09217087524507321</v>
       </c>
       <c r="C10">
-        <v>68.78572146213986</v>
+        <v>68.19543692987099</v>
       </c>
       <c r="D10">
-        <v>66.19572146213986</v>
+        <v>66.34043692987099</v>
       </c>
       <c r="E10">
-        <v>-27.12</v>
+        <v>-26.385</v>
       </c>
       <c r="F10">
-        <v>5.88</v>
+        <v>6.614999999999999</v>
       </c>
       <c r="G10">
         <v>8.470000000000001</v>
@@ -2107,28 +2107,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M10">
-        <v>0.295764</v>
+        <v>0.3327344999999999</v>
       </c>
       <c r="N10">
-        <v>5.473235999999999</v>
+        <v>5.436265499999999</v>
       </c>
       <c r="O10">
-        <v>0.8209853999999999</v>
+        <v>0.8154398249999999</v>
       </c>
       <c r="P10">
-        <v>4.652250599999999</v>
+        <v>4.620825674999999</v>
       </c>
       <c r="Q10">
-        <v>9.003250599999999</v>
+        <v>8.971825674999998</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.096578097955147</v>
+        <v>0.09705815960997055</v>
       </c>
       <c r="T10">
-        <v>0.9632417545410923</v>
+        <v>0.9723483467393386</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.50541648070759</v>
+        <v>17.33814798285119</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09217087524507321</v>
+        <v>0.09206950037141115</v>
       </c>
       <c r="C11">
-        <v>68.19543692987099</v>
+        <v>67.60578653076288</v>
       </c>
       <c r="D11">
-        <v>66.34043692987099</v>
+        <v>66.48578653076288</v>
       </c>
       <c r="E11">
-        <v>-26.385</v>
+        <v>-25.65</v>
       </c>
       <c r="F11">
-        <v>6.614999999999999</v>
+        <v>7.35</v>
       </c>
       <c r="G11">
         <v>8.470000000000001</v>
@@ -2189,28 +2189,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M11">
-        <v>0.3327344999999999</v>
+        <v>0.369705</v>
       </c>
       <c r="N11">
-        <v>5.436265499999999</v>
+        <v>5.399295</v>
       </c>
       <c r="O11">
-        <v>0.8154398249999999</v>
+        <v>0.8098942499999999</v>
       </c>
       <c r="P11">
-        <v>4.620825674999999</v>
+        <v>4.589400749999999</v>
       </c>
       <c r="Q11">
-        <v>8.971825674999998</v>
+        <v>8.940400749999998</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09705815960997055</v>
+        <v>0.09754888930156794</v>
       </c>
       <c r="T11">
-        <v>0.9723483467393386</v>
+        <v>0.9816573076531016</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.33814798285119</v>
+        <v>15.60433318456607</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09206950037141115</v>
+        <v>0.0919681254977491</v>
       </c>
       <c r="C12">
-        <v>67.60578653076288</v>
+        <v>67.0167744420591</v>
       </c>
       <c r="D12">
-        <v>66.48578653076288</v>
+        <v>66.6317744420591</v>
       </c>
       <c r="E12">
-        <v>-25.65</v>
+        <v>-24.915</v>
       </c>
       <c r="F12">
-        <v>7.350000000000001</v>
+        <v>8.085000000000001</v>
       </c>
       <c r="G12">
         <v>8.470000000000001</v>
@@ -2271,28 +2271,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M12">
-        <v>0.369705</v>
+        <v>0.4066755</v>
       </c>
       <c r="N12">
-        <v>5.399295</v>
+        <v>5.362324499999999</v>
       </c>
       <c r="O12">
-        <v>0.8098942499999999</v>
+        <v>0.8043486749999998</v>
       </c>
       <c r="P12">
-        <v>4.589400749999999</v>
+        <v>4.557975824999999</v>
       </c>
       <c r="Q12">
-        <v>8.940400749999998</v>
+        <v>8.908975824999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09754888930156794</v>
+        <v>0.09805064662668439</v>
       </c>
       <c r="T12">
-        <v>0.9816573076531016</v>
+        <v>0.991175458699758</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.60433318456607</v>
+        <v>14.18575744051461</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0919681254977491</v>
+        <v>0.09186675062408706</v>
       </c>
       <c r="C13">
-        <v>67.0167744420591</v>
+        <v>66.42840487777318</v>
       </c>
       <c r="D13">
-        <v>66.6317744420591</v>
+        <v>66.77840487777318</v>
       </c>
       <c r="E13">
-        <v>-24.915</v>
+        <v>-24.18</v>
       </c>
       <c r="F13">
-        <v>8.085000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="G13">
         <v>8.470000000000001</v>
@@ -2353,28 +2353,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M13">
-        <v>0.4066755</v>
+        <v>0.443646</v>
       </c>
       <c r="N13">
-        <v>5.362324499999999</v>
+        <v>5.325353999999999</v>
       </c>
       <c r="O13">
-        <v>0.8043486749999998</v>
+        <v>0.7988030999999999</v>
       </c>
       <c r="P13">
-        <v>4.557975824999999</v>
+        <v>4.526550899999999</v>
       </c>
       <c r="Q13">
-        <v>8.908975824999999</v>
+        <v>8.877550899999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09805064662668439</v>
+        <v>0.09856380752737165</v>
       </c>
       <c r="T13">
-        <v>0.991175458699758</v>
+        <v>1.000909931361111</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.18575744051461</v>
+        <v>13.00361098713839</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09186675062408706</v>
+        <v>0.09193112575042502</v>
       </c>
       <c r="C14">
-        <v>66.42840487777318</v>
+        <v>65.60021685817202</v>
       </c>
       <c r="D14">
-        <v>66.77840487777318</v>
+        <v>66.68521685817203</v>
       </c>
       <c r="E14">
-        <v>-24.18</v>
+        <v>-23.445</v>
       </c>
       <c r="F14">
-        <v>8.82</v>
+        <v>9.555</v>
       </c>
       <c r="G14">
         <v>8.470000000000001</v>
@@ -2435,45 +2435,45 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M14">
-        <v>0.443646</v>
+        <v>0.494949</v>
       </c>
       <c r="N14">
-        <v>5.325353999999999</v>
+        <v>5.274050999999999</v>
       </c>
       <c r="O14">
-        <v>0.7988030999999999</v>
+        <v>0.7911076499999998</v>
       </c>
       <c r="P14">
-        <v>4.526550899999999</v>
+        <v>4.482943349999999</v>
       </c>
       <c r="Q14">
-        <v>8.877550899999999</v>
+        <v>8.833943349999998</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09856380752737165</v>
+        <v>0.09908876523037358</v>
       </c>
       <c r="T14">
-        <v>1.000909931361111</v>
+        <v>1.010868185003185</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.15</v>
       </c>
       <c r="W14">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.00361098713839</v>
+        <v>11.6557463496239</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09193112575042502</v>
+        <v>0.09184250087676293</v>
       </c>
       <c r="C15">
-        <v>65.60021685817202</v>
+        <v>64.99357584837983</v>
       </c>
       <c r="D15">
-        <v>66.68521685817203</v>
+        <v>66.81357584837984</v>
       </c>
       <c r="E15">
-        <v>-23.445</v>
+        <v>-22.71</v>
       </c>
       <c r="F15">
-        <v>9.555</v>
+        <v>10.29</v>
       </c>
       <c r="G15">
         <v>8.470000000000001</v>
@@ -2517,28 +2517,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M15">
-        <v>0.494949</v>
+        <v>0.533022</v>
       </c>
       <c r="N15">
-        <v>5.274050999999999</v>
+        <v>5.235977999999999</v>
       </c>
       <c r="O15">
-        <v>0.7911076499999998</v>
+        <v>0.7853966999999998</v>
       </c>
       <c r="P15">
-        <v>4.482943349999999</v>
+        <v>4.4505813</v>
       </c>
       <c r="Q15">
-        <v>8.833943349999998</v>
+        <v>8.801581299999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09908876523037358</v>
+        <v>0.09962593125204994</v>
       </c>
       <c r="T15">
-        <v>1.010868185003185</v>
+        <v>1.021058025939261</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.6557463496239</v>
+        <v>10.82319303893648</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09184250087676293</v>
+        <v>0.09175387600310091</v>
       </c>
       <c r="C16">
-        <v>64.99357584837983</v>
+        <v>64.38742993498771</v>
       </c>
       <c r="D16">
-        <v>66.81357584837984</v>
+        <v>66.94242993498771</v>
       </c>
       <c r="E16">
-        <v>-22.71</v>
+        <v>-21.975</v>
       </c>
       <c r="F16">
-        <v>10.29</v>
+        <v>11.025</v>
       </c>
       <c r="G16">
         <v>8.470000000000001</v>
@@ -2599,28 +2599,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M16">
-        <v>0.533022</v>
+        <v>0.5710950000000001</v>
       </c>
       <c r="N16">
-        <v>5.235977999999999</v>
+        <v>5.197904999999999</v>
       </c>
       <c r="O16">
-        <v>0.7853966999999998</v>
+        <v>0.7796857499999997</v>
       </c>
       <c r="P16">
-        <v>4.4505813</v>
+        <v>4.418219249999999</v>
       </c>
       <c r="Q16">
-        <v>8.801581299999999</v>
+        <v>8.769219249999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09962593125204994</v>
+        <v>0.1001757364742364</v>
       </c>
       <c r="T16">
-        <v>1.021058025939261</v>
+        <v>1.031487627838538</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.82319303893648</v>
+        <v>10.10164683634071</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09175387600310091</v>
+        <v>0.09189645112943887</v>
       </c>
       <c r="C17">
-        <v>64.38742993498771</v>
+        <v>63.44537873752025</v>
       </c>
       <c r="D17">
-        <v>66.94242993498771</v>
+        <v>66.73537873752025</v>
       </c>
       <c r="E17">
-        <v>-21.975</v>
+        <v>-21.24</v>
       </c>
       <c r="F17">
-        <v>11.025</v>
+        <v>11.76</v>
       </c>
       <c r="G17">
         <v>8.470000000000001</v>
@@ -2681,45 +2681,45 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M17">
-        <v>0.571095</v>
+        <v>0.6291599999999999</v>
       </c>
       <c r="N17">
-        <v>5.197905</v>
+        <v>5.13984</v>
       </c>
       <c r="O17">
-        <v>0.77968575</v>
+        <v>0.7709759999999999</v>
       </c>
       <c r="P17">
-        <v>4.41821925</v>
+        <v>4.368863999999999</v>
       </c>
       <c r="Q17">
-        <v>8.769219249999999</v>
+        <v>8.719863999999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1001757364742364</v>
+        <v>0.100738632296951</v>
       </c>
       <c r="T17">
-        <v>1.031487627838538</v>
+        <v>1.04216555359256</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.15</v>
       </c>
       <c r="W17">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>10.10164683634071</v>
+        <v>9.16936868205226</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09189645112943887</v>
+        <v>0.0918222762557768</v>
       </c>
       <c r="C18">
-        <v>63.44537873752025</v>
+        <v>62.81793726546299</v>
       </c>
       <c r="D18">
-        <v>66.73537873752025</v>
+        <v>66.84293726546299</v>
       </c>
       <c r="E18">
-        <v>-21.24</v>
+        <v>-20.505</v>
       </c>
       <c r="F18">
-        <v>11.76</v>
+        <v>12.495</v>
       </c>
       <c r="G18">
         <v>8.470000000000001</v>
@@ -2763,28 +2763,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M18">
-        <v>0.6291599999999999</v>
+        <v>0.6684825000000001</v>
       </c>
       <c r="N18">
-        <v>5.13984</v>
+        <v>5.100517499999999</v>
       </c>
       <c r="O18">
-        <v>0.7709759999999999</v>
+        <v>0.7650776249999998</v>
       </c>
       <c r="P18">
-        <v>4.368863999999999</v>
+        <v>4.335439874999999</v>
       </c>
       <c r="Q18">
-        <v>8.719863999999999</v>
+        <v>8.686439874999998</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.100738632296951</v>
+        <v>0.1013150918744299</v>
       </c>
       <c r="T18">
-        <v>1.04216555359256</v>
+        <v>1.053100778762342</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.16936868205226</v>
+        <v>8.629994053696242</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0918222762557768</v>
+        <v>0.09174810138211476</v>
       </c>
       <c r="C19">
-        <v>62.81793726546299</v>
+        <v>62.19084306086535</v>
       </c>
       <c r="D19">
-        <v>66.84293726546299</v>
+        <v>66.95084306086535</v>
       </c>
       <c r="E19">
-        <v>-20.505</v>
+        <v>-19.77</v>
       </c>
       <c r="F19">
-        <v>12.495</v>
+        <v>13.23</v>
       </c>
       <c r="G19">
         <v>8.470000000000001</v>
@@ -2845,28 +2845,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M19">
-        <v>0.6684825000000001</v>
+        <v>0.7078050000000001</v>
       </c>
       <c r="N19">
-        <v>5.100517499999999</v>
+        <v>5.061194999999999</v>
       </c>
       <c r="O19">
-        <v>0.7650776249999998</v>
+        <v>0.7591792499999998</v>
       </c>
       <c r="P19">
-        <v>4.335439874999999</v>
+        <v>4.302015749999999</v>
       </c>
       <c r="Q19">
-        <v>8.686439874999998</v>
+        <v>8.653015749999998</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1013150918744299</v>
+        <v>0.1019056114416034</v>
       </c>
       <c r="T19">
-        <v>1.053100778762342</v>
+        <v>1.064302716741143</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.629994053696242</v>
+        <v>8.150549939602005</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09174810138211477</v>
+        <v>0.09167392650845274</v>
       </c>
       <c r="C20">
-        <v>62.19084306086534</v>
+        <v>61.56409780824761</v>
       </c>
       <c r="D20">
-        <v>66.95084306086534</v>
+        <v>67.05909780824761</v>
       </c>
       <c r="E20">
-        <v>-19.77</v>
+        <v>-19.035</v>
       </c>
       <c r="F20">
-        <v>13.23</v>
+        <v>13.965</v>
       </c>
       <c r="G20">
         <v>8.470000000000001</v>
@@ -2927,28 +2927,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M20">
-        <v>0.7078049999999999</v>
+        <v>0.7471274999999999</v>
       </c>
       <c r="N20">
-        <v>5.061195</v>
+        <v>5.021872499999999</v>
       </c>
       <c r="O20">
-        <v>0.75917925</v>
+        <v>0.7532808749999998</v>
       </c>
       <c r="P20">
-        <v>4.30201575</v>
+        <v>4.268591624999999</v>
       </c>
       <c r="Q20">
-        <v>8.65301575</v>
+        <v>8.619591624999998</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1019056114416034</v>
+        <v>0.1025107117388305</v>
       </c>
       <c r="T20">
-        <v>1.064302716741143</v>
+        <v>1.075781245781148</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.150549939602008</v>
+        <v>7.721573626991376</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09167392650845274</v>
+        <v>0.09173575163479068</v>
       </c>
       <c r="C21">
-        <v>61.56409780824761</v>
+        <v>60.73884267914762</v>
       </c>
       <c r="D21">
-        <v>67.05909780824761</v>
+        <v>66.96884267914763</v>
       </c>
       <c r="E21">
-        <v>-19.035</v>
+        <v>-18.3</v>
       </c>
       <c r="F21">
-        <v>13.965</v>
+        <v>14.7</v>
       </c>
       <c r="G21">
         <v>8.470000000000001</v>
@@ -3009,45 +3009,45 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M21">
-        <v>0.7471274999999999</v>
+        <v>0.7982100000000001</v>
       </c>
       <c r="N21">
-        <v>5.021872499999999</v>
+        <v>4.970789999999999</v>
       </c>
       <c r="O21">
-        <v>0.7532808749999998</v>
+        <v>0.7456184999999999</v>
       </c>
       <c r="P21">
-        <v>4.268591624999999</v>
+        <v>4.225171499999999</v>
       </c>
       <c r="Q21">
-        <v>8.619591624999998</v>
+        <v>8.576171499999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1025107117388305</v>
+        <v>0.1031309395434883</v>
       </c>
       <c r="T21">
-        <v>1.075781245781148</v>
+        <v>1.087546738047154</v>
       </c>
       <c r="U21">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.15</v>
       </c>
       <c r="W21">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>7.721573626991376</v>
+        <v>7.227421355282443</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09173575163479068</v>
+        <v>0.09166837676112863</v>
       </c>
       <c r="C22">
-        <v>60.73884267914762</v>
+        <v>60.10221148208781</v>
       </c>
       <c r="D22">
-        <v>66.96884267914763</v>
+        <v>67.06721148208781</v>
       </c>
       <c r="E22">
-        <v>-18.3</v>
+        <v>-17.565</v>
       </c>
       <c r="F22">
-        <v>14.7</v>
+        <v>15.435</v>
       </c>
       <c r="G22">
         <v>8.470000000000001</v>
@@ -3091,28 +3091,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M22">
-        <v>0.7982100000000001</v>
+        <v>0.8381205000000002</v>
       </c>
       <c r="N22">
-        <v>4.970789999999999</v>
+        <v>4.930879499999999</v>
       </c>
       <c r="O22">
-        <v>0.7456184999999999</v>
+        <v>0.7396319249999997</v>
       </c>
       <c r="P22">
-        <v>4.225171499999999</v>
+        <v>4.191247574999999</v>
       </c>
       <c r="Q22">
-        <v>8.576171499999999</v>
+        <v>8.542247574999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1031309395434883</v>
+        <v>0.1037668693178843</v>
       </c>
       <c r="T22">
-        <v>1.087546738047154</v>
+        <v>1.099610090876857</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.227421355282443</v>
+        <v>6.883258433602325</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09166837676112863</v>
+        <v>0.09160100188746657</v>
       </c>
       <c r="C23">
-        <v>60.10221148208781</v>
+        <v>59.46586969291853</v>
       </c>
       <c r="D23">
-        <v>67.06721148208781</v>
+        <v>67.16586969291853</v>
       </c>
       <c r="E23">
-        <v>-17.565</v>
+        <v>-16.83</v>
       </c>
       <c r="F23">
-        <v>15.435</v>
+        <v>16.17</v>
       </c>
       <c r="G23">
         <v>8.470000000000001</v>
@@ -3173,28 +3173,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M23">
-        <v>0.8381204999999999</v>
+        <v>0.8780310000000001</v>
       </c>
       <c r="N23">
-        <v>4.9308795</v>
+        <v>4.890968999999999</v>
       </c>
       <c r="O23">
-        <v>0.739631925</v>
+        <v>0.7336453499999999</v>
       </c>
       <c r="P23">
-        <v>4.191247574999999</v>
+        <v>4.157323649999999</v>
       </c>
       <c r="Q23">
-        <v>8.542247574999999</v>
+        <v>8.508323649999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1037668693178843</v>
+        <v>0.1044191049839315</v>
       </c>
       <c r="T23">
-        <v>1.099610090876856</v>
+        <v>1.111982760445782</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.883258433602328</v>
+        <v>6.570383050256766</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09160100188746657</v>
+        <v>0.09153362701380453</v>
       </c>
       <c r="C24">
-        <v>59.46586969291853</v>
+        <v>58.82981859070867</v>
       </c>
       <c r="D24">
-        <v>67.16586969291853</v>
+        <v>67.26481859070867</v>
       </c>
       <c r="E24">
-        <v>-16.83</v>
+        <v>-16.095</v>
       </c>
       <c r="F24">
-        <v>16.17</v>
+        <v>16.905</v>
       </c>
       <c r="G24">
         <v>8.470000000000001</v>
@@ -3255,28 +3255,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M24">
-        <v>0.8780310000000001</v>
+        <v>0.9179415000000001</v>
       </c>
       <c r="N24">
-        <v>4.890968999999999</v>
+        <v>4.851058499999999</v>
       </c>
       <c r="O24">
-        <v>0.7336453499999999</v>
+        <v>0.7276587749999998</v>
       </c>
       <c r="P24">
-        <v>4.157323649999999</v>
+        <v>4.123399724999999</v>
       </c>
       <c r="Q24">
-        <v>8.508323649999999</v>
+        <v>8.474399724999998</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1044191049839315</v>
+        <v>0.1050882818361098</v>
       </c>
       <c r="T24">
-        <v>1.111982760445782</v>
+        <v>1.124676798055459</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.570383050256766</v>
+        <v>6.284714221984733</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09153362701380453</v>
+        <v>0.09167025214014249</v>
       </c>
       <c r="C25">
-        <v>58.82981859070867</v>
+        <v>57.89446947751919</v>
       </c>
       <c r="D25">
-        <v>67.26481859070867</v>
+        <v>67.0644694775192</v>
       </c>
       <c r="E25">
-        <v>-16.095</v>
+        <v>-15.36</v>
       </c>
       <c r="F25">
-        <v>16.905</v>
+        <v>17.64</v>
       </c>
       <c r="G25">
         <v>8.470000000000001</v>
@@ -3337,45 +3337,45 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M25">
-        <v>0.9179415000000001</v>
+        <v>0.975492</v>
       </c>
       <c r="N25">
-        <v>4.851058499999999</v>
+        <v>4.793507999999999</v>
       </c>
       <c r="O25">
-        <v>0.7276587749999998</v>
+        <v>0.7190261999999998</v>
       </c>
       <c r="P25">
-        <v>4.123399724999999</v>
+        <v>4.074481799999999</v>
       </c>
       <c r="Q25">
-        <v>8.474399724999998</v>
+        <v>8.4254818</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1050882818361098</v>
+        <v>0.1057750686054506</v>
       </c>
       <c r="T25">
-        <v>1.124676798055459</v>
+        <v>1.137704889286443</v>
       </c>
       <c r="U25">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.15</v>
       </c>
       <c r="W25">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.284714221984733</v>
+        <v>5.913938812414657</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09167025214014249</v>
+        <v>0.09161137726648043</v>
       </c>
       <c r="C26">
-        <v>57.89446947751919</v>
+        <v>57.24565793993399</v>
       </c>
       <c r="D26">
-        <v>67.0644694775192</v>
+        <v>67.15065793993399</v>
       </c>
       <c r="E26">
-        <v>-15.36</v>
+        <v>-14.625</v>
       </c>
       <c r="F26">
-        <v>17.64</v>
+        <v>18.375</v>
       </c>
       <c r="G26">
         <v>8.470000000000001</v>
@@ -3419,28 +3419,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M26">
-        <v>0.975492</v>
+        <v>1.0161375</v>
       </c>
       <c r="N26">
-        <v>4.793507999999999</v>
+        <v>4.752862499999999</v>
       </c>
       <c r="O26">
-        <v>0.7190261999999998</v>
+        <v>0.7129293749999999</v>
       </c>
       <c r="P26">
-        <v>4.074481799999999</v>
+        <v>4.039933124999999</v>
       </c>
       <c r="Q26">
-        <v>8.4254818</v>
+        <v>8.390933125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1057750686054506</v>
+        <v>0.1064801696886406</v>
       </c>
       <c r="T26">
-        <v>1.137704889286443</v>
+        <v>1.151080396283586</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.913938812414657</v>
+        <v>5.677381259918071</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09161137726648043</v>
+        <v>0.0915525023928184</v>
       </c>
       <c r="C27">
-        <v>57.24565793993399</v>
+        <v>56.5970682190613</v>
       </c>
       <c r="D27">
-        <v>67.15065793993399</v>
+        <v>67.2370682190613</v>
       </c>
       <c r="E27">
-        <v>-14.625</v>
+        <v>-13.89</v>
       </c>
       <c r="F27">
-        <v>18.375</v>
+        <v>19.11</v>
       </c>
       <c r="G27">
         <v>8.470000000000001</v>
@@ -3501,28 +3501,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M27">
-        <v>1.0161375</v>
+        <v>1.056783</v>
       </c>
       <c r="N27">
-        <v>4.752862499999999</v>
+        <v>4.712216999999999</v>
       </c>
       <c r="O27">
-        <v>0.7129293749999999</v>
+        <v>0.7068325499999998</v>
       </c>
       <c r="P27">
-        <v>4.039933124999999</v>
+        <v>4.005384449999999</v>
       </c>
       <c r="Q27">
-        <v>8.390933125</v>
+        <v>8.35638445</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1064801696886406</v>
+        <v>0.1072043275578627</v>
       </c>
       <c r="T27">
-        <v>1.151080396283586</v>
+        <v>1.164817403469842</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.677381259918071</v>
+        <v>5.459020442228915</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0915525023928184</v>
+        <v>0.09149362751915635</v>
       </c>
       <c r="C28">
-        <v>56.5970682190613</v>
+        <v>55.94870117231378</v>
       </c>
       <c r="D28">
-        <v>67.2370682190613</v>
+        <v>67.32370117231378</v>
       </c>
       <c r="E28">
-        <v>-13.89</v>
+        <v>-13.155</v>
       </c>
       <c r="F28">
-        <v>19.11</v>
+        <v>19.845</v>
       </c>
       <c r="G28">
         <v>8.470000000000001</v>
@@ -3583,28 +3583,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M28">
-        <v>1.056783</v>
+        <v>1.0974285</v>
       </c>
       <c r="N28">
-        <v>4.712216999999999</v>
+        <v>4.671571499999999</v>
       </c>
       <c r="O28">
-        <v>0.7068325499999998</v>
+        <v>0.7007357249999998</v>
       </c>
       <c r="P28">
-        <v>4.005384449999999</v>
+        <v>3.970835774999999</v>
       </c>
       <c r="Q28">
-        <v>8.35638445</v>
+        <v>8.321835774999998</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1072043275578627</v>
+        <v>0.1079483253687073</v>
       </c>
       <c r="T28">
-        <v>1.164817403469842</v>
+        <v>1.178930767017364</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.459020442228915</v>
+        <v>5.256834499924139</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09149362751915635</v>
+        <v>0.0914347526454943</v>
       </c>
       <c r="C29">
-        <v>55.94870117231378</v>
+        <v>55.30055766152876</v>
       </c>
       <c r="D29">
-        <v>67.32370117231378</v>
+        <v>67.41055766152876</v>
       </c>
       <c r="E29">
-        <v>-13.155</v>
+        <v>-12.42</v>
       </c>
       <c r="F29">
-        <v>19.845</v>
+        <v>20.58</v>
       </c>
       <c r="G29">
         <v>8.470000000000001</v>
@@ -3665,28 +3665,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M29">
-        <v>1.0974285</v>
+        <v>1.138074</v>
       </c>
       <c r="N29">
-        <v>4.671571499999999</v>
+        <v>4.630925999999999</v>
       </c>
       <c r="O29">
-        <v>0.7007357249999998</v>
+        <v>0.6946388999999998</v>
       </c>
       <c r="P29">
-        <v>3.970835774999999</v>
+        <v>3.936287099999999</v>
       </c>
       <c r="Q29">
-        <v>8.321835774999998</v>
+        <v>8.287287099999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1079483253687073</v>
+        <v>0.1087129897854087</v>
       </c>
       <c r="T29">
-        <v>1.178930767017364</v>
+        <v>1.193436168441207</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.256834499924139</v>
+        <v>5.069090410641134</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0914347526454943</v>
+        <v>0.09137587777183225</v>
       </c>
       <c r="C30">
-        <v>55.30055766152876</v>
+        <v>54.65263855299683</v>
       </c>
       <c r="D30">
-        <v>67.41055766152876</v>
+        <v>67.49763855299683</v>
       </c>
       <c r="E30">
-        <v>-12.42</v>
+        <v>-11.685</v>
       </c>
       <c r="F30">
-        <v>20.58</v>
+        <v>21.315</v>
       </c>
       <c r="G30">
         <v>8.470000000000001</v>
@@ -3747,28 +3747,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M30">
-        <v>1.138074</v>
+        <v>1.1787195</v>
       </c>
       <c r="N30">
-        <v>4.630925999999999</v>
+        <v>4.590280499999999</v>
       </c>
       <c r="O30">
-        <v>0.6946388999999998</v>
+        <v>0.6885420749999998</v>
       </c>
       <c r="P30">
-        <v>3.936287099999999</v>
+        <v>3.901738424999999</v>
       </c>
       <c r="Q30">
-        <v>8.287287099999999</v>
+        <v>8.252738424999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1087129897854087</v>
+        <v>0.1094991940448342</v>
       </c>
       <c r="T30">
-        <v>1.193436168441207</v>
+        <v>1.20835017272206</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.069090410641134</v>
+        <v>4.894294189584543</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09137587777183225</v>
+        <v>0.09131700289817021</v>
       </c>
       <c r="C31">
-        <v>54.65263855299683</v>
+        <v>54.00494471749064</v>
       </c>
       <c r="D31">
-        <v>67.49763855299683</v>
+        <v>67.58494471749064</v>
       </c>
       <c r="E31">
-        <v>-11.685</v>
+        <v>-10.95</v>
       </c>
       <c r="F31">
-        <v>21.315</v>
+        <v>22.05</v>
       </c>
       <c r="G31">
         <v>8.470000000000001</v>
@@ -3829,28 +3829,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M31">
-        <v>1.1787195</v>
+        <v>1.219365</v>
       </c>
       <c r="N31">
-        <v>4.5902805</v>
+        <v>4.549634999999999</v>
       </c>
       <c r="O31">
-        <v>0.6885420749999999</v>
+        <v>0.6824452499999999</v>
       </c>
       <c r="P31">
-        <v>3.901738425</v>
+        <v>3.86718975</v>
       </c>
       <c r="Q31">
-        <v>8.252738425</v>
+        <v>8.218189750000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1094991940448342</v>
+        <v>0.1103078612831003</v>
       </c>
       <c r="T31">
-        <v>1.20835017272206</v>
+        <v>1.223690291410937</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.894294189584545</v>
+        <v>4.731151049931726</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09131700289817021</v>
+        <v>0.09125812802450815</v>
       </c>
       <c r="C32">
-        <v>54.00494471749064</v>
+        <v>53.35747703029409</v>
       </c>
       <c r="D32">
-        <v>67.58494471749064</v>
+        <v>67.67247703029409</v>
       </c>
       <c r="E32">
-        <v>-10.95</v>
+        <v>-10.215</v>
       </c>
       <c r="F32">
-        <v>22.05</v>
+        <v>22.785</v>
       </c>
       <c r="G32">
         <v>8.470000000000001</v>
@@ -3911,28 +3911,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M32">
-        <v>1.219365</v>
+        <v>1.2600105</v>
       </c>
       <c r="N32">
-        <v>4.549634999999999</v>
+        <v>4.508989499999999</v>
       </c>
       <c r="O32">
-        <v>0.6824452499999999</v>
+        <v>0.6763484249999999</v>
       </c>
       <c r="P32">
-        <v>3.86718975</v>
+        <v>3.832641074999999</v>
       </c>
       <c r="Q32">
-        <v>8.218189750000001</v>
+        <v>8.183641074999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1103078612831003</v>
+        <v>0.1111399681514611</v>
       </c>
       <c r="T32">
-        <v>1.223690291410937</v>
+        <v>1.23947505122123</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.731151049931726</v>
+        <v>4.578533274127476</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09125812802450815</v>
+        <v>0.09187925315084609</v>
       </c>
       <c r="C33">
-        <v>53.35747703029409</v>
+        <v>51.71028612070094</v>
       </c>
       <c r="D33">
-        <v>67.67247703029409</v>
+        <v>66.76028612070094</v>
       </c>
       <c r="E33">
-        <v>-10.215</v>
+        <v>-9.48</v>
       </c>
       <c r="F33">
-        <v>22.785</v>
+        <v>23.52</v>
       </c>
       <c r="G33">
         <v>8.470000000000001</v>
@@ -3993,45 +3993,45 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M33">
-        <v>1.2600105</v>
+        <v>1.359456</v>
       </c>
       <c r="N33">
-        <v>4.508989499999999</v>
+        <v>4.409543999999999</v>
       </c>
       <c r="O33">
-        <v>0.6763484249999999</v>
+        <v>0.6614315999999999</v>
       </c>
       <c r="P33">
-        <v>3.832641074999999</v>
+        <v>3.7481124</v>
       </c>
       <c r="Q33">
-        <v>8.183641074999999</v>
+        <v>8.099112399999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1111399681514611</v>
+        <v>0.1119965487512443</v>
       </c>
       <c r="T33">
-        <v>1.23947505122123</v>
+        <v>1.255724068673003</v>
       </c>
       <c r="U33">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V33">
         <v>0.15</v>
       </c>
       <c r="W33">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.578533274127476</v>
+        <v>4.243609208389238</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09187925315084609</v>
+        <v>0.09184162827718406</v>
       </c>
       <c r="C34">
-        <v>51.71028612070094</v>
+        <v>51.02984212631852</v>
       </c>
       <c r="D34">
-        <v>66.76028612070094</v>
+        <v>66.81484212631852</v>
       </c>
       <c r="E34">
-        <v>-9.48</v>
+        <v>-8.744999999999997</v>
       </c>
       <c r="F34">
-        <v>23.52</v>
+        <v>24.255</v>
       </c>
       <c r="G34">
         <v>8.470000000000001</v>
@@ -4075,28 +4075,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M34">
-        <v>1.359456</v>
+        <v>1.401939</v>
       </c>
       <c r="N34">
-        <v>4.409543999999999</v>
+        <v>4.367060999999999</v>
       </c>
       <c r="O34">
-        <v>0.6614315999999999</v>
+        <v>0.6550591499999998</v>
       </c>
       <c r="P34">
-        <v>3.7481124</v>
+        <v>3.712001849999999</v>
       </c>
       <c r="Q34">
-        <v>8.099112399999999</v>
+        <v>8.063001849999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1119965487512443</v>
+        <v>0.1128786989211703</v>
       </c>
       <c r="T34">
-        <v>1.255724068673003</v>
+        <v>1.272458131421844</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.243609208389238</v>
+        <v>4.115014989953199</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09184162827718406</v>
+        <v>0.09281550340352202</v>
       </c>
       <c r="C35">
-        <v>51.02984212631852</v>
+        <v>48.91084518687185</v>
       </c>
       <c r="D35">
-        <v>66.81484212631852</v>
+        <v>65.43084518687185</v>
       </c>
       <c r="E35">
-        <v>-8.744999999999997</v>
+        <v>-8.009999999999998</v>
       </c>
       <c r="F35">
-        <v>24.255</v>
+        <v>24.99</v>
       </c>
       <c r="G35">
         <v>8.470000000000001</v>
@@ -4157,45 +4157,45 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M35">
-        <v>1.401939</v>
+        <v>1.531887</v>
       </c>
       <c r="N35">
-        <v>4.367060999999999</v>
+        <v>4.237112999999999</v>
       </c>
       <c r="O35">
-        <v>0.6550591499999998</v>
+        <v>0.6355669499999999</v>
       </c>
       <c r="P35">
-        <v>3.712001849999999</v>
+        <v>3.601546049999999</v>
       </c>
       <c r="Q35">
-        <v>8.063001849999999</v>
+        <v>7.952546049999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1128786989211703</v>
+        <v>0.1137875809144273</v>
       </c>
       <c r="T35">
-        <v>1.272458131421844</v>
+        <v>1.289699286981255</v>
       </c>
       <c r="U35">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V35">
         <v>0.15</v>
       </c>
       <c r="W35">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.115014989953199</v>
+        <v>3.765943571555864</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09281550340352202</v>
+        <v>0.09280762852985994</v>
       </c>
       <c r="C36">
-        <v>48.91084518687185</v>
+        <v>48.18680637882228</v>
       </c>
       <c r="D36">
-        <v>65.43084518687185</v>
+        <v>65.44180637882228</v>
       </c>
       <c r="E36">
-        <v>-8.009999999999998</v>
+        <v>-7.274999999999999</v>
       </c>
       <c r="F36">
-        <v>24.99</v>
+        <v>25.725</v>
       </c>
       <c r="G36">
         <v>8.470000000000001</v>
@@ -4239,28 +4239,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M36">
-        <v>1.531887</v>
+        <v>1.5769425</v>
       </c>
       <c r="N36">
-        <v>4.237112999999999</v>
+        <v>4.192057499999999</v>
       </c>
       <c r="O36">
-        <v>0.6355669499999999</v>
+        <v>0.6288086249999998</v>
       </c>
       <c r="P36">
-        <v>3.601546049999999</v>
+        <v>3.563248874999999</v>
       </c>
       <c r="Q36">
-        <v>7.952546049999999</v>
+        <v>7.914248874999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1137875809144273</v>
+        <v>0.1147244285074769</v>
       </c>
       <c r="T36">
-        <v>1.289699286981255</v>
+        <v>1.307470939634803</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.765943571555864</v>
+        <v>3.658345183797125</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09280762852985994</v>
+        <v>0.09279975365619791</v>
       </c>
       <c r="C37">
-        <v>48.18680637882228</v>
+        <v>47.4627712438983</v>
       </c>
       <c r="D37">
-        <v>65.44180637882228</v>
+        <v>65.45277124389831</v>
       </c>
       <c r="E37">
-        <v>-7.274999999999999</v>
+        <v>-6.539999999999996</v>
       </c>
       <c r="F37">
-        <v>25.725</v>
+        <v>26.46</v>
       </c>
       <c r="G37">
         <v>8.470000000000001</v>
@@ -4321,28 +4321,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M37">
-        <v>1.5769425</v>
+        <v>1.621998</v>
       </c>
       <c r="N37">
-        <v>4.192057499999999</v>
+        <v>4.147001999999999</v>
       </c>
       <c r="O37">
-        <v>0.6288086249999998</v>
+        <v>0.6220502999999998</v>
       </c>
       <c r="P37">
-        <v>3.563248874999999</v>
+        <v>3.524951699999999</v>
       </c>
       <c r="Q37">
-        <v>7.914248874999999</v>
+        <v>7.875951699999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1147244285074769</v>
+        <v>0.1156905525878092</v>
       </c>
       <c r="T37">
-        <v>1.307470939634803</v>
+        <v>1.325797956433773</v>
       </c>
       <c r="U37">
         <v>0.0613</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.658345183797125</v>
+        <v>3.556724484247205</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09279975365619791</v>
+        <v>0.09367247878253586</v>
       </c>
       <c r="C38">
-        <v>47.46277124389832</v>
+        <v>45.53455377311553</v>
       </c>
       <c r="D38">
-        <v>65.45277124389831</v>
+        <v>64.25955377311553</v>
       </c>
       <c r="E38">
-        <v>-6.540000000000003</v>
+        <v>-5.805</v>
       </c>
       <c r="F38">
-        <v>26.46</v>
+        <v>27.195</v>
       </c>
       <c r="G38">
         <v>8.470000000000001</v>
@@ -4403,45 +4403,45 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M38">
-        <v>1.621998</v>
+        <v>1.7431995</v>
       </c>
       <c r="N38">
-        <v>4.147002</v>
+        <v>4.025800499999999</v>
       </c>
       <c r="O38">
-        <v>0.6220502999999999</v>
+        <v>0.6038700749999998</v>
       </c>
       <c r="P38">
-        <v>3.5249517</v>
+        <v>3.421930424999999</v>
       </c>
       <c r="Q38">
-        <v>7.8759517</v>
+        <v>7.772930424999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1156905525878092</v>
+        <v>0.1166873472738665</v>
       </c>
       <c r="T38">
-        <v>1.325797956433773</v>
+        <v>1.344706783289854</v>
       </c>
       <c r="U38">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V38">
         <v>0.15</v>
       </c>
       <c r="W38">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.556724484247206</v>
+        <v>3.309431880860451</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09367247878253586</v>
+        <v>0.09368840390887381</v>
       </c>
       <c r="C39">
-        <v>45.53455377311553</v>
+        <v>44.77818447640218</v>
       </c>
       <c r="D39">
-        <v>64.25955377311553</v>
+        <v>64.23818447640218</v>
       </c>
       <c r="E39">
-        <v>-5.805</v>
+        <v>-5.07</v>
       </c>
       <c r="F39">
-        <v>27.195</v>
+        <v>27.93</v>
       </c>
       <c r="G39">
         <v>8.470000000000001</v>
@@ -4485,28 +4485,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M39">
-        <v>1.7431995</v>
+        <v>1.790313</v>
       </c>
       <c r="N39">
-        <v>4.025800499999999</v>
+        <v>3.978686999999999</v>
       </c>
       <c r="O39">
-        <v>0.6038700749999998</v>
+        <v>0.5968030499999998</v>
       </c>
       <c r="P39">
-        <v>3.421930424999999</v>
+        <v>3.381883949999999</v>
       </c>
       <c r="Q39">
-        <v>7.772930424999999</v>
+        <v>7.73288395</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1166873472738665</v>
+        <v>0.1177162966272158</v>
       </c>
       <c r="T39">
-        <v>1.344706783289854</v>
+        <v>1.364225572302583</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.309431880860451</v>
+        <v>3.222341568206229</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09368840390887381</v>
+        <v>0.09370432903521178</v>
       </c>
       <c r="C40">
-        <v>44.77818447640218</v>
+        <v>44.02182938753836</v>
       </c>
       <c r="D40">
-        <v>64.23818447640218</v>
+        <v>64.21682938753837</v>
       </c>
       <c r="E40">
-        <v>-5.07</v>
+        <v>-4.334999999999997</v>
       </c>
       <c r="F40">
-        <v>27.93</v>
+        <v>28.665</v>
       </c>
       <c r="G40">
         <v>8.470000000000001</v>
@@ -4567,28 +4567,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M40">
-        <v>1.790313</v>
+        <v>1.8374265</v>
       </c>
       <c r="N40">
-        <v>3.978686999999999</v>
+        <v>3.931573499999999</v>
       </c>
       <c r="O40">
-        <v>0.5968030499999998</v>
+        <v>0.5897360249999998</v>
       </c>
       <c r="P40">
-        <v>3.381883949999999</v>
+        <v>3.341837474999999</v>
       </c>
       <c r="Q40">
-        <v>7.73288395</v>
+        <v>7.692837474999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1177162966272158</v>
+        <v>0.1187789820249373</v>
       </c>
       <c r="T40">
-        <v>1.364225572302583</v>
+        <v>1.38438432161081</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.222341568206229</v>
+        <v>3.13971742543171</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09370432903521178</v>
+        <v>0.09372025416154972</v>
       </c>
       <c r="C41">
-        <v>44.02182938753836</v>
+        <v>43.26548849235924</v>
       </c>
       <c r="D41">
-        <v>64.21682938753837</v>
+        <v>64.19548849235925</v>
       </c>
       <c r="E41">
-        <v>-4.334999999999997</v>
+        <v>-3.599999999999998</v>
       </c>
       <c r="F41">
-        <v>28.665</v>
+        <v>29.4</v>
       </c>
       <c r="G41">
         <v>8.470000000000001</v>
@@ -4649,28 +4649,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M41">
-        <v>1.8374265</v>
+        <v>1.88454</v>
       </c>
       <c r="N41">
-        <v>3.931573499999999</v>
+        <v>3.884459999999999</v>
       </c>
       <c r="O41">
-        <v>0.5897360249999998</v>
+        <v>0.5826689999999998</v>
       </c>
       <c r="P41">
-        <v>3.341837474999999</v>
+        <v>3.301790999999999</v>
       </c>
       <c r="Q41">
-        <v>7.692837474999999</v>
+        <v>7.652790999999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1187789820249373</v>
+        <v>0.1198770902692496</v>
       </c>
       <c r="T41">
-        <v>1.38438432161081</v>
+        <v>1.405215029229313</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.13971742543171</v>
+        <v>3.061224489795917</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09372025416154972</v>
+        <v>0.09645447928788767</v>
       </c>
       <c r="C42">
-        <v>43.26548849235924</v>
+        <v>39.06534740116817</v>
       </c>
       <c r="D42">
-        <v>64.19548849235925</v>
+        <v>60.73034740116817</v>
       </c>
       <c r="E42">
-        <v>-3.599999999999998</v>
+        <v>-2.864999999999998</v>
       </c>
       <c r="F42">
-        <v>29.4</v>
+        <v>30.135</v>
       </c>
       <c r="G42">
         <v>8.470000000000001</v>
@@ -4731,45 +4731,45 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M42">
-        <v>1.88454</v>
+        <v>2.1667065</v>
       </c>
       <c r="N42">
-        <v>3.884459999999999</v>
+        <v>3.602293499999999</v>
       </c>
       <c r="O42">
-        <v>0.5826689999999998</v>
+        <v>0.5403440249999999</v>
       </c>
       <c r="P42">
-        <v>3.301790999999999</v>
+        <v>3.061949474999999</v>
       </c>
       <c r="Q42">
-        <v>7.652790999999999</v>
+        <v>7.412949475</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1198770902692496</v>
+        <v>0.1210124225218435</v>
       </c>
       <c r="T42">
-        <v>1.405215029229313</v>
+        <v>1.426751862529798</v>
       </c>
       <c r="U42">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V42">
         <v>0.15</v>
       </c>
       <c r="W42">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.061224489795917</v>
+        <v>2.662566434355552</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09645447928788767</v>
+        <v>0.09653670441422563</v>
       </c>
       <c r="C43">
-        <v>39.06534740116817</v>
+        <v>38.23192633607808</v>
       </c>
       <c r="D43">
-        <v>60.73034740116817</v>
+        <v>60.63192633607808</v>
       </c>
       <c r="E43">
-        <v>-2.864999999999998</v>
+        <v>-2.129999999999995</v>
       </c>
       <c r="F43">
-        <v>30.135</v>
+        <v>30.87</v>
       </c>
       <c r="G43">
         <v>8.470000000000001</v>
@@ -4813,28 +4813,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M43">
-        <v>2.1667065</v>
+        <v>2.219553</v>
       </c>
       <c r="N43">
-        <v>3.602293499999999</v>
+        <v>3.549446999999999</v>
       </c>
       <c r="O43">
-        <v>0.5403440249999999</v>
+        <v>0.5324170499999998</v>
       </c>
       <c r="P43">
-        <v>3.061949474999999</v>
+        <v>3.017029949999999</v>
       </c>
       <c r="Q43">
-        <v>7.412949475</v>
+        <v>7.368029949999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1210124225218435</v>
+        <v>0.122186904162458</v>
       </c>
       <c r="T43">
-        <v>1.426751862529798</v>
+        <v>1.449031345254438</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.662566434355552</v>
+        <v>2.599171995442325</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09653670441422564</v>
+        <v>0.09661892954056359</v>
       </c>
       <c r="C44">
-        <v>38.23192633607807</v>
+        <v>37.39882376193553</v>
       </c>
       <c r="D44">
-        <v>60.63192633607806</v>
+        <v>60.53382376193554</v>
       </c>
       <c r="E44">
-        <v>-2.130000000000003</v>
+        <v>-1.395</v>
       </c>
       <c r="F44">
-        <v>30.87</v>
+        <v>31.605</v>
       </c>
       <c r="G44">
         <v>8.470000000000001</v>
@@ -4895,28 +4895,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M44">
-        <v>2.219553</v>
+        <v>2.2723995</v>
       </c>
       <c r="N44">
-        <v>3.549446999999999</v>
+        <v>3.496600499999999</v>
       </c>
       <c r="O44">
-        <v>0.5324170499999998</v>
+        <v>0.5244900749999999</v>
       </c>
       <c r="P44">
-        <v>3.01702995</v>
+        <v>2.972110424999999</v>
       </c>
       <c r="Q44">
-        <v>7.368029949999999</v>
+        <v>7.323110424999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.122186904162458</v>
+        <v>0.1234025956851993</v>
       </c>
       <c r="T44">
-        <v>1.449031345254438</v>
+        <v>1.47209256421503</v>
       </c>
       <c r="U44">
         <v>0.07190000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.599171995442325</v>
+        <v>2.538726135083201</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09661892954056359</v>
+        <v>0.09815975466690154</v>
       </c>
       <c r="C45">
-        <v>37.39882376193553</v>
+        <v>34.8824548987872</v>
       </c>
       <c r="D45">
-        <v>60.53382376193554</v>
+        <v>58.75245489878721</v>
       </c>
       <c r="E45">
-        <v>-1.395</v>
+        <v>-0.6599999999999966</v>
       </c>
       <c r="F45">
-        <v>31.605</v>
+        <v>32.34</v>
       </c>
       <c r="G45">
         <v>8.470000000000001</v>
@@ -4977,45 +4977,45 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M45">
-        <v>2.2723995</v>
+        <v>2.451372000000001</v>
       </c>
       <c r="N45">
-        <v>3.496600499999999</v>
+        <v>3.317627999999999</v>
       </c>
       <c r="O45">
-        <v>0.5244900749999999</v>
+        <v>0.4976441999999998</v>
       </c>
       <c r="P45">
-        <v>2.972110424999999</v>
+        <v>2.819983799999999</v>
       </c>
       <c r="Q45">
-        <v>7.323110424999999</v>
+        <v>7.170983799999998</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1234025956851993</v>
+        <v>0.1246617047623242</v>
       </c>
       <c r="T45">
-        <v>1.47209256421503</v>
+        <v>1.495977398138501</v>
       </c>
       <c r="U45">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V45">
         <v>0.15</v>
       </c>
       <c r="W45">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.538726135083201</v>
+        <v>2.353375986998301</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09815975466690154</v>
+        <v>0.0982751297932395</v>
       </c>
       <c r="C46">
-        <v>34.8824548987872</v>
+        <v>34.01827804999576</v>
       </c>
       <c r="D46">
-        <v>58.75245489878721</v>
+        <v>58.62327804999575</v>
       </c>
       <c r="E46">
-        <v>-0.6599999999999966</v>
+        <v>0.07500000000000284</v>
       </c>
       <c r="F46">
-        <v>32.34</v>
+        <v>33.075</v>
       </c>
       <c r="G46">
         <v>8.470000000000001</v>
@@ -5059,28 +5059,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M46">
-        <v>2.451372000000001</v>
+        <v>2.507085</v>
       </c>
       <c r="N46">
-        <v>3.317627999999999</v>
+        <v>3.261914999999999</v>
       </c>
       <c r="O46">
-        <v>0.4976441999999998</v>
+        <v>0.4892872499999998</v>
       </c>
       <c r="P46">
-        <v>2.819983799999999</v>
+        <v>2.772627749999999</v>
       </c>
       <c r="Q46">
-        <v>7.170983799999998</v>
+        <v>7.123627749999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1246617047623242</v>
+        <v>0.1259665996240718</v>
       </c>
       <c r="T46">
-        <v>1.495977398138501</v>
+        <v>1.52073077147737</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.353375986998301</v>
+        <v>2.301078742842783</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0982751297932395</v>
+        <v>0.09839050491957745</v>
       </c>
       <c r="C47">
-        <v>34.01827804999576</v>
+        <v>33.15466798774771</v>
       </c>
       <c r="D47">
-        <v>58.62327804999575</v>
+        <v>58.49466798774772</v>
       </c>
       <c r="E47">
-        <v>0.07500000000000284</v>
+        <v>0.8100000000000023</v>
       </c>
       <c r="F47">
-        <v>33.075</v>
+        <v>33.81</v>
       </c>
       <c r="G47">
         <v>8.470000000000001</v>
@@ -5141,28 +5141,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M47">
-        <v>2.507085</v>
+        <v>2.562798</v>
       </c>
       <c r="N47">
-        <v>3.261914999999999</v>
+        <v>3.206201999999999</v>
       </c>
       <c r="O47">
-        <v>0.4892872499999998</v>
+        <v>0.4809302999999998</v>
       </c>
       <c r="P47">
-        <v>2.772627749999999</v>
+        <v>2.725271699999999</v>
       </c>
       <c r="Q47">
-        <v>7.123627749999999</v>
+        <v>7.076271699999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1259665996240718</v>
+        <v>0.1273198239251434</v>
       </c>
       <c r="T47">
-        <v>1.52073077147737</v>
+        <v>1.546400936421383</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.301078742842783</v>
+        <v>2.251055291911418</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09839050491957745</v>
+        <v>0.0985058800459154</v>
       </c>
       <c r="C48">
-        <v>33.15466798774771</v>
+        <v>32.29162098989276</v>
       </c>
       <c r="D48">
-        <v>58.49466798774772</v>
+        <v>58.36662098989276</v>
       </c>
       <c r="E48">
-        <v>0.8100000000000023</v>
+        <v>1.545000000000002</v>
       </c>
       <c r="F48">
-        <v>33.81</v>
+        <v>34.545</v>
       </c>
       <c r="G48">
         <v>8.470000000000001</v>
@@ -5223,28 +5223,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M48">
-        <v>2.562798</v>
+        <v>2.618511</v>
       </c>
       <c r="N48">
-        <v>3.206201999999999</v>
+        <v>3.150488999999999</v>
       </c>
       <c r="O48">
-        <v>0.4809302999999998</v>
+        <v>0.4725733499999998</v>
       </c>
       <c r="P48">
-        <v>2.725271699999999</v>
+        <v>2.677915649999999</v>
       </c>
       <c r="Q48">
-        <v>7.076271699999999</v>
+        <v>7.028915649999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1273198239251434</v>
+        <v>0.12872411329418</v>
       </c>
       <c r="T48">
-        <v>1.546400936421383</v>
+        <v>1.573039786834981</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.251055291911418</v>
+        <v>2.203160498466494</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0985058800459154</v>
+        <v>0.09862125517225334</v>
       </c>
       <c r="C49">
-        <v>32.29162098989276</v>
+        <v>31.42913336680112</v>
       </c>
       <c r="D49">
-        <v>58.36662098989276</v>
+        <v>58.23913336680112</v>
       </c>
       <c r="E49">
-        <v>1.545000000000002</v>
+        <v>2.280000000000001</v>
       </c>
       <c r="F49">
-        <v>34.545</v>
+        <v>35.28</v>
       </c>
       <c r="G49">
         <v>8.470000000000001</v>
@@ -5305,28 +5305,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M49">
-        <v>2.618511</v>
+        <v>2.674224</v>
       </c>
       <c r="N49">
-        <v>3.150488999999999</v>
+        <v>3.094775999999999</v>
       </c>
       <c r="O49">
-        <v>0.4725733499999998</v>
+        <v>0.4642163999999999</v>
       </c>
       <c r="P49">
-        <v>2.677915649999999</v>
+        <v>2.630559599999999</v>
       </c>
       <c r="Q49">
-        <v>7.028915649999999</v>
+        <v>6.981559599999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.12872411329418</v>
+        <v>0.1301824137927949</v>
       </c>
       <c r="T49">
-        <v>1.573039786834981</v>
+        <v>1.600703208418333</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.203160498466494</v>
+        <v>2.157261321415109</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09862125517225334</v>
+        <v>0.09873663029859128</v>
       </c>
       <c r="C50">
-        <v>31.42913336680112</v>
+        <v>30.56720146100912</v>
       </c>
       <c r="D50">
-        <v>58.23913336680112</v>
+        <v>58.11220146100911</v>
       </c>
       <c r="E50">
-        <v>2.280000000000001</v>
+        <v>3.015000000000001</v>
       </c>
       <c r="F50">
-        <v>35.28</v>
+        <v>36.015</v>
       </c>
       <c r="G50">
         <v>8.470000000000001</v>
@@ -5387,28 +5387,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M50">
-        <v>2.674224</v>
+        <v>2.729937</v>
       </c>
       <c r="N50">
-        <v>3.094775999999999</v>
+        <v>3.039062999999999</v>
       </c>
       <c r="O50">
-        <v>0.4642163999999999</v>
+        <v>0.4558594499999998</v>
       </c>
       <c r="P50">
-        <v>2.630559599999999</v>
+        <v>2.583203549999999</v>
       </c>
       <c r="Q50">
-        <v>6.981559599999999</v>
+        <v>6.934203549999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1301824137927949</v>
+        <v>0.1316979025462574</v>
       </c>
       <c r="T50">
-        <v>1.600703208418333</v>
+        <v>1.629451470063777</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.157261321415109</v>
+        <v>2.11323558016174</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09873663029859128</v>
+        <v>0.09885200542492925</v>
       </c>
       <c r="C51">
-        <v>30.56720146100912</v>
+        <v>29.70582164686941</v>
       </c>
       <c r="D51">
-        <v>58.11220146100911</v>
+        <v>57.9858216468694</v>
       </c>
       <c r="E51">
-        <v>3.015000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="F51">
-        <v>36.015</v>
+        <v>36.75</v>
       </c>
       <c r="G51">
         <v>8.470000000000001</v>
@@ -5469,28 +5469,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M51">
-        <v>2.729937</v>
+        <v>2.78565</v>
       </c>
       <c r="N51">
-        <v>3.039062999999999</v>
+        <v>2.983349999999999</v>
       </c>
       <c r="O51">
-        <v>0.4558594499999998</v>
+        <v>0.4475024999999998</v>
       </c>
       <c r="P51">
-        <v>2.583203549999999</v>
+        <v>2.535847499999999</v>
       </c>
       <c r="Q51">
-        <v>6.934203549999999</v>
+        <v>6.886847499999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1316979025462574</v>
+        <v>0.1332740108498585</v>
       </c>
       <c r="T51">
-        <v>1.629451470063777</v>
+        <v>1.65934966217504</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.11323558016174</v>
+        <v>2.070970868558505</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09885200542492925</v>
+        <v>0.09896738055126719</v>
       </c>
       <c r="C52">
-        <v>29.70582164686941</v>
+        <v>28.84499033020587</v>
       </c>
       <c r="D52">
-        <v>57.9858216468694</v>
+        <v>57.85999033020587</v>
       </c>
       <c r="E52">
-        <v>3.75</v>
+        <v>4.484999999999999</v>
       </c>
       <c r="F52">
-        <v>36.75</v>
+        <v>37.485</v>
       </c>
       <c r="G52">
         <v>8.470000000000001</v>
@@ -5551,28 +5551,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M52">
-        <v>2.78565</v>
+        <v>2.841363</v>
       </c>
       <c r="N52">
-        <v>2.983349999999999</v>
+        <v>2.927636999999999</v>
       </c>
       <c r="O52">
-        <v>0.4475024999999998</v>
+        <v>0.4391455499999998</v>
       </c>
       <c r="P52">
-        <v>2.535847499999999</v>
+        <v>2.488491449999999</v>
       </c>
       <c r="Q52">
-        <v>6.886847499999999</v>
+        <v>6.839491449999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1332740108498585</v>
+        <v>0.1349144501046269</v>
       </c>
       <c r="T52">
-        <v>1.65934966217504</v>
+        <v>1.69046818865819</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.070970868558505</v>
+        <v>2.030363596625985</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09896738055126719</v>
+        <v>0.1053591556776051</v>
       </c>
       <c r="C53">
-        <v>28.84499033020587</v>
+        <v>21.90056639201825</v>
       </c>
       <c r="D53">
-        <v>57.85999033020587</v>
+        <v>51.65056639201825</v>
       </c>
       <c r="E53">
-        <v>4.484999999999999</v>
+        <v>5.219999999999999</v>
       </c>
       <c r="F53">
-        <v>37.485</v>
+        <v>38.22</v>
       </c>
       <c r="G53">
         <v>8.470000000000001</v>
@@ -5633,45 +5633,45 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M53">
-        <v>2.841363</v>
+        <v>3.4398</v>
       </c>
       <c r="N53">
-        <v>2.927636999999999</v>
+        <v>2.329199999999999</v>
       </c>
       <c r="O53">
-        <v>0.4391455499999998</v>
+        <v>0.3493799999999999</v>
       </c>
       <c r="P53">
-        <v>2.488491449999999</v>
+        <v>1.979819999999999</v>
       </c>
       <c r="Q53">
-        <v>6.839491449999999</v>
+        <v>6.330819999999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1349144501046269</v>
+        <v>0.1366232409950107</v>
       </c>
       <c r="T53">
-        <v>1.69046818865819</v>
+        <v>1.722883320411471</v>
       </c>
       <c r="U53">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V53">
         <v>0.15</v>
       </c>
       <c r="W53">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.030363596625985</v>
+        <v>1.677132391418106</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1053591556776051</v>
+        <v>0.1055952308039431</v>
       </c>
       <c r="C54">
-        <v>21.90056639201825</v>
+        <v>20.96164688501938</v>
       </c>
       <c r="D54">
-        <v>51.65056639201825</v>
+        <v>51.44664688501939</v>
       </c>
       <c r="E54">
-        <v>5.219999999999999</v>
+        <v>5.955000000000005</v>
       </c>
       <c r="F54">
-        <v>38.22</v>
+        <v>38.95500000000001</v>
       </c>
       <c r="G54">
         <v>8.470000000000001</v>
@@ -5715,28 +5715,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M54">
-        <v>3.4398</v>
+        <v>3.50595</v>
       </c>
       <c r="N54">
-        <v>2.329199999999999</v>
+        <v>2.263049999999999</v>
       </c>
       <c r="O54">
-        <v>0.3493799999999999</v>
+        <v>0.3394574999999998</v>
       </c>
       <c r="P54">
-        <v>1.979819999999999</v>
+        <v>1.923592499999999</v>
       </c>
       <c r="Q54">
-        <v>6.330819999999999</v>
+        <v>6.274592499999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1366232409950107</v>
+        <v>0.1384047463913683</v>
       </c>
       <c r="T54">
-        <v>1.722883320411471</v>
+        <v>1.756677819473403</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.677132391418106</v>
+        <v>1.645488384032858</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1055952308039431</v>
+        <v>0.1058313059302811</v>
       </c>
       <c r="C55">
-        <v>20.96164688501938</v>
+        <v>20.02433121863775</v>
       </c>
       <c r="D55">
-        <v>51.44664688501939</v>
+        <v>51.24433121863775</v>
       </c>
       <c r="E55">
-        <v>5.955000000000005</v>
+        <v>6.690000000000005</v>
       </c>
       <c r="F55">
-        <v>38.95500000000001</v>
+        <v>39.69</v>
       </c>
       <c r="G55">
         <v>8.470000000000001</v>
@@ -5797,28 +5797,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M55">
-        <v>3.50595</v>
+        <v>3.5721</v>
       </c>
       <c r="N55">
-        <v>2.263049999999999</v>
+        <v>2.196899999999999</v>
       </c>
       <c r="O55">
-        <v>0.3394574999999998</v>
+        <v>0.3295349999999999</v>
       </c>
       <c r="P55">
-        <v>1.923592499999999</v>
+        <v>1.867364999999999</v>
       </c>
       <c r="Q55">
-        <v>6.274592499999999</v>
+        <v>6.218364999999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1384047463913683</v>
+        <v>0.1402637085440893</v>
       </c>
       <c r="T55">
-        <v>1.756677819473403</v>
+        <v>1.791941644581506</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.645488384032858</v>
+        <v>1.615016376921139</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1058313059302811</v>
+        <v>0.106067381056619</v>
       </c>
       <c r="C56">
-        <v>20.02433121863775</v>
+        <v>19.08860054551992</v>
       </c>
       <c r="D56">
-        <v>51.24433121863775</v>
+        <v>51.04360054551992</v>
       </c>
       <c r="E56">
-        <v>6.690000000000005</v>
+        <v>7.425000000000004</v>
       </c>
       <c r="F56">
-        <v>39.69</v>
+        <v>40.425</v>
       </c>
       <c r="G56">
         <v>8.470000000000001</v>
@@ -5879,28 +5879,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M56">
-        <v>3.5721</v>
+        <v>3.63825</v>
       </c>
       <c r="N56">
-        <v>2.196899999999999</v>
+        <v>2.130749999999999</v>
       </c>
       <c r="O56">
-        <v>0.3295349999999999</v>
+        <v>0.3196124999999999</v>
       </c>
       <c r="P56">
-        <v>1.867364999999999</v>
+        <v>1.811137499999999</v>
       </c>
       <c r="Q56">
-        <v>6.218364999999999</v>
+        <v>6.162137499999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1402637085440893</v>
+        <v>0.1422052912369312</v>
       </c>
       <c r="T56">
-        <v>1.791941644581506</v>
+        <v>1.828772750805524</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.615016376921139</v>
+        <v>1.5856524427953</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.106067381056619</v>
+        <v>0.106303456182957</v>
       </c>
       <c r="C57">
-        <v>19.08860054551992</v>
+        <v>18.15443631247034</v>
       </c>
       <c r="D57">
-        <v>51.04360054551992</v>
+        <v>50.84443631247034</v>
       </c>
       <c r="E57">
-        <v>7.425000000000004</v>
+        <v>8.160000000000004</v>
       </c>
       <c r="F57">
-        <v>40.425</v>
+        <v>41.16</v>
       </c>
       <c r="G57">
         <v>8.470000000000001</v>
@@ -5961,28 +5961,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M57">
-        <v>3.63825</v>
+        <v>3.7044</v>
       </c>
       <c r="N57">
-        <v>2.130749999999999</v>
+        <v>2.064599999999999</v>
       </c>
       <c r="O57">
-        <v>0.3196124999999999</v>
+        <v>0.3096899999999999</v>
       </c>
       <c r="P57">
-        <v>1.811137499999999</v>
+        <v>1.754909999999999</v>
       </c>
       <c r="Q57">
-        <v>6.162137499999999</v>
+        <v>6.10591</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1422052912369312</v>
+        <v>0.1442351276885386</v>
       </c>
       <c r="T57">
-        <v>1.828772750805524</v>
+        <v>1.867277998221544</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.5856524427953</v>
+        <v>1.557337220602526</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.106303456182957</v>
+        <v>0.1065395313092949</v>
       </c>
       <c r="C58">
-        <v>18.15443631247034</v>
+        <v>17.22182025473477</v>
       </c>
       <c r="D58">
-        <v>50.84443631247034</v>
+        <v>50.64682025473478</v>
       </c>
       <c r="E58">
-        <v>8.160000000000004</v>
+        <v>8.895000000000003</v>
       </c>
       <c r="F58">
-        <v>41.16</v>
+        <v>41.895</v>
       </c>
       <c r="G58">
         <v>8.470000000000001</v>
@@ -6043,28 +6043,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M58">
-        <v>3.7044</v>
+        <v>3.77055</v>
       </c>
       <c r="N58">
-        <v>2.064599999999999</v>
+        <v>1.998449999999999</v>
       </c>
       <c r="O58">
-        <v>0.3096899999999999</v>
+        <v>0.2997674999999999</v>
       </c>
       <c r="P58">
-        <v>1.754909999999999</v>
+        <v>1.698682499999999</v>
       </c>
       <c r="Q58">
-        <v>6.10591</v>
+        <v>6.049682499999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1442351276885386</v>
+        <v>0.1463593751378952</v>
       </c>
       <c r="T58">
-        <v>1.867277998221544</v>
+        <v>1.907574187377843</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.557337220602526</v>
+        <v>1.530015514977921</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1065395313092949</v>
+        <v>0.1067756064356329</v>
       </c>
       <c r="C59">
-        <v>17.22182025473477</v>
+        <v>16.29073439041666</v>
       </c>
       <c r="D59">
-        <v>50.64682025473478</v>
+        <v>50.45073439041666</v>
       </c>
       <c r="E59">
-        <v>8.895000000000003</v>
+        <v>9.630000000000003</v>
       </c>
       <c r="F59">
-        <v>41.895</v>
+        <v>42.63</v>
       </c>
       <c r="G59">
         <v>8.470000000000001</v>
@@ -6125,28 +6125,28 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M59">
-        <v>3.77055</v>
+        <v>3.8367</v>
       </c>
       <c r="N59">
-        <v>1.998449999999999</v>
+        <v>1.932299999999999</v>
       </c>
       <c r="O59">
-        <v>0.2997674999999999</v>
+        <v>0.2898449999999999</v>
       </c>
       <c r="P59">
-        <v>1.698682499999999</v>
+        <v>1.642454999999999</v>
       </c>
       <c r="Q59">
-        <v>6.049682499999999</v>
+        <v>5.993454999999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1463593751378952</v>
+        <v>0.1485847772276973</v>
       </c>
       <c r="T59">
-        <v>1.907574187377843</v>
+        <v>1.949789242684442</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.530015514977921</v>
+        <v>1.503635937133474</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1067756064356329</v>
+        <v>0.1371076279087846</v>
       </c>
       <c r="C60">
-        <v>16.29073439041669</v>
+        <v>-1.203793744462921</v>
       </c>
       <c r="D60">
-        <v>50.45073439041668</v>
+        <v>33.69120625553708</v>
       </c>
       <c r="E60">
-        <v>9.629999999999995</v>
+        <v>10.36499999999999</v>
       </c>
       <c r="F60">
-        <v>42.63</v>
+        <v>43.36499999999999</v>
       </c>
       <c r="G60">
         <v>8.470000000000001</v>
@@ -6207,45 +6207,45 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M60">
-        <v>3.8367</v>
+        <v>6.365982</v>
       </c>
       <c r="N60">
-        <v>1.9323</v>
+        <v>-0.5969820000000006</v>
       </c>
       <c r="O60">
-        <v>0.289845</v>
+        <v>-0.08954730000000008</v>
       </c>
       <c r="P60">
-        <v>1.642455</v>
+        <v>-0.5074347000000005</v>
       </c>
       <c r="Q60">
-        <v>5.993455</v>
+        <v>3.843565299999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1485847772276973</v>
+        <v>0.151875847064731</v>
       </c>
       <c r="T60">
-        <v>1.949789242684441</v>
+        <v>2.012219621367429</v>
       </c>
       <c r="U60">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.15</v>
+        <v>0.1359334663528737</v>
       </c>
       <c r="W60">
-        <v>0.0765</v>
+        <v>0.1268449671393981</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y60">
-        <v>1.503635937133474</v>
+        <v>0.9062231090191583</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1371076279087846</v>
+        <v>0.1381176279087846</v>
       </c>
       <c r="C61">
-        <v>-1.203793744462921</v>
+        <v>-2.307392018583613</v>
       </c>
       <c r="D61">
-        <v>33.69120625553708</v>
+        <v>33.32260798141639</v>
       </c>
       <c r="E61">
-        <v>10.36499999999999</v>
+        <v>11.1</v>
       </c>
       <c r="F61">
-        <v>43.36499999999999</v>
+        <v>44.1</v>
       </c>
       <c r="G61">
         <v>8.470000000000001</v>
@@ -6289,37 +6289,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M61">
-        <v>6.365982</v>
+        <v>6.473880000000001</v>
       </c>
       <c r="N61">
-        <v>-0.5969820000000006</v>
+        <v>-0.7048800000000019</v>
       </c>
       <c r="O61">
-        <v>-0.08954730000000008</v>
+        <v>-0.1057320000000003</v>
       </c>
       <c r="P61">
-        <v>-0.5074347000000005</v>
+        <v>-0.5991480000000017</v>
       </c>
       <c r="Q61">
-        <v>3.843565299999999</v>
+        <v>3.751851999999998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.151875847064731</v>
+        <v>0.1545277432413493</v>
       </c>
       <c r="T61">
-        <v>2.012219621367429</v>
+        <v>2.062525111901615</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1359334663528737</v>
+        <v>0.1336679085803258</v>
       </c>
       <c r="W61">
-        <v>0.1268449671393981</v>
+        <v>0.1271775510204082</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.9062231090191583</v>
+        <v>0.8911193905355055</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1381176279087846</v>
+        <v>0.1391276279087846</v>
       </c>
       <c r="C62">
-        <v>-2.307392018583613</v>
+        <v>-3.403012285222395</v>
       </c>
       <c r="D62">
-        <v>33.32260798141639</v>
+        <v>32.96198771477761</v>
       </c>
       <c r="E62">
-        <v>11.1</v>
+        <v>11.835</v>
       </c>
       <c r="F62">
-        <v>44.1</v>
+        <v>44.835</v>
       </c>
       <c r="G62">
         <v>8.470000000000001</v>
@@ -6371,37 +6371,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M62">
-        <v>6.473880000000001</v>
+        <v>6.581778000000001</v>
       </c>
       <c r="N62">
-        <v>-0.7048800000000019</v>
+        <v>-0.8127780000000016</v>
       </c>
       <c r="O62">
-        <v>-0.1057320000000003</v>
+        <v>-0.1219167000000002</v>
       </c>
       <c r="P62">
-        <v>-0.5991480000000017</v>
+        <v>-0.6908613000000013</v>
       </c>
       <c r="Q62">
-        <v>3.751851999999998</v>
+        <v>3.660138699999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1545277432413493</v>
+        <v>0.1573156340936916</v>
       </c>
       <c r="T62">
-        <v>2.062525111901615</v>
+        <v>2.115410371181143</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1336679085803258</v>
+        <v>0.1314766313904844</v>
       </c>
       <c r="W62">
-        <v>0.1271775510204082</v>
+        <v>0.1274992305118769</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8911193905355055</v>
+        <v>0.8765108759365628</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1391276279087846</v>
+        <v>0.1401376279087846</v>
       </c>
       <c r="C63">
-        <v>-3.403012285222395</v>
+        <v>-4.490910787441628</v>
       </c>
       <c r="D63">
-        <v>32.96198771477761</v>
+        <v>32.60908921255837</v>
       </c>
       <c r="E63">
-        <v>11.835</v>
+        <v>12.57</v>
       </c>
       <c r="F63">
-        <v>44.835</v>
+        <v>45.57</v>
       </c>
       <c r="G63">
         <v>8.470000000000001</v>
@@ -6453,37 +6453,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M63">
-        <v>6.581778000000001</v>
+        <v>6.689676</v>
       </c>
       <c r="N63">
-        <v>-0.8127780000000016</v>
+        <v>-0.9206760000000012</v>
       </c>
       <c r="O63">
-        <v>-0.1219167000000002</v>
+        <v>-0.1381014000000002</v>
       </c>
       <c r="P63">
-        <v>-0.6908613000000013</v>
+        <v>-0.782574600000001</v>
       </c>
       <c r="Q63">
-        <v>3.660138699999999</v>
+        <v>3.568425399999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1573156340936916</v>
+        <v>0.1602502560435256</v>
       </c>
       <c r="T63">
-        <v>2.115410371181143</v>
+        <v>2.171079065159594</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1314766313904844</v>
+        <v>0.1293560405616057</v>
       </c>
       <c r="W63">
-        <v>0.1274992305118769</v>
+        <v>0.1278105332455563</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8765108759365628</v>
+        <v>0.8623736037440377</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1401376279087846</v>
+        <v>0.1411476279087847</v>
       </c>
       <c r="C64">
-        <v>-4.490910787441628</v>
+        <v>-5.571332910959917</v>
       </c>
       <c r="D64">
-        <v>32.60908921255837</v>
+        <v>32.26366708904008</v>
       </c>
       <c r="E64">
-        <v>12.57</v>
+        <v>13.305</v>
       </c>
       <c r="F64">
-        <v>45.57</v>
+        <v>46.305</v>
       </c>
       <c r="G64">
         <v>8.470000000000001</v>
@@ -6535,37 +6535,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M64">
-        <v>6.689676</v>
+        <v>6.797574000000001</v>
       </c>
       <c r="N64">
-        <v>-0.9206760000000012</v>
+        <v>-1.028574000000002</v>
       </c>
       <c r="O64">
-        <v>-0.1381014000000002</v>
+        <v>-0.1542861000000002</v>
       </c>
       <c r="P64">
-        <v>-0.782574600000001</v>
+        <v>-0.8742879000000014</v>
       </c>
       <c r="Q64">
-        <v>3.568425399999999</v>
+        <v>3.476712099999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1602502560435256</v>
+        <v>0.1633435062068641</v>
       </c>
       <c r="T64">
-        <v>2.171079065159594</v>
+        <v>2.229756877731475</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1293560405616057</v>
+        <v>0.1273027700765008</v>
       </c>
       <c r="W64">
-        <v>0.1278105332455563</v>
+        <v>0.1281119533527697</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8623736037440377</v>
+        <v>0.8486851338433385</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1411476279087847</v>
+        <v>0.1421576279087847</v>
       </c>
       <c r="C65">
-        <v>-5.571332910959917</v>
+        <v>-6.644513753173861</v>
       </c>
       <c r="D65">
-        <v>32.26366708904008</v>
+        <v>31.92548624682614</v>
       </c>
       <c r="E65">
-        <v>13.305</v>
+        <v>14.04</v>
       </c>
       <c r="F65">
-        <v>46.305</v>
+        <v>47.04</v>
       </c>
       <c r="G65">
         <v>8.470000000000001</v>
@@ -6617,37 +6617,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M65">
-        <v>6.797574000000001</v>
+        <v>6.905472</v>
       </c>
       <c r="N65">
-        <v>-1.028574000000002</v>
+        <v>-1.136472000000001</v>
       </c>
       <c r="O65">
-        <v>-0.1542861000000002</v>
+        <v>-0.1704708000000002</v>
       </c>
       <c r="P65">
-        <v>-0.8742879000000014</v>
+        <v>-0.9660012000000011</v>
       </c>
       <c r="Q65">
-        <v>3.476712099999999</v>
+        <v>3.384998799999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1633435062068641</v>
+        <v>0.1666086036014993</v>
       </c>
       <c r="T65">
-        <v>2.229756877731475</v>
+        <v>2.291694568779572</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1273027700765008</v>
+        <v>0.1253136642940555</v>
       </c>
       <c r="W65">
-        <v>0.1281119533527697</v>
+        <v>0.1284039540816327</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8486851338433385</v>
+        <v>0.8354244286270365</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1421576279087847</v>
+        <v>0.1431676279087846</v>
       </c>
       <c r="C66">
-        <v>-6.644513753173861</v>
+        <v>-7.710678656764813</v>
       </c>
       <c r="D66">
-        <v>31.92548624682614</v>
+        <v>31.59432134323518</v>
       </c>
       <c r="E66">
-        <v>14.04</v>
+        <v>14.775</v>
       </c>
       <c r="F66">
-        <v>47.04</v>
+        <v>47.775</v>
       </c>
       <c r="G66">
         <v>8.470000000000001</v>
@@ -6699,37 +6699,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M66">
-        <v>6.905472</v>
+        <v>7.01337</v>
       </c>
       <c r="N66">
-        <v>-1.136472000000001</v>
+        <v>-1.244370000000001</v>
       </c>
       <c r="O66">
-        <v>-0.1704708000000002</v>
+        <v>-0.1866555000000001</v>
       </c>
       <c r="P66">
-        <v>-0.9660012000000011</v>
+        <v>-1.057714500000001</v>
       </c>
       <c r="Q66">
-        <v>3.384998799999999</v>
+        <v>3.293285499999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1666086036014993</v>
+        <v>0.1700602779901135</v>
       </c>
       <c r="T66">
-        <v>2.291694568779572</v>
+        <v>2.357171556458988</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1253136642940555</v>
+        <v>0.1233857617664546</v>
       </c>
       <c r="W66">
-        <v>0.1284039540816327</v>
+        <v>0.1286869701726845</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8354244286270365</v>
+        <v>0.8225717451096974</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1431676279087846</v>
+        <v>0.1441776279087847</v>
       </c>
       <c r="C67">
-        <v>-7.710678656764813</v>
+        <v>-8.770043710435928</v>
       </c>
       <c r="D67">
-        <v>31.59432134323518</v>
+        <v>31.26995628956408</v>
       </c>
       <c r="E67">
-        <v>14.775</v>
+        <v>15.51000000000001</v>
       </c>
       <c r="F67">
-        <v>47.775</v>
+        <v>48.51000000000001</v>
       </c>
       <c r="G67">
         <v>8.470000000000001</v>
@@ -6781,37 +6781,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M67">
-        <v>7.01337</v>
+        <v>7.121268000000001</v>
       </c>
       <c r="N67">
-        <v>-1.244370000000001</v>
+        <v>-1.352268000000002</v>
       </c>
       <c r="O67">
-        <v>-0.1866555000000001</v>
+        <v>-0.2028402000000003</v>
       </c>
       <c r="P67">
-        <v>-1.057714500000001</v>
+        <v>-1.149427800000002</v>
       </c>
       <c r="Q67">
-        <v>3.293285499999999</v>
+        <v>3.201572199999998</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1700602779901135</v>
+        <v>0.1737149920486463</v>
       </c>
       <c r="T67">
-        <v>2.357171556458988</v>
+        <v>2.426500131648959</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.1233857617664546</v>
+        <v>0.1215162805275689</v>
       </c>
       <c r="W67">
-        <v>0.1286869701726845</v>
+        <v>0.1289614100185529</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8225717451096974</v>
+        <v>0.8101085368504595</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1441776279087847</v>
+        <v>0.1823874296907596</v>
       </c>
       <c r="C68">
-        <v>-8.770043710435928</v>
+        <v>-18.25269226243218</v>
       </c>
       <c r="D68">
-        <v>31.26995628956408</v>
+        <v>22.52230773756783</v>
       </c>
       <c r="E68">
-        <v>15.51000000000001</v>
+        <v>16.245</v>
       </c>
       <c r="F68">
-        <v>48.51000000000001</v>
+        <v>49.245</v>
       </c>
       <c r="G68">
         <v>8.470000000000001</v>
@@ -6863,45 +6863,45 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M68">
-        <v>7.121268000000001</v>
+        <v>9.888396000000002</v>
       </c>
       <c r="N68">
-        <v>-1.352268000000002</v>
+        <v>-4.119396000000003</v>
       </c>
       <c r="O68">
-        <v>-0.2028402000000003</v>
+        <v>-0.6179094000000004</v>
       </c>
       <c r="P68">
-        <v>-1.149427800000002</v>
+        <v>-3.501486600000002</v>
       </c>
       <c r="Q68">
-        <v>3.201572199999998</v>
+        <v>0.8495133999999975</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1737149920486463</v>
+        <v>0.1806815123591353</v>
       </c>
       <c r="T68">
-        <v>2.426500131648959</v>
+        <v>2.558652447650417</v>
       </c>
       <c r="U68">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1215162805275689</v>
+        <v>0.08751166518816597</v>
       </c>
       <c r="W68">
-        <v>0.1289614100185529</v>
+        <v>0.1832276576302163</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.8101085368504595</v>
+        <v>0.5834111012544398</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1823874296907596</v>
+        <v>0.1839374296907596</v>
       </c>
       <c r="C69">
-        <v>-18.25269226243218</v>
+        <v>-19.24040853977555</v>
       </c>
       <c r="D69">
-        <v>22.52230773756783</v>
+        <v>22.26959146022445</v>
       </c>
       <c r="E69">
-        <v>16.245</v>
+        <v>16.98</v>
       </c>
       <c r="F69">
-        <v>49.245</v>
+        <v>49.98</v>
       </c>
       <c r="G69">
         <v>8.470000000000001</v>
@@ -6945,37 +6945,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M69">
-        <v>9.888396000000002</v>
+        <v>10.035984</v>
       </c>
       <c r="N69">
-        <v>-4.119396000000003</v>
+        <v>-4.266984000000002</v>
       </c>
       <c r="O69">
-        <v>-0.6179094000000004</v>
+        <v>-0.6400476000000003</v>
       </c>
       <c r="P69">
-        <v>-3.501486600000002</v>
+        <v>-3.626936400000001</v>
       </c>
       <c r="Q69">
-        <v>0.8495133999999975</v>
+        <v>0.7240635999999987</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1806815123591353</v>
+        <v>0.1848965596203583</v>
       </c>
       <c r="T69">
-        <v>2.558652447650417</v>
+        <v>2.638610336639493</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.08751166518816597</v>
+        <v>0.08622472893539884</v>
       </c>
       <c r="W69">
-        <v>0.1832276576302163</v>
+        <v>0.1834860744297719</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5834111012544398</v>
+        <v>0.5748315262359922</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1839374296907596</v>
+        <v>0.1854874296907596</v>
       </c>
       <c r="C70">
-        <v>-19.24040853977555</v>
+        <v>-20.22251643516574</v>
       </c>
       <c r="D70">
-        <v>22.26959146022445</v>
+        <v>22.02248356483427</v>
       </c>
       <c r="E70">
-        <v>16.98</v>
+        <v>17.715</v>
       </c>
       <c r="F70">
-        <v>49.98</v>
+        <v>50.715</v>
       </c>
       <c r="G70">
         <v>8.470000000000001</v>
@@ -7027,37 +7027,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M70">
-        <v>10.035984</v>
+        <v>10.183572</v>
       </c>
       <c r="N70">
-        <v>-4.266984000000002</v>
+        <v>-4.414572000000002</v>
       </c>
       <c r="O70">
-        <v>-0.6400476000000003</v>
+        <v>-0.6621858000000004</v>
       </c>
       <c r="P70">
-        <v>-3.626936400000001</v>
+        <v>-3.752386200000002</v>
       </c>
       <c r="Q70">
-        <v>0.7240635999999987</v>
+        <v>0.5986137999999981</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1848965596203583</v>
+        <v>0.1893835454145634</v>
       </c>
       <c r="T70">
-        <v>2.638610336639493</v>
+        <v>2.723726799111735</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.08622472893539884</v>
+        <v>0.08497509518271189</v>
       </c>
       <c r="W70">
-        <v>0.1834860744297719</v>
+        <v>0.1837370008873115</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5748315262359922</v>
+        <v>0.5665006345514126</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1854874296907596</v>
+        <v>0.1870374296907596</v>
       </c>
       <c r="C71">
-        <v>-20.22251643516574</v>
+        <v>-21.19920059495419</v>
       </c>
       <c r="D71">
-        <v>22.02248356483427</v>
+        <v>21.78079940504581</v>
       </c>
       <c r="E71">
-        <v>17.715</v>
+        <v>18.45</v>
       </c>
       <c r="F71">
-        <v>50.715</v>
+        <v>51.45</v>
       </c>
       <c r="G71">
         <v>8.470000000000001</v>
@@ -7109,37 +7109,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M71">
-        <v>10.183572</v>
+        <v>10.33116</v>
       </c>
       <c r="N71">
-        <v>-4.414572000000002</v>
+        <v>-4.562160000000001</v>
       </c>
       <c r="O71">
-        <v>-0.6621858000000004</v>
+        <v>-0.6843240000000002</v>
       </c>
       <c r="P71">
-        <v>-3.752386200000002</v>
+        <v>-3.877836000000001</v>
       </c>
       <c r="Q71">
-        <v>0.5986137999999981</v>
+        <v>0.4731639999999988</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1893835454145634</v>
+        <v>0.1941696635950489</v>
       </c>
       <c r="T71">
-        <v>2.723726799111735</v>
+        <v>2.814517692415459</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.08497509518271189</v>
+        <v>0.0837611652515303</v>
       </c>
       <c r="W71">
-        <v>0.1837370008873115</v>
+        <v>0.1839807580174927</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5665006345514126</v>
+        <v>0.5584077683435353</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1870374296907596</v>
+        <v>0.1885874296907596</v>
       </c>
       <c r="C72">
-        <v>-21.19920059495419</v>
+        <v>-22.17063764792823</v>
       </c>
       <c r="D72">
-        <v>21.78079940504581</v>
+        <v>21.54436235207177</v>
       </c>
       <c r="E72">
-        <v>18.45</v>
+        <v>19.185</v>
       </c>
       <c r="F72">
-        <v>51.45</v>
+        <v>52.185</v>
       </c>
       <c r="G72">
         <v>8.470000000000001</v>
@@ -7191,37 +7191,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M72">
-        <v>10.33116</v>
+        <v>10.478748</v>
       </c>
       <c r="N72">
-        <v>-4.562160000000001</v>
+        <v>-4.709748000000002</v>
       </c>
       <c r="O72">
-        <v>-0.6843240000000002</v>
+        <v>-0.7064622000000003</v>
       </c>
       <c r="P72">
-        <v>-3.877836000000001</v>
+        <v>-4.003285800000002</v>
       </c>
       <c r="Q72">
-        <v>0.4731639999999988</v>
+        <v>0.3477141999999978</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1941696635950489</v>
+        <v>0.1992858588914299</v>
       </c>
       <c r="T72">
-        <v>2.814517692415459</v>
+        <v>2.911570026636682</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.0837611652515303</v>
+        <v>0.08258143052967776</v>
       </c>
       <c r="W72">
-        <v>0.1839807580174927</v>
+        <v>0.1842176487496407</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5584077683435353</v>
+        <v>0.5505428701978518</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1885874296907595</v>
+        <v>0.1901374296907595</v>
       </c>
       <c r="C73">
-        <v>-22.17063764792822</v>
+        <v>-23.13699663580307</v>
       </c>
       <c r="D73">
-        <v>21.54436235207178</v>
+        <v>21.31300336419693</v>
       </c>
       <c r="E73">
-        <v>19.185</v>
+        <v>19.91999999999999</v>
       </c>
       <c r="F73">
-        <v>52.185</v>
+        <v>52.91999999999999</v>
       </c>
       <c r="G73">
         <v>8.470000000000001</v>
@@ -7273,37 +7273,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M73">
-        <v>10.478748</v>
+        <v>10.626336</v>
       </c>
       <c r="N73">
-        <v>-4.709748</v>
+        <v>-4.857335999999999</v>
       </c>
       <c r="O73">
-        <v>-0.7064622</v>
+        <v>-0.7286003999999998</v>
       </c>
       <c r="P73">
-        <v>-4.0032858</v>
+        <v>-4.1287356</v>
       </c>
       <c r="Q73">
-        <v>0.3477141999999995</v>
+        <v>0.2222644000000003</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1992858588914298</v>
+        <v>0.2047674967089809</v>
       </c>
       <c r="T73">
-        <v>2.911570026636681</v>
+        <v>3.015554670445134</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.08258143052967777</v>
+        <v>0.08143446621676559</v>
       </c>
       <c r="W73">
-        <v>0.1842176487496407</v>
+        <v>0.1844479591836735</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5505428701978519</v>
+        <v>0.542896441445104</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1901374296907595</v>
+        <v>0.1916874296907596</v>
       </c>
       <c r="C74">
-        <v>-23.13699663580307</v>
+        <v>-24.09843941627108</v>
       </c>
       <c r="D74">
-        <v>21.31300336419693</v>
+        <v>21.08656058372893</v>
       </c>
       <c r="E74">
-        <v>19.91999999999999</v>
+        <v>20.655</v>
       </c>
       <c r="F74">
-        <v>52.91999999999999</v>
+        <v>53.655</v>
       </c>
       <c r="G74">
         <v>8.470000000000001</v>
@@ -7355,37 +7355,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M74">
-        <v>10.626336</v>
+        <v>10.773924</v>
       </c>
       <c r="N74">
-        <v>-4.857335999999999</v>
+        <v>-5.004924000000002</v>
       </c>
       <c r="O74">
-        <v>-0.7286003999999998</v>
+        <v>-0.7507386000000003</v>
       </c>
       <c r="P74">
-        <v>-4.1287356</v>
+        <v>-4.254185400000002</v>
       </c>
       <c r="Q74">
-        <v>0.2222644000000003</v>
+        <v>0.09681459999999831</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2047674967089809</v>
+        <v>0.2106551817722765</v>
       </c>
       <c r="T74">
-        <v>3.015554670445134</v>
+        <v>3.12724188046162</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.08143446621676559</v>
+        <v>0.0803189255836592</v>
       </c>
       <c r="W74">
-        <v>0.1844479591836735</v>
+        <v>0.1846719597428012</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.542896441445104</v>
+        <v>0.5354595038910612</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1916874296907596</v>
+        <v>0.1932374296907596</v>
       </c>
       <c r="C75">
-        <v>-24.09843941627108</v>
+        <v>-25.05512104062748</v>
       </c>
       <c r="D75">
-        <v>21.08656058372893</v>
+        <v>20.86487895937252</v>
       </c>
       <c r="E75">
-        <v>20.655</v>
+        <v>21.39</v>
       </c>
       <c r="F75">
-        <v>53.655</v>
+        <v>54.39</v>
       </c>
       <c r="G75">
         <v>8.470000000000001</v>
@@ -7437,37 +7437,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M75">
-        <v>10.773924</v>
+        <v>10.921512</v>
       </c>
       <c r="N75">
-        <v>-5.004924000000002</v>
+        <v>-5.152512000000001</v>
       </c>
       <c r="O75">
-        <v>-0.7507386000000003</v>
+        <v>-0.7728768</v>
       </c>
       <c r="P75">
-        <v>-4.254185400000002</v>
+        <v>-4.379635200000001</v>
       </c>
       <c r="Q75">
-        <v>0.09681459999999831</v>
+        <v>-0.02863520000000097</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2106551817722765</v>
+        <v>0.2169957656865948</v>
       </c>
       <c r="T75">
-        <v>3.12724188046162</v>
+        <v>3.247520414325529</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.0803189255836592</v>
+        <v>0.07923353469739353</v>
       </c>
       <c r="W75">
-        <v>0.1846719597428012</v>
+        <v>0.1848899062327634</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5354595038910612</v>
+        <v>0.5282235646492903</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1932374296907596</v>
+        <v>0.1947874296907595</v>
       </c>
       <c r="C76">
-        <v>-25.05512104062748</v>
+        <v>-26.00719010782431</v>
       </c>
       <c r="D76">
-        <v>20.86487895937252</v>
+        <v>20.64780989217569</v>
       </c>
       <c r="E76">
-        <v>21.39</v>
+        <v>22.125</v>
       </c>
       <c r="F76">
-        <v>54.39</v>
+        <v>55.125</v>
       </c>
       <c r="G76">
         <v>8.470000000000001</v>
@@ -7519,37 +7519,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M76">
-        <v>10.921512</v>
+        <v>11.0691</v>
       </c>
       <c r="N76">
-        <v>-5.152512000000001</v>
+        <v>-5.300100000000001</v>
       </c>
       <c r="O76">
-        <v>-0.7728768</v>
+        <v>-0.7950150000000001</v>
       </c>
       <c r="P76">
-        <v>-4.379635200000001</v>
+        <v>-4.505085000000001</v>
       </c>
       <c r="Q76">
-        <v>-0.02863520000000097</v>
+        <v>-0.1540850000000011</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2169957656865948</v>
+        <v>0.2238435963140586</v>
       </c>
       <c r="T76">
-        <v>3.247520414325529</v>
+        <v>3.377421230898551</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.07923353469739353</v>
+        <v>0.07817708756809495</v>
       </c>
       <c r="W76">
-        <v>0.1848899062327634</v>
+        <v>0.1851020408163265</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5282235646492903</v>
+        <v>0.5211805837872997</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1947874296907595</v>
+        <v>0.1963374296907596</v>
       </c>
       <c r="C77">
-        <v>-26.00719010782431</v>
+        <v>-26.95478909665132</v>
       </c>
       <c r="D77">
-        <v>20.64780989217569</v>
+        <v>20.43521090334868</v>
       </c>
       <c r="E77">
-        <v>22.125</v>
+        <v>22.86</v>
       </c>
       <c r="F77">
-        <v>55.125</v>
+        <v>55.86</v>
       </c>
       <c r="G77">
         <v>8.470000000000001</v>
@@ -7601,37 +7601,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M77">
-        <v>11.0691</v>
+        <v>11.216688</v>
       </c>
       <c r="N77">
-        <v>-5.300100000000001</v>
+        <v>-5.447688</v>
       </c>
       <c r="O77">
-        <v>-0.7950150000000001</v>
+        <v>-0.8171532</v>
       </c>
       <c r="P77">
-        <v>-4.505085000000001</v>
+        <v>-4.6305348</v>
       </c>
       <c r="Q77">
-        <v>-0.1540850000000011</v>
+        <v>-0.2795348000000004</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2238435963140586</v>
+        <v>0.2312620794938111</v>
       </c>
       <c r="T77">
-        <v>3.377421230898551</v>
+        <v>3.518147115519323</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.07817708756809495</v>
+        <v>0.07714844167904107</v>
       </c>
       <c r="W77">
-        <v>0.1851020408163265</v>
+        <v>0.1853085929108486</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5211805837872997</v>
+        <v>0.5143229445269406</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1963374296907596</v>
+        <v>0.1978874296907595</v>
       </c>
       <c r="C78">
-        <v>-26.95478909665132</v>
+        <v>-27.89805467760429</v>
       </c>
       <c r="D78">
-        <v>20.43521090334868</v>
+        <v>20.22694532239571</v>
       </c>
       <c r="E78">
-        <v>22.86</v>
+        <v>23.595</v>
       </c>
       <c r="F78">
-        <v>55.86</v>
+        <v>56.595</v>
       </c>
       <c r="G78">
         <v>8.470000000000001</v>
@@ -7683,37 +7683,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M78">
-        <v>11.216688</v>
+        <v>11.364276</v>
       </c>
       <c r="N78">
-        <v>-5.447688</v>
+        <v>-5.595276000000001</v>
       </c>
       <c r="O78">
-        <v>-0.8171532</v>
+        <v>-0.8392914000000001</v>
       </c>
       <c r="P78">
-        <v>-4.6305348</v>
+        <v>-4.755984600000001</v>
       </c>
       <c r="Q78">
-        <v>-0.2795348000000004</v>
+        <v>-0.4049846000000006</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2312620794938111</v>
+        <v>0.239325648167455</v>
       </c>
       <c r="T78">
-        <v>3.518147115519323</v>
+        <v>3.671110033585381</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.07714844167904107</v>
+        <v>0.07614651386502756</v>
       </c>
       <c r="W78">
-        <v>0.1853085929108486</v>
+        <v>0.1855097800159025</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5143229445269406</v>
+        <v>0.5076434257668503</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1978874296907595</v>
+        <v>0.1994374296907595</v>
       </c>
       <c r="C79">
-        <v>-27.89805467760429</v>
+        <v>-28.83711800587539</v>
       </c>
       <c r="D79">
-        <v>20.22694532239571</v>
+        <v>20.02288199412461</v>
       </c>
       <c r="E79">
-        <v>23.595</v>
+        <v>24.33000000000001</v>
       </c>
       <c r="F79">
-        <v>56.595</v>
+        <v>57.33000000000001</v>
       </c>
       <c r="G79">
         <v>8.470000000000001</v>
@@ -7765,37 +7765,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M79">
-        <v>11.364276</v>
+        <v>11.511864</v>
       </c>
       <c r="N79">
-        <v>-5.595276000000001</v>
+        <v>-5.742864000000002</v>
       </c>
       <c r="O79">
-        <v>-0.8392914000000001</v>
+        <v>-0.8614296000000002</v>
       </c>
       <c r="P79">
-        <v>-4.755984600000001</v>
+        <v>-4.881434400000002</v>
       </c>
       <c r="Q79">
-        <v>-0.4049846000000006</v>
+        <v>-0.5304344000000016</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.239325648167455</v>
+        <v>0.248122268538703</v>
       </c>
       <c r="T79">
-        <v>3.671110033585381</v>
+        <v>3.837978671475625</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.07614651386502756</v>
+        <v>0.0751702765077836</v>
       </c>
       <c r="W79">
-        <v>0.1855097800159025</v>
+        <v>0.1857058084772371</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5076434257668503</v>
+        <v>0.5011351767185575</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1994374296907595</v>
+        <v>0.2290489320276259</v>
       </c>
       <c r="C80">
-        <v>-28.83711800587539</v>
+        <v>-32.80764909683113</v>
       </c>
       <c r="D80">
-        <v>20.02288199412461</v>
+        <v>16.78735090316887</v>
       </c>
       <c r="E80">
-        <v>24.33000000000001</v>
+        <v>25.065</v>
       </c>
       <c r="F80">
-        <v>57.33000000000001</v>
+        <v>58.065</v>
       </c>
       <c r="G80">
         <v>8.470000000000001</v>
@@ -7847,45 +7847,45 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M80">
-        <v>11.511864</v>
+        <v>13.691727</v>
       </c>
       <c r="N80">
-        <v>-5.742864000000002</v>
+        <v>-7.922727000000003</v>
       </c>
       <c r="O80">
-        <v>-0.8614296000000002</v>
+        <v>-1.18840905</v>
       </c>
       <c r="P80">
-        <v>-4.881434400000002</v>
+        <v>-6.734317950000002</v>
       </c>
       <c r="Q80">
-        <v>-0.5304344000000016</v>
+        <v>-2.383317950000002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.248122268538703</v>
+        <v>0.2597161972161002</v>
       </c>
       <c r="T80">
-        <v>3.837978671475625</v>
+        <v>4.057911214264153</v>
       </c>
       <c r="U80">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0751702765077836</v>
+        <v>0.06320239952198869</v>
       </c>
       <c r="W80">
-        <v>0.1857058084772371</v>
+        <v>0.2208968741927151</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.5011351767185575</v>
+        <v>0.4213493301465914</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2290489320276259</v>
+        <v>0.230948932027626</v>
       </c>
       <c r="C81">
-        <v>-32.80764909683113</v>
+        <v>-33.71492104226835</v>
       </c>
       <c r="D81">
-        <v>16.78735090316887</v>
+        <v>16.61507895773165</v>
       </c>
       <c r="E81">
-        <v>25.065</v>
+        <v>25.8</v>
       </c>
       <c r="F81">
-        <v>58.065</v>
+        <v>58.8</v>
       </c>
       <c r="G81">
         <v>8.470000000000001</v>
@@ -7929,37 +7929,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M81">
-        <v>13.691727</v>
+        <v>13.86504</v>
       </c>
       <c r="N81">
-        <v>-7.922727000000003</v>
+        <v>-8.096040000000002</v>
       </c>
       <c r="O81">
-        <v>-1.18840905</v>
+        <v>-1.214406</v>
       </c>
       <c r="P81">
-        <v>-6.734317950000002</v>
+        <v>-6.881634000000002</v>
       </c>
       <c r="Q81">
-        <v>-2.383317950000002</v>
+        <v>-2.530634000000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2597161972161002</v>
+        <v>0.2704120070769052</v>
       </c>
       <c r="T81">
-        <v>4.057911214264153</v>
+        <v>4.260806774977361</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06320239952198869</v>
+        <v>0.06241236952796383</v>
       </c>
       <c r="W81">
-        <v>0.2208968741927151</v>
+        <v>0.2210831632653061</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4213493301465914</v>
+        <v>0.416082463519759</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.230948932027626</v>
+        <v>0.2328489320276259</v>
       </c>
       <c r="C82">
-        <v>-33.71492104226835</v>
+        <v>-34.61869319016294</v>
       </c>
       <c r="D82">
-        <v>16.61507895773165</v>
+        <v>16.44630680983706</v>
       </c>
       <c r="E82">
-        <v>25.8</v>
+        <v>26.535</v>
       </c>
       <c r="F82">
-        <v>58.8</v>
+        <v>59.535</v>
       </c>
       <c r="G82">
         <v>8.470000000000001</v>
@@ -8011,37 +8011,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M82">
-        <v>13.86504</v>
+        <v>14.038353</v>
       </c>
       <c r="N82">
-        <v>-8.096040000000002</v>
+        <v>-8.269353000000002</v>
       </c>
       <c r="O82">
-        <v>-1.214406</v>
+        <v>-1.24040295</v>
       </c>
       <c r="P82">
-        <v>-6.881634000000002</v>
+        <v>-7.028950050000002</v>
       </c>
       <c r="Q82">
-        <v>-2.530634000000002</v>
+        <v>-2.677950050000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2704120070769052</v>
+        <v>0.2822336916599003</v>
       </c>
       <c r="T82">
-        <v>4.260806774977361</v>
+        <v>4.485059763134064</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06241236952796383</v>
+        <v>0.0616418464473717</v>
       </c>
       <c r="W82">
-        <v>0.2210831632653061</v>
+        <v>0.2212648526077098</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.416082463519759</v>
+        <v>0.4109456429824779</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2328489320276259</v>
+        <v>0.2347489320276259</v>
       </c>
       <c r="C83">
-        <v>-34.61869319016294</v>
+        <v>-35.51907111849184</v>
       </c>
       <c r="D83">
-        <v>16.44630680983706</v>
+        <v>16.28092888150816</v>
       </c>
       <c r="E83">
-        <v>26.535</v>
+        <v>27.27</v>
       </c>
       <c r="F83">
-        <v>59.535</v>
+        <v>60.27</v>
       </c>
       <c r="G83">
         <v>8.470000000000001</v>
@@ -8093,37 +8093,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M83">
-        <v>14.038353</v>
+        <v>14.211666</v>
       </c>
       <c r="N83">
-        <v>-8.269353000000002</v>
+        <v>-8.442666000000003</v>
       </c>
       <c r="O83">
-        <v>-1.24040295</v>
+        <v>-1.2663999</v>
       </c>
       <c r="P83">
-        <v>-7.028950050000002</v>
+        <v>-7.176266100000002</v>
       </c>
       <c r="Q83">
-        <v>-2.677950050000002</v>
+        <v>-2.825266100000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2822336916599003</v>
+        <v>0.2953688967521169</v>
       </c>
       <c r="T83">
-        <v>4.485059763134064</v>
+        <v>4.734229749974846</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.0616418464473717</v>
+        <v>0.06089011661264765</v>
       </c>
       <c r="W83">
-        <v>0.2212648526077098</v>
+        <v>0.2214421105027377</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4109456429824779</v>
+        <v>0.4059341107509843</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2347489320276259</v>
+        <v>0.2366489320276259</v>
       </c>
       <c r="C84">
-        <v>-35.51907111849184</v>
+        <v>-36.41615620089821</v>
       </c>
       <c r="D84">
-        <v>16.28092888150816</v>
+        <v>16.11884379910179</v>
       </c>
       <c r="E84">
-        <v>27.27</v>
+        <v>28.005</v>
       </c>
       <c r="F84">
-        <v>60.27</v>
+        <v>61.005</v>
       </c>
       <c r="G84">
         <v>8.470000000000001</v>
@@ -8175,37 +8175,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M84">
-        <v>14.211666</v>
+        <v>14.384979</v>
       </c>
       <c r="N84">
-        <v>-8.442666000000003</v>
+        <v>-8.615979000000003</v>
       </c>
       <c r="O84">
-        <v>-1.2663999</v>
+        <v>-1.29239685</v>
       </c>
       <c r="P84">
-        <v>-7.176266100000002</v>
+        <v>-7.323582150000003</v>
       </c>
       <c r="Q84">
-        <v>-2.825266100000002</v>
+        <v>-2.972582150000003</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2953688967521169</v>
+        <v>0.3100494200904768</v>
       </c>
       <c r="T84">
-        <v>4.734229749974846</v>
+        <v>5.012713852914543</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06089011661264765</v>
+        <v>0.06015650074984466</v>
       </c>
       <c r="W84">
-        <v>0.2214421105027377</v>
+        <v>0.2216150971231866</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4059341107509843</v>
+        <v>0.4010433383322978</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2366489320276259</v>
+        <v>0.238548932027626</v>
       </c>
       <c r="C85">
-        <v>-36.41615620089821</v>
+        <v>-37.31004581390996</v>
       </c>
       <c r="D85">
-        <v>16.11884379910179</v>
+        <v>15.95995418609005</v>
       </c>
       <c r="E85">
-        <v>28.005</v>
+        <v>28.74000000000001</v>
       </c>
       <c r="F85">
-        <v>61.005</v>
+        <v>61.74000000000001</v>
       </c>
       <c r="G85">
         <v>8.470000000000001</v>
@@ -8257,37 +8257,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M85">
-        <v>14.384979</v>
+        <v>14.558292</v>
       </c>
       <c r="N85">
-        <v>-8.615979000000003</v>
+        <v>-8.789292000000003</v>
       </c>
       <c r="O85">
-        <v>-1.29239685</v>
+        <v>-1.3183938</v>
       </c>
       <c r="P85">
-        <v>-7.323582150000003</v>
+        <v>-7.470898200000002</v>
       </c>
       <c r="Q85">
-        <v>-2.972582150000003</v>
+        <v>-3.119898200000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3100494200904768</v>
+        <v>0.3265650088461317</v>
       </c>
       <c r="T85">
-        <v>5.012713852914543</v>
+        <v>5.326008468721704</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06015650074984466</v>
+        <v>0.05944035193139412</v>
       </c>
       <c r="W85">
-        <v>0.2216150971231866</v>
+        <v>0.2217839650145773</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4010433383322978</v>
+        <v>0.3962690128759609</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2385489320276259</v>
+        <v>0.2404489320276259</v>
       </c>
       <c r="C86">
-        <v>-37.31004581390995</v>
+        <v>-38.2008335320222</v>
       </c>
       <c r="D86">
-        <v>15.95995418609004</v>
+        <v>15.8041664679778</v>
       </c>
       <c r="E86">
-        <v>28.73999999999999</v>
+        <v>29.475</v>
       </c>
       <c r="F86">
-        <v>61.73999999999999</v>
+        <v>62.475</v>
       </c>
       <c r="G86">
         <v>8.470000000000001</v>
@@ -8339,37 +8339,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M86">
-        <v>14.558292</v>
+        <v>14.731605</v>
       </c>
       <c r="N86">
-        <v>-8.789292</v>
+        <v>-8.962605</v>
       </c>
       <c r="O86">
-        <v>-1.3183938</v>
+        <v>-1.34439075</v>
       </c>
       <c r="P86">
-        <v>-7.4708982</v>
+        <v>-7.61821425</v>
       </c>
       <c r="Q86">
-        <v>-3.1198982</v>
+        <v>-3.26721425</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3265650088461314</v>
+        <v>0.3452826761025402</v>
       </c>
       <c r="T86">
-        <v>5.326008468721699</v>
+        <v>5.681075699969813</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05944035193139414</v>
+        <v>0.05874105367337774</v>
       </c>
       <c r="W86">
-        <v>0.2217839650145773</v>
+        <v>0.2219488595438175</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3962690128759611</v>
+        <v>0.3916070244891849</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2404489320276259</v>
+        <v>0.2423489320276259</v>
       </c>
       <c r="C87">
-        <v>-38.2008335320222</v>
+        <v>-39.08860931146495</v>
       </c>
       <c r="D87">
-        <v>15.8041664679778</v>
+        <v>15.65139068853505</v>
       </c>
       <c r="E87">
-        <v>29.475</v>
+        <v>30.21</v>
       </c>
       <c r="F87">
-        <v>62.475</v>
+        <v>63.21</v>
       </c>
       <c r="G87">
         <v>8.470000000000001</v>
@@ -8421,37 +8421,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M87">
-        <v>14.731605</v>
+        <v>14.904918</v>
       </c>
       <c r="N87">
-        <v>-8.962605</v>
+        <v>-9.135918</v>
       </c>
       <c r="O87">
-        <v>-1.34439075</v>
+        <v>-1.3703877</v>
       </c>
       <c r="P87">
-        <v>-7.61821425</v>
+        <v>-7.7655303</v>
       </c>
       <c r="Q87">
-        <v>-3.26721425</v>
+        <v>-3.4145303</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3452826761025402</v>
+        <v>0.3666742958241502</v>
       </c>
       <c r="T87">
-        <v>5.681075699969813</v>
+        <v>6.086866821396228</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05874105367337774</v>
+        <v>0.05805801816554776</v>
       </c>
       <c r="W87">
-        <v>0.2219488595438175</v>
+        <v>0.2221099193165638</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3916070244891849</v>
+        <v>0.3870534544369851</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2423489320276259</v>
+        <v>0.2442489320276259</v>
       </c>
       <c r="C88">
-        <v>-39.08860931146495</v>
+        <v>-39.97345966341381</v>
       </c>
       <c r="D88">
-        <v>15.65139068853505</v>
+        <v>15.5015403365862</v>
       </c>
       <c r="E88">
-        <v>30.21</v>
+        <v>30.945</v>
       </c>
       <c r="F88">
-        <v>63.21</v>
+        <v>63.945</v>
       </c>
       <c r="G88">
         <v>8.470000000000001</v>
@@ -8503,37 +8503,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M88">
-        <v>14.904918</v>
+        <v>15.078231</v>
       </c>
       <c r="N88">
-        <v>-9.135918</v>
+        <v>-9.309231</v>
       </c>
       <c r="O88">
-        <v>-1.3703877</v>
+        <v>-1.39638465</v>
       </c>
       <c r="P88">
-        <v>-7.7655303</v>
+        <v>-7.912846350000001</v>
       </c>
       <c r="Q88">
-        <v>-3.4145303</v>
+        <v>-3.561846350000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3666742958241502</v>
+        <v>0.3913569339644695</v>
       </c>
       <c r="T88">
-        <v>6.086866821396228</v>
+        <v>6.555087346119015</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05805801816554776</v>
+        <v>0.05739068462341503</v>
       </c>
       <c r="W88">
-        <v>0.2221099193165638</v>
+        <v>0.2222672765657988</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3870534544369851</v>
+        <v>0.3826045641561002</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2442489320276259</v>
+        <v>0.2461489320276259</v>
       </c>
       <c r="C89">
-        <v>-39.97345966341381</v>
+        <v>-40.85546781734524</v>
       </c>
       <c r="D89">
-        <v>15.5015403365862</v>
+        <v>15.35453218265477</v>
       </c>
       <c r="E89">
-        <v>30.945</v>
+        <v>31.68000000000001</v>
       </c>
       <c r="F89">
-        <v>63.945</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="G89">
         <v>8.470000000000001</v>
@@ -8585,37 +8585,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M89">
-        <v>15.078231</v>
+        <v>15.251544</v>
       </c>
       <c r="N89">
-        <v>-9.309231</v>
+        <v>-9.482544000000004</v>
       </c>
       <c r="O89">
-        <v>-1.39638465</v>
+        <v>-1.422381600000001</v>
       </c>
       <c r="P89">
-        <v>-7.912846350000001</v>
+        <v>-8.060162400000003</v>
       </c>
       <c r="Q89">
-        <v>-3.561846350000001</v>
+        <v>-3.709162400000003</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3913569339644695</v>
+        <v>0.4201533451281753</v>
       </c>
       <c r="T89">
-        <v>6.555087346119015</v>
+        <v>7.101344624962266</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05739068462341503</v>
+        <v>0.0567385177526944</v>
       </c>
       <c r="W89">
-        <v>0.2222672765657988</v>
+        <v>0.2224210575139147</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3826045641561002</v>
+        <v>0.3782567850179626</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2461489320276259</v>
+        <v>0.2480489320276259</v>
       </c>
       <c r="C90">
-        <v>-40.85546781734524</v>
+        <v>-41.7347138751838</v>
       </c>
       <c r="D90">
-        <v>15.35453218265477</v>
+        <v>15.21028612481621</v>
       </c>
       <c r="E90">
-        <v>31.68000000000001</v>
+        <v>32.41500000000001</v>
       </c>
       <c r="F90">
-        <v>64.68000000000001</v>
+        <v>65.41500000000001</v>
       </c>
       <c r="G90">
         <v>8.470000000000001</v>
@@ -8667,37 +8667,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M90">
-        <v>15.251544</v>
+        <v>15.424857</v>
       </c>
       <c r="N90">
-        <v>-9.482544000000004</v>
+        <v>-9.655857000000005</v>
       </c>
       <c r="O90">
-        <v>-1.422381600000001</v>
+        <v>-1.448378550000001</v>
       </c>
       <c r="P90">
-        <v>-8.060162400000003</v>
+        <v>-8.207478450000004</v>
       </c>
       <c r="Q90">
-        <v>-3.709162400000003</v>
+        <v>-3.856478450000004</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4201533451281753</v>
+        <v>0.4541854674125549</v>
       </c>
       <c r="T90">
-        <v>7.101344624962266</v>
+        <v>7.746921409049746</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0567385177526944</v>
+        <v>0.05610100631727086</v>
       </c>
       <c r="W90">
-        <v>0.2224210575139147</v>
+        <v>0.2225713827103875</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3782567850179626</v>
+        <v>0.3740067087818058</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2480489320276259</v>
+        <v>0.249948932027626</v>
       </c>
       <c r="C91">
-        <v>-41.7347138751838</v>
+        <v>-42.61127495684177</v>
       </c>
       <c r="D91">
-        <v>15.21028612481621</v>
+        <v>15.06872504315824</v>
       </c>
       <c r="E91">
-        <v>32.41500000000001</v>
+        <v>33.15000000000001</v>
       </c>
       <c r="F91">
-        <v>65.41500000000001</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="G91">
         <v>8.470000000000001</v>
@@ -8749,37 +8749,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M91">
-        <v>15.424857</v>
+        <v>15.59817</v>
       </c>
       <c r="N91">
-        <v>-9.655857000000005</v>
+        <v>-9.829170000000001</v>
       </c>
       <c r="O91">
-        <v>-1.448378550000001</v>
+        <v>-1.4743755</v>
       </c>
       <c r="P91">
-        <v>-8.207478450000004</v>
+        <v>-8.354794500000001</v>
       </c>
       <c r="Q91">
-        <v>-3.856478450000004</v>
+        <v>-4.003794500000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4541854674125549</v>
+        <v>0.4950240141538105</v>
       </c>
       <c r="T91">
-        <v>7.746921409049746</v>
+        <v>8.521613549954722</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05610100631727086</v>
+        <v>0.05547766180263453</v>
       </c>
       <c r="W91">
-        <v>0.2225713827103875</v>
+        <v>0.2227183673469388</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3740067087818058</v>
+        <v>0.3698510786842303</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.249948932027626</v>
+        <v>0.2518489320276259</v>
       </c>
       <c r="C92">
-        <v>-42.61127495684177</v>
+        <v>-43.48522533770645</v>
       </c>
       <c r="D92">
-        <v>15.06872504315824</v>
+        <v>14.92977466229355</v>
       </c>
       <c r="E92">
-        <v>33.15000000000001</v>
+        <v>33.88500000000001</v>
       </c>
       <c r="F92">
-        <v>66.15000000000001</v>
+        <v>66.88500000000001</v>
       </c>
       <c r="G92">
         <v>8.470000000000001</v>
@@ -8831,37 +8831,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M92">
-        <v>15.59817</v>
+        <v>15.771483</v>
       </c>
       <c r="N92">
-        <v>-9.829170000000001</v>
+        <v>-10.002483</v>
       </c>
       <c r="O92">
-        <v>-1.4743755</v>
+        <v>-1.50037245</v>
       </c>
       <c r="P92">
-        <v>-8.354794500000001</v>
+        <v>-8.502110550000001</v>
       </c>
       <c r="Q92">
-        <v>-4.003794500000001</v>
+        <v>-4.151110550000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4950240141538105</v>
+        <v>0.5449377935042339</v>
       </c>
       <c r="T92">
-        <v>8.521613549954722</v>
+        <v>9.468459499949692</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05547766180263453</v>
+        <v>0.05486801716744074</v>
       </c>
       <c r="W92">
-        <v>0.2227183673469388</v>
+        <v>0.2228621215519175</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3698510786842303</v>
+        <v>0.3657867811162716</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2518489320276259</v>
+        <v>0.2537489320276259</v>
       </c>
       <c r="C93">
-        <v>-43.48522533770645</v>
+        <v>-44.3566365785903</v>
       </c>
       <c r="D93">
-        <v>14.92977466229355</v>
+        <v>14.79336342140971</v>
       </c>
       <c r="E93">
-        <v>33.88500000000001</v>
+        <v>34.62</v>
       </c>
       <c r="F93">
-        <v>66.88500000000001</v>
+        <v>67.62</v>
       </c>
       <c r="G93">
         <v>8.470000000000001</v>
@@ -8913,37 +8913,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M93">
-        <v>15.771483</v>
+        <v>15.944796</v>
       </c>
       <c r="N93">
-        <v>-10.002483</v>
+        <v>-10.175796</v>
       </c>
       <c r="O93">
-        <v>-1.50037245</v>
+        <v>-1.5263694</v>
       </c>
       <c r="P93">
-        <v>-8.502110550000001</v>
+        <v>-8.649426600000002</v>
       </c>
       <c r="Q93">
-        <v>-4.151110550000001</v>
+        <v>-4.298426600000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5449377935042339</v>
+        <v>0.6073300176922632</v>
       </c>
       <c r="T93">
-        <v>9.468459499949692</v>
+        <v>10.65201693744341</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05486801716744074</v>
+        <v>0.0542716256764903</v>
       </c>
       <c r="W93">
-        <v>0.2228621215519175</v>
+        <v>0.2230027506654836</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3657867811162716</v>
+        <v>0.3618108378432687</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2537489320276259</v>
+        <v>0.255648932027626</v>
       </c>
       <c r="C94">
-        <v>-44.3566365785903</v>
+        <v>-45.22557764862146</v>
       </c>
       <c r="D94">
-        <v>14.79336342140971</v>
+        <v>14.65942235137854</v>
       </c>
       <c r="E94">
-        <v>34.62</v>
+        <v>35.355</v>
       </c>
       <c r="F94">
-        <v>67.62</v>
+        <v>68.355</v>
       </c>
       <c r="G94">
         <v>8.470000000000001</v>
@@ -8995,37 +8995,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M94">
-        <v>15.944796</v>
+        <v>16.118109</v>
       </c>
       <c r="N94">
-        <v>-10.175796</v>
+        <v>-10.349109</v>
       </c>
       <c r="O94">
-        <v>-1.5263694</v>
+        <v>-1.55236635</v>
       </c>
       <c r="P94">
-        <v>-8.649426600000002</v>
+        <v>-8.796742650000002</v>
       </c>
       <c r="Q94">
-        <v>-4.298426600000002</v>
+        <v>-4.445742650000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6073300176922632</v>
+        <v>0.6875485916483008</v>
       </c>
       <c r="T94">
-        <v>10.65201693744341</v>
+        <v>12.17373364279246</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0542716256764903</v>
+        <v>0.05368805980900116</v>
       </c>
       <c r="W94">
-        <v>0.2230027506654836</v>
+        <v>0.2231403554970375</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3618108378432687</v>
+        <v>0.3579203987266744</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.255648932027626</v>
+        <v>0.257548932027626</v>
       </c>
       <c r="C95">
-        <v>-45.22557764862146</v>
+        <v>-46.09211504151838</v>
       </c>
       <c r="D95">
-        <v>14.65942235137854</v>
+        <v>14.52788495848163</v>
       </c>
       <c r="E95">
-        <v>35.355</v>
+        <v>36.09</v>
       </c>
       <c r="F95">
-        <v>68.355</v>
+        <v>69.09</v>
       </c>
       <c r="G95">
         <v>8.470000000000001</v>
@@ -9077,37 +9077,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M95">
-        <v>16.118109</v>
+        <v>16.291422</v>
       </c>
       <c r="N95">
-        <v>-10.349109</v>
+        <v>-10.522422</v>
       </c>
       <c r="O95">
-        <v>-1.55236635</v>
+        <v>-1.5783633</v>
       </c>
       <c r="P95">
-        <v>-8.796742650000002</v>
+        <v>-8.944058700000003</v>
       </c>
       <c r="Q95">
-        <v>-4.445742650000002</v>
+        <v>-4.593058700000003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6875485916483008</v>
+        <v>0.7945066902563512</v>
       </c>
       <c r="T95">
-        <v>12.17373364279246</v>
+        <v>14.20268924992455</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05368805980900116</v>
+        <v>0.05311691023656497</v>
       </c>
       <c r="W95">
-        <v>0.2231403554970375</v>
+        <v>0.223275032566218</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3579203987266744</v>
+        <v>0.3541127349104332</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.257548932027626</v>
+        <v>0.2594489320276259</v>
       </c>
       <c r="C96">
-        <v>-46.09211504151838</v>
+        <v>-46.95631288565993</v>
       </c>
       <c r="D96">
-        <v>14.52788495848163</v>
+        <v>14.39868711434008</v>
       </c>
       <c r="E96">
-        <v>36.09</v>
+        <v>36.825</v>
       </c>
       <c r="F96">
-        <v>69.09</v>
+        <v>69.825</v>
       </c>
       <c r="G96">
         <v>8.470000000000001</v>
@@ -9159,37 +9159,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M96">
-        <v>16.291422</v>
+        <v>16.464735</v>
       </c>
       <c r="N96">
-        <v>-10.522422</v>
+        <v>-10.695735</v>
       </c>
       <c r="O96">
-        <v>-1.5783633</v>
+        <v>-1.60436025</v>
       </c>
       <c r="P96">
-        <v>-8.944058700000003</v>
+        <v>-9.091374750000002</v>
       </c>
       <c r="Q96">
-        <v>-4.593058700000003</v>
+        <v>-4.740374750000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7945066902563512</v>
+        <v>0.944248028307622</v>
       </c>
       <c r="T96">
-        <v>14.20268924992455</v>
+        <v>17.04322709990947</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05311691023656497</v>
+        <v>0.05255778486565376</v>
       </c>
       <c r="W96">
-        <v>0.223275032566218</v>
+        <v>0.2234068743286788</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3541127349104332</v>
+        <v>0.3503852324376917</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2594489320276259</v>
+        <v>0.2613489320276259</v>
       </c>
       <c r="C97">
-        <v>-46.95631288565993</v>
+        <v>-47.81823304833436</v>
       </c>
       <c r="D97">
-        <v>14.39868711434008</v>
+        <v>14.27176695166564</v>
       </c>
       <c r="E97">
-        <v>36.825</v>
+        <v>37.56</v>
       </c>
       <c r="F97">
-        <v>69.825</v>
+        <v>70.56</v>
       </c>
       <c r="G97">
         <v>8.470000000000001</v>
@@ -9241,37 +9241,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M97">
-        <v>16.464735</v>
+        <v>16.638048</v>
       </c>
       <c r="N97">
-        <v>-10.695735</v>
+        <v>-10.869048</v>
       </c>
       <c r="O97">
-        <v>-1.60436025</v>
+        <v>-1.6303572</v>
       </c>
       <c r="P97">
-        <v>-9.091374750000002</v>
+        <v>-9.238690800000002</v>
       </c>
       <c r="Q97">
-        <v>-4.740374750000002</v>
+        <v>-4.887690800000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.944248028307622</v>
+        <v>1.168860035384528</v>
       </c>
       <c r="T97">
-        <v>17.04322709990947</v>
+        <v>21.30403387488684</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05255778486565376</v>
+        <v>0.05201030793996987</v>
       </c>
       <c r="W97">
-        <v>0.2234068743286788</v>
+        <v>0.2235359693877551</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3503852324376917</v>
+        <v>0.3467353862664657</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2613489320276259</v>
+        <v>0.2632489320276259</v>
       </c>
       <c r="C98">
-        <v>-47.81823304833436</v>
+        <v>-48.6779352345227</v>
       </c>
       <c r="D98">
-        <v>14.27176695166564</v>
+        <v>14.1470647654773</v>
       </c>
       <c r="E98">
-        <v>37.56</v>
+        <v>38.295</v>
       </c>
       <c r="F98">
-        <v>70.56</v>
+        <v>71.295</v>
       </c>
       <c r="G98">
         <v>8.470000000000001</v>
@@ -9323,37 +9323,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M98">
-        <v>16.638048</v>
+        <v>16.811361</v>
       </c>
       <c r="N98">
-        <v>-10.869048</v>
+        <v>-11.042361</v>
       </c>
       <c r="O98">
-        <v>-1.6303572</v>
+        <v>-1.656354150000001</v>
       </c>
       <c r="P98">
-        <v>-9.238690800000002</v>
+        <v>-9.386006850000003</v>
       </c>
       <c r="Q98">
-        <v>-4.887690800000002</v>
+        <v>-5.035006850000003</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.168860035384525</v>
+        <v>1.5432133805127</v>
       </c>
       <c r="T98">
-        <v>21.30403387488678</v>
+        <v>28.40537849984904</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05201030793996987</v>
+        <v>0.05147411919832069</v>
       </c>
       <c r="W98">
-        <v>0.2235359693877551</v>
+        <v>0.223662402693036</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3467353862664657</v>
+        <v>0.3431607946554712</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2632489320276259</v>
+        <v>0.2651489320276259</v>
       </c>
       <c r="C99">
-        <v>-48.6779352345227</v>
+        <v>-49.53547708054828</v>
       </c>
       <c r="D99">
-        <v>14.1470647654773</v>
+        <v>14.02452291945172</v>
       </c>
       <c r="E99">
-        <v>38.295</v>
+        <v>39.03</v>
       </c>
       <c r="F99">
-        <v>71.295</v>
+        <v>72.03</v>
       </c>
       <c r="G99">
         <v>8.470000000000001</v>
@@ -9405,37 +9405,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M99">
-        <v>16.811361</v>
+        <v>16.984674</v>
       </c>
       <c r="N99">
-        <v>-11.042361</v>
+        <v>-11.215674</v>
       </c>
       <c r="O99">
-        <v>-1.656354150000001</v>
+        <v>-1.6823511</v>
       </c>
       <c r="P99">
-        <v>-9.386006850000003</v>
+        <v>-9.533322900000003</v>
       </c>
       <c r="Q99">
-        <v>-5.035006850000003</v>
+        <v>-5.182322900000004</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.5432133805127</v>
+        <v>2.291920070769049</v>
       </c>
       <c r="T99">
-        <v>28.40537849984904</v>
+        <v>42.60806774977356</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05147411919832069</v>
+        <v>0.05094887308405212</v>
       </c>
       <c r="W99">
-        <v>0.223662402693036</v>
+        <v>0.2237862557267805</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3431607946554712</v>
+        <v>0.3396591538936807</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2651489320276259</v>
+        <v>0.267048932027626</v>
       </c>
       <c r="C100">
-        <v>-49.53547708054828</v>
+        <v>-50.39091424290093</v>
       </c>
       <c r="D100">
-        <v>14.02452291945172</v>
+        <v>13.90408575709908</v>
       </c>
       <c r="E100">
-        <v>39.03</v>
+        <v>39.765</v>
       </c>
       <c r="F100">
-        <v>72.03</v>
+        <v>72.765</v>
       </c>
       <c r="G100">
         <v>8.470000000000001</v>
@@ -9487,37 +9487,37 @@
         <v>5.768999999999999</v>
       </c>
       <c r="M100">
-        <v>16.984674</v>
+        <v>17.157987</v>
       </c>
       <c r="N100">
-        <v>-11.215674</v>
+        <v>-11.388987</v>
       </c>
       <c r="O100">
-        <v>-1.6823511</v>
+        <v>-1.708348050000001</v>
       </c>
       <c r="P100">
-        <v>-9.533322900000003</v>
+        <v>-9.680638950000002</v>
       </c>
       <c r="Q100">
-        <v>-5.182322900000004</v>
+        <v>-5.329638950000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.291920070769049</v>
+        <v>4.5380401415381</v>
       </c>
       <c r="T100">
-        <v>42.60806774977356</v>
+        <v>85.21613549954714</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05094887308405212</v>
+        <v>0.05043423800239503</v>
       </c>
       <c r="W100">
-        <v>0.2237862557267805</v>
+        <v>0.2239076066790353</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3396591538936807</v>
+        <v>0.3362282533493001</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.267048932027626</v>
-      </c>
-      <c r="C101">
-        <v>-50.39091424290093</v>
-      </c>
-      <c r="D101">
-        <v>13.90408575709908</v>
-      </c>
-      <c r="E101">
-        <v>39.765</v>
-      </c>
-      <c r="F101">
-        <v>72.765</v>
-      </c>
-      <c r="G101">
-        <v>8.470000000000001</v>
-      </c>
-      <c r="H101">
-        <v>40.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>10.12</v>
-      </c>
-      <c r="K101">
-        <v>4.351</v>
-      </c>
-      <c r="L101">
-        <v>5.768999999999999</v>
-      </c>
-      <c r="M101">
-        <v>17.157987</v>
-      </c>
-      <c r="N101">
-        <v>-11.388987</v>
-      </c>
-      <c r="O101">
-        <v>-1.708348050000001</v>
-      </c>
-      <c r="P101">
-        <v>-9.680638950000002</v>
-      </c>
-      <c r="Q101">
-        <v>-5.329638950000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.5380401415381</v>
-      </c>
-      <c r="T101">
-        <v>85.21613549954714</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05043423800239503</v>
-      </c>
-      <c r="W101">
-        <v>0.2239076066790353</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3362282533493001</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
